--- a/data/talt_cyano/talt_cyano_digitized.xlsx
+++ b/data/talt_cyano/talt_cyano_digitized.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29116"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29212"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="19093" documentId="11_0B1D56BE9CDCCE836B02CE7A5FB0D4A9BBFD1C62" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F2ADCEC-DB11-48E8-ADF7-5530D4630CAD}"/>
+  <xr:revisionPtr revIDLastSave="20435" documentId="11_0B1D56BE9CDCCE836B02CE7A5FB0D4A9BBFD1C62" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ED0097AE-E8BF-4194-85E9-A632FE632A20}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1614" uniqueCount="359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1854" uniqueCount="390">
   <si>
     <t>Date</t>
   </si>
@@ -1050,6 +1050,9 @@
     <t>High wave action, dirty</t>
   </si>
   <si>
+    <t xml:space="preserve">B </t>
+  </si>
+  <si>
     <t xml:space="preserve">Tamateaāio </t>
   </si>
   <si>
@@ -1071,6 +1074,9 @@
     <t>Light wave action</t>
   </si>
   <si>
+    <t>Logged samples came up as 0 on the missing values on the proDSS?</t>
+  </si>
+  <si>
     <t xml:space="preserve">Light wave action </t>
   </si>
   <si>
@@ -1086,10 +1092,19 @@
     <t xml:space="preserve">FluoroQuick Mal </t>
   </si>
   <si>
+    <t xml:space="preserve">Rakaumotahi </t>
+  </si>
+  <si>
     <t>14/07/2025</t>
   </si>
   <si>
+    <t>Korekore-te-whiwhia</t>
+  </si>
+  <si>
     <t xml:space="preserve">16/07/2025 </t>
+  </si>
+  <si>
+    <t>Korekore-piri-ki-ngā-Tangaroa</t>
   </si>
   <si>
     <t xml:space="preserve">18/07/2025 </t>
@@ -1107,7 +1122,85 @@
     <t>23/07/2025</t>
   </si>
   <si>
-    <t>26/07/2025</t>
+    <t>25/07/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIND DATA SHEET WHERE DID IT GOOOOO!!! </t>
+  </si>
+  <si>
+    <t>28/07/2025</t>
+  </si>
+  <si>
+    <t>Ripples</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31/07/2025 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tamateangana </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blue skies, partly cloudy. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sampling after heavy rains </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blue skies, high winds </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloudy, light winds </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ripples,  clear </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sensor unscrewed from probe, couldn't open chamber to rescrew and fix so was advised to not use it until fixed! </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Probe Malfunction </t>
+  </si>
+  <si>
+    <t xml:space="preserve">After heavy rains </t>
+  </si>
+  <si>
+    <t>13/8/2025</t>
+  </si>
+  <si>
+    <t>Korekore-te-whiawhia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ripples, hazy </t>
+  </si>
+  <si>
+    <t>14/08/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Partly cloudy </t>
+  </si>
+  <si>
+    <t xml:space="preserve">flat, clear-hazy </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ripples, clear </t>
+  </si>
+  <si>
+    <t xml:space="preserve">15/08/2025 </t>
+  </si>
+  <si>
+    <t>Korekore-piri-ki-nga-tangaroa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sunny with partial cloud </t>
+  </si>
+  <si>
+    <t xml:space="preserve">18/08/2025 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">20/08/2025 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">22/08/2025 </t>
   </si>
 </sst>
 </file>
@@ -1268,7 +1361,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1330,6 +1423,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1664,7 +1758,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S2334"/>
+  <dimension ref="A1:S2707"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.7109375" customWidth="1"/>
@@ -57178,7 +57272,7 @@
         <v>1</v>
       </c>
       <c r="E1995" s="2" t="s">
-        <v>21</v>
+        <v>339</v>
       </c>
       <c r="F1995">
         <v>0.1</v>
@@ -57202,13 +57296,13 @@
         <v>0.15</v>
       </c>
       <c r="P1995" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q1995" t="s">
         <v>212</v>
       </c>
       <c r="R1995" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="1996" spans="1:18">
@@ -57812,7 +57906,7 @@
         <v>1</v>
       </c>
       <c r="E2026" s="2" t="s">
-        <v>21</v>
+        <v>339</v>
       </c>
       <c r="F2026">
         <v>0.1</v>
@@ -57836,7 +57930,7 @@
         <v>1</v>
       </c>
       <c r="P2026" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q2026" t="s">
         <v>328</v>
@@ -57905,7 +57999,7 @@
         <v>1.02</v>
       </c>
       <c r="R2029" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="2030" spans="1:18">
@@ -57968,7 +58062,7 @@
         <v>1.79</v>
       </c>
       <c r="R2032" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="2033" spans="2:18">
@@ -58031,7 +58125,7 @@
         <v>2.36</v>
       </c>
       <c r="R2035" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="2036" spans="2:18">
@@ -58094,7 +58188,7 @@
         <v>0.99</v>
       </c>
       <c r="R2038" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="2039" spans="2:18">
@@ -58157,7 +58251,7 @@
         <v>0.42</v>
       </c>
       <c r="R2041" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="2042" spans="2:18">
@@ -58217,7 +58311,7 @@
         <v>0.66</v>
       </c>
       <c r="R2044" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="2045" spans="2:18">
@@ -58294,7 +58388,7 @@
         <v>0.41</v>
       </c>
     </row>
-    <row r="2049" spans="1:18">
+    <row r="2049" spans="1:19">
       <c r="D2049">
         <v>3</v>
       </c>
@@ -58308,7 +58402,7 @@
         <v>0.41</v>
       </c>
     </row>
-    <row r="2050" spans="1:18">
+    <row r="2050" spans="1:19">
       <c r="B2050" s="1">
         <v>0.59722222222222221</v>
       </c>
@@ -58340,7 +58434,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="2051" spans="1:18">
+    <row r="2051" spans="1:19">
       <c r="D2051">
         <v>2</v>
       </c>
@@ -58354,7 +58448,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="2052" spans="1:18">
+    <row r="2052" spans="1:19">
       <c r="D2052">
         <v>3</v>
       </c>
@@ -58368,7 +58462,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="2053" spans="1:18">
+    <row r="2053" spans="1:19">
       <c r="B2053" s="1">
         <v>0.59722222222222221</v>
       </c>
@@ -58397,7 +58491,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="2054" spans="1:18">
+    <row r="2054" spans="1:19">
       <c r="C2054" s="3"/>
       <c r="D2054">
         <v>2</v>
@@ -58412,7 +58506,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="2055" spans="1:18">
+    <row r="2055" spans="1:19">
       <c r="D2055">
         <v>3</v>
       </c>
@@ -58426,10 +58520,10 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="2056" spans="1:18" s="19" customFormat="1">
+    <row r="2056" spans="1:19" s="19" customFormat="1">
       <c r="E2056" s="36"/>
     </row>
-    <row r="2057" spans="1:18">
+    <row r="2057" spans="1:19">
       <c r="A2057" s="16">
         <v>45845</v>
       </c>
@@ -58443,7 +58537,7 @@
         <v>1</v>
       </c>
       <c r="E2057" s="2" t="s">
-        <v>21</v>
+        <v>56</v>
       </c>
       <c r="F2057">
         <v>0.1</v>
@@ -58467,13 +58561,16 @@
         <v>105</v>
       </c>
       <c r="Q2057" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="R2057" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="2058" spans="1:18">
+        <v>346</v>
+      </c>
+      <c r="S2057" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="2058" spans="1:19">
       <c r="D2058">
         <v>2</v>
       </c>
@@ -58487,7 +58584,7 @@
         <v>3.33</v>
       </c>
     </row>
-    <row r="2059" spans="1:18">
+    <row r="2059" spans="1:19">
       <c r="D2059">
         <v>3</v>
       </c>
@@ -58501,7 +58598,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="2060" spans="1:18">
+    <row r="2060" spans="1:19">
       <c r="B2060" s="1">
         <v>0.5625</v>
       </c>
@@ -58533,10 +58630,10 @@
         <v>0.21</v>
       </c>
       <c r="R2060" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="2061" spans="1:18">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="2061" spans="1:19">
       <c r="D2061">
         <v>2</v>
       </c>
@@ -58550,7 +58647,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="2062" spans="1:18">
+    <row r="2062" spans="1:19">
       <c r="D2062">
         <v>3</v>
       </c>
@@ -58564,7 +58661,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="2063" spans="1:18">
+    <row r="2063" spans="1:19">
       <c r="B2063" s="1">
         <v>0.58333333333333337</v>
       </c>
@@ -58596,10 +58693,10 @@
         <v>55.87</v>
       </c>
       <c r="R2063" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="2064" spans="1:18">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="2064" spans="1:19">
       <c r="D2064">
         <v>2</v>
       </c>
@@ -58992,10 +59089,10 @@
         <v>0.47</v>
       </c>
       <c r="R2084" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="S2084" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="2085" spans="1:19">
@@ -59044,7 +59141,7 @@
         <v>1</v>
       </c>
       <c r="E2088" s="2" t="s">
-        <v>21</v>
+        <v>56</v>
       </c>
       <c r="F2088">
         <v>0.1</v>
@@ -59068,13 +59165,13 @@
         <v>0.28999999999999998</v>
       </c>
       <c r="P2088" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Q2088" t="s">
         <v>212</v>
       </c>
       <c r="R2088" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="2089" spans="1:19">
@@ -59200,7 +59297,7 @@
         <v>0.8</v>
       </c>
       <c r="R2094" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="2095" spans="1:19">
@@ -59263,7 +59360,7 @@
         <v>0.74</v>
       </c>
       <c r="R2097" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="2098" spans="2:18">
@@ -59326,7 +59423,7 @@
         <v>0.2</v>
       </c>
       <c r="R2100" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="2101" spans="2:18">
@@ -59389,7 +59486,7 @@
         <v>0.34</v>
       </c>
       <c r="R2103" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="2104" spans="2:18">
@@ -59452,7 +59549,7 @@
         <v>0</v>
       </c>
       <c r="R2106" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="2107" spans="2:18">
@@ -59515,7 +59612,7 @@
         <v>0.24</v>
       </c>
       <c r="R2109" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="2110" spans="2:18">
@@ -59578,10 +59675,10 @@
         <v>0.09</v>
       </c>
       <c r="R2112" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="2113" spans="1:15">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="2113" spans="1:16">
       <c r="D2113">
         <v>2</v>
       </c>
@@ -59595,7 +59692,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="2114" spans="1:15">
+    <row r="2114" spans="1:16">
       <c r="D2114">
         <v>3</v>
       </c>
@@ -59609,7 +59706,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="2115" spans="1:15">
+    <row r="2115" spans="1:16">
       <c r="B2115" s="1">
         <v>0.5625</v>
       </c>
@@ -59641,7 +59738,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="2116" spans="1:15">
+    <row r="2116" spans="1:16">
       <c r="C2116" s="3"/>
       <c r="D2116">
         <v>2</v>
@@ -59656,7 +59753,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="2117" spans="1:15">
+    <row r="2117" spans="1:16">
       <c r="D2117">
         <v>3</v>
       </c>
@@ -59670,10 +59767,10 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="2118" spans="1:15" s="19" customFormat="1">
+    <row r="2118" spans="1:16" s="19" customFormat="1">
       <c r="E2118" s="36"/>
     </row>
-    <row r="2119" spans="1:15">
+    <row r="2119" spans="1:16">
       <c r="A2119" s="16">
         <v>45968</v>
       </c>
@@ -59683,11 +59780,8 @@
       <c r="D2119">
         <v>1</v>
       </c>
-      <c r="E2119" s="2" t="s">
-        <v>21</v>
-      </c>
       <c r="G2119" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="L2119">
         <v>12.8</v>
@@ -59701,18 +59795,21 @@
       <c r="O2119">
         <v>1.1599999999999999</v>
       </c>
-    </row>
-    <row r="2120" spans="1:15">
+      <c r="P2119" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="2120" spans="1:16">
       <c r="D2120">
         <v>2</v>
       </c>
     </row>
-    <row r="2121" spans="1:15">
+    <row r="2121" spans="1:16">
       <c r="D2121">
         <v>3</v>
       </c>
     </row>
-    <row r="2122" spans="1:15">
+    <row r="2122" spans="1:16">
       <c r="C2122" s="3" t="s">
         <v>25</v>
       </c>
@@ -59732,17 +59829,17 @@
         <v>0.38</v>
       </c>
     </row>
-    <row r="2123" spans="1:15">
+    <row r="2123" spans="1:16">
       <c r="D2123">
         <v>2</v>
       </c>
     </row>
-    <row r="2124" spans="1:15">
+    <row r="2124" spans="1:16">
       <c r="D2124">
         <v>3</v>
       </c>
     </row>
-    <row r="2125" spans="1:15">
+    <row r="2125" spans="1:16">
       <c r="C2125" s="3" t="s">
         <v>27</v>
       </c>
@@ -59762,17 +59859,17 @@
         <v>1.54</v>
       </c>
     </row>
-    <row r="2126" spans="1:15">
+    <row r="2126" spans="1:16">
       <c r="D2126">
         <v>2</v>
       </c>
     </row>
-    <row r="2127" spans="1:15">
+    <row r="2127" spans="1:16">
       <c r="D2127">
         <v>3</v>
       </c>
     </row>
-    <row r="2128" spans="1:15">
+    <row r="2128" spans="1:16">
       <c r="C2128" s="3" t="s">
         <v>58</v>
       </c>
@@ -59947,12 +60044,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2145" spans="1:15">
+    <row r="2145" spans="1:16">
       <c r="D2145">
         <v>3</v>
       </c>
     </row>
-    <row r="2146" spans="1:15">
+    <row r="2146" spans="1:16">
       <c r="C2146" s="3" t="s">
         <v>34</v>
       </c>
@@ -59972,23 +60069,23 @@
         <v>6.33</v>
       </c>
     </row>
-    <row r="2147" spans="1:15">
+    <row r="2147" spans="1:16">
       <c r="C2147" s="3"/>
       <c r="D2147">
         <v>2</v>
       </c>
     </row>
-    <row r="2148" spans="1:15">
+    <row r="2148" spans="1:16">
       <c r="D2148">
         <v>3</v>
       </c>
     </row>
-    <row r="2149" spans="1:15" s="19" customFormat="1">
+    <row r="2149" spans="1:16" s="19" customFormat="1">
       <c r="E2149" s="36"/>
     </row>
-    <row r="2150" spans="1:15">
+    <row r="2150" spans="1:16">
       <c r="A2150" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="C2150" s="3" t="s">
         <v>20</v>
@@ -59996,9 +60093,6 @@
       <c r="D2150">
         <v>1</v>
       </c>
-      <c r="E2150" s="2" t="s">
-        <v>21</v>
-      </c>
       <c r="L2150">
         <v>12.9</v>
       </c>
@@ -60011,18 +60105,21 @@
       <c r="O2150">
         <v>0.68</v>
       </c>
-    </row>
-    <row r="2151" spans="1:15">
+      <c r="P2150" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="2151" spans="1:16">
       <c r="D2151">
         <v>2</v>
       </c>
     </row>
-    <row r="2152" spans="1:15">
+    <row r="2152" spans="1:16">
       <c r="D2152">
         <v>3</v>
       </c>
     </row>
-    <row r="2153" spans="1:15">
+    <row r="2153" spans="1:16">
       <c r="C2153" s="3" t="s">
         <v>25</v>
       </c>
@@ -60042,17 +60139,17 @@
         <v>0.32</v>
       </c>
     </row>
-    <row r="2154" spans="1:15">
+    <row r="2154" spans="1:16">
       <c r="D2154">
         <v>2</v>
       </c>
     </row>
-    <row r="2155" spans="1:15">
+    <row r="2155" spans="1:16">
       <c r="D2155">
         <v>3</v>
       </c>
     </row>
-    <row r="2156" spans="1:15">
+    <row r="2156" spans="1:16">
       <c r="C2156" s="3" t="s">
         <v>27</v>
       </c>
@@ -60072,17 +60169,17 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="2157" spans="1:15">
+    <row r="2157" spans="1:16">
       <c r="D2157">
         <v>2</v>
       </c>
     </row>
-    <row r="2158" spans="1:15">
+    <row r="2158" spans="1:16">
       <c r="D2158">
         <v>3</v>
       </c>
     </row>
-    <row r="2159" spans="1:15">
+    <row r="2159" spans="1:16">
       <c r="C2159" s="3" t="s">
         <v>58</v>
       </c>
@@ -60102,7 +60199,7 @@
         <v>4.4800000000000004</v>
       </c>
     </row>
-    <row r="2160" spans="1:15">
+    <row r="2160" spans="1:16">
       <c r="D2160">
         <v>2</v>
       </c>
@@ -60262,7 +60359,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2177" spans="1:15">
+    <row r="2177" spans="1:16">
       <c r="C2177" s="3" t="s">
         <v>34</v>
       </c>
@@ -60282,23 +60379,23 @@
         <v>0.77</v>
       </c>
     </row>
-    <row r="2178" spans="1:15">
+    <row r="2178" spans="1:16">
       <c r="C2178" s="3"/>
       <c r="D2178">
         <v>2</v>
       </c>
     </row>
-    <row r="2179" spans="1:15">
+    <row r="2179" spans="1:16">
       <c r="D2179">
         <v>3</v>
       </c>
     </row>
-    <row r="2180" spans="1:15" s="19" customFormat="1">
+    <row r="2180" spans="1:16" s="19" customFormat="1">
       <c r="E2180" s="36"/>
     </row>
-    <row r="2181" spans="1:15">
+    <row r="2181" spans="1:16">
       <c r="A2181" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="B2181" s="1">
         <v>0.47916666666666669</v>
@@ -60333,8 +60430,11 @@
       <c r="O2181">
         <v>0.68</v>
       </c>
-    </row>
-    <row r="2182" spans="1:15">
+      <c r="P2181" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="2182" spans="1:16">
       <c r="D2182">
         <v>2</v>
       </c>
@@ -60348,7 +60448,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="2183" spans="1:15">
+    <row r="2183" spans="1:16">
       <c r="D2183">
         <v>3</v>
       </c>
@@ -60362,7 +60462,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="2184" spans="1:15">
+    <row r="2184" spans="1:16">
       <c r="B2184" s="1">
         <v>0.49027777777777776</v>
       </c>
@@ -60394,7 +60494,7 @@
         <v>1.18</v>
       </c>
     </row>
-    <row r="2185" spans="1:15">
+    <row r="2185" spans="1:16">
       <c r="D2185">
         <v>2</v>
       </c>
@@ -60408,7 +60508,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="2186" spans="1:15">
+    <row r="2186" spans="1:16">
       <c r="D2186">
         <v>3</v>
       </c>
@@ -60422,7 +60522,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="2187" spans="1:15">
+    <row r="2187" spans="1:16">
       <c r="B2187" s="1">
         <v>0.50277777777777777</v>
       </c>
@@ -60454,7 +60554,7 @@
         <v>0.89</v>
       </c>
     </row>
-    <row r="2188" spans="1:15">
+    <row r="2188" spans="1:16">
       <c r="D2188">
         <v>2</v>
       </c>
@@ -60468,7 +60568,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="2189" spans="1:15">
+    <row r="2189" spans="1:16">
       <c r="D2189">
         <v>3</v>
       </c>
@@ -60482,7 +60582,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="2190" spans="1:15">
+    <row r="2190" spans="1:16">
       <c r="B2190" s="1">
         <v>0.51736111111111116</v>
       </c>
@@ -60514,7 +60614,7 @@
         <v>2.23</v>
       </c>
     </row>
-    <row r="2191" spans="1:15">
+    <row r="2191" spans="1:16">
       <c r="D2191">
         <v>2</v>
       </c>
@@ -60528,7 +60628,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="2192" spans="1:15">
+    <row r="2192" spans="1:16">
       <c r="D2192">
         <v>3</v>
       </c>
@@ -60908,7 +61008,7 @@
     </row>
     <row r="2212" spans="1:18">
       <c r="A2212" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="B2212" s="1">
         <v>0.45833333333333331</v>
@@ -60950,7 +61050,7 @@
         <v>212</v>
       </c>
       <c r="R2212" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="2213" spans="1:18">
@@ -61517,7 +61617,7 @@
         <v>0.04</v>
       </c>
       <c r="R2239" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="2240" spans="2:18">
@@ -61554,7 +61654,7 @@
     </row>
     <row r="2243" spans="1:18">
       <c r="A2243" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="B2243" s="1">
         <v>0.50416666666666665</v>
@@ -61593,7 +61693,7 @@
         <v>147</v>
       </c>
       <c r="Q2243" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="R2243" t="s">
         <v>171</v>
@@ -61848,7 +61948,7 @@
         <v>0.2</v>
       </c>
       <c r="R2255" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
     </row>
     <row r="2256" spans="1:18">
@@ -62200,7 +62300,7 @@
     </row>
     <row r="2274" spans="1:17">
       <c r="A2274" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="C2274" s="3" t="s">
         <v>20</v>
@@ -62236,7 +62336,7 @@
         <v>157</v>
       </c>
       <c r="Q2274" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
     </row>
     <row r="2275" spans="1:17">
@@ -62784,9 +62884,9 @@
     <row r="2304" spans="3:15" s="19" customFormat="1">
       <c r="E2304" s="36"/>
     </row>
-    <row r="2305" spans="1:5">
+    <row r="2305" spans="1:19">
       <c r="A2305" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="C2305" s="3" t="s">
         <v>20</v>
@@ -62797,18 +62897,21 @@
       <c r="E2305" s="2" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="2306" spans="1:5">
+      <c r="S2305" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="2306" spans="1:19">
       <c r="D2306">
         <v>2</v>
       </c>
     </row>
-    <row r="2307" spans="1:5">
+    <row r="2307" spans="1:19">
       <c r="D2307">
         <v>3</v>
       </c>
     </row>
-    <row r="2308" spans="1:5">
+    <row r="2308" spans="1:19">
       <c r="C2308" s="3" t="s">
         <v>25</v>
       </c>
@@ -62816,17 +62919,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2309" spans="1:5">
+    <row r="2309" spans="1:19">
       <c r="D2309">
         <v>2</v>
       </c>
     </row>
-    <row r="2310" spans="1:5">
+    <row r="2310" spans="1:19">
       <c r="D2310">
         <v>3</v>
       </c>
     </row>
-    <row r="2311" spans="1:5">
+    <row r="2311" spans="1:19">
       <c r="C2311" s="3" t="s">
         <v>27</v>
       </c>
@@ -62834,17 +62937,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2312" spans="1:5">
+    <row r="2312" spans="1:19">
       <c r="D2312">
         <v>2</v>
       </c>
     </row>
-    <row r="2313" spans="1:5">
+    <row r="2313" spans="1:19">
       <c r="D2313">
         <v>3</v>
       </c>
     </row>
-    <row r="2314" spans="1:5">
+    <row r="2314" spans="1:19">
       <c r="C2314" s="3" t="s">
         <v>58</v>
       </c>
@@ -62852,17 +62955,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2315" spans="1:5">
+    <row r="2315" spans="1:19">
       <c r="D2315">
         <v>2</v>
       </c>
     </row>
-    <row r="2316" spans="1:5">
+    <row r="2316" spans="1:19">
       <c r="D2316">
         <v>3</v>
       </c>
     </row>
-    <row r="2317" spans="1:5">
+    <row r="2317" spans="1:19">
       <c r="C2317" s="3" t="s">
         <v>29</v>
       </c>
@@ -62870,17 +62973,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2318" spans="1:5">
+    <row r="2318" spans="1:19">
       <c r="D2318">
         <v>2</v>
       </c>
     </row>
-    <row r="2319" spans="1:5">
+    <row r="2319" spans="1:19">
       <c r="D2319">
         <v>3</v>
       </c>
     </row>
-    <row r="2320" spans="1:5">
+    <row r="2320" spans="1:19">
       <c r="C2320" s="3" t="s">
         <v>30</v>
       </c>
@@ -62888,17 +62991,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2321" spans="3:4">
+    <row r="2321" spans="1:18">
       <c r="D2321">
         <v>2</v>
       </c>
     </row>
-    <row r="2322" spans="3:4">
+    <row r="2322" spans="1:18">
       <c r="D2322">
         <v>3</v>
       </c>
     </row>
-    <row r="2323" spans="3:4">
+    <row r="2323" spans="1:18">
       <c r="C2323" s="3" t="s">
         <v>31</v>
       </c>
@@ -62906,17 +63009,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2324" spans="3:4">
+    <row r="2324" spans="1:18">
       <c r="D2324">
         <v>2</v>
       </c>
     </row>
-    <row r="2325" spans="3:4">
+    <row r="2325" spans="1:18">
       <c r="D2325">
         <v>3</v>
       </c>
     </row>
-    <row r="2326" spans="3:4">
+    <row r="2326" spans="1:18">
       <c r="C2326" s="3" t="s">
         <v>32</v>
       </c>
@@ -62924,17 +63027,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2327" spans="3:4">
+    <row r="2327" spans="1:18">
       <c r="D2327">
         <v>2</v>
       </c>
     </row>
-    <row r="2328" spans="3:4">
+    <row r="2328" spans="1:18">
       <c r="D2328">
         <v>3</v>
       </c>
     </row>
-    <row r="2329" spans="3:4">
+    <row r="2329" spans="1:18">
       <c r="C2329" s="3" t="s">
         <v>41</v>
       </c>
@@ -62942,17 +63045,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2330" spans="3:4">
+    <row r="2330" spans="1:18">
       <c r="D2330">
         <v>2</v>
       </c>
     </row>
-    <row r="2331" spans="3:4">
+    <row r="2331" spans="1:18">
       <c r="D2331">
         <v>3</v>
       </c>
     </row>
-    <row r="2332" spans="3:4">
+    <row r="2332" spans="1:18">
       <c r="C2332" s="3" t="s">
         <v>34</v>
       </c>
@@ -62960,16 +63063,7028 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2333" spans="3:4">
+    <row r="2333" spans="1:18">
       <c r="C2333" s="3"/>
       <c r="D2333">
         <v>2</v>
       </c>
     </row>
-    <row r="2334" spans="3:4">
+    <row r="2334" spans="1:18">
       <c r="D2334">
         <v>3</v>
       </c>
+    </row>
+    <row r="2335" spans="1:18" s="19" customFormat="1">
+      <c r="E2335" s="36"/>
+    </row>
+    <row r="2336" spans="1:18">
+      <c r="A2336" t="s">
+        <v>365</v>
+      </c>
+      <c r="B2336" s="1">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="C2336" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2336">
+        <v>1</v>
+      </c>
+      <c r="E2336" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2336">
+        <v>0.1</v>
+      </c>
+      <c r="G2336">
+        <v>0</v>
+      </c>
+      <c r="H2336">
+        <v>0</v>
+      </c>
+      <c r="L2336">
+        <v>10.8</v>
+      </c>
+      <c r="M2336">
+        <v>98.6</v>
+      </c>
+      <c r="N2336">
+        <v>0.85</v>
+      </c>
+      <c r="O2336">
+        <v>0.53</v>
+      </c>
+      <c r="P2336" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q2336" t="s">
+        <v>360</v>
+      </c>
+      <c r="R2336" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="2337" spans="2:15">
+      <c r="D2337">
+        <v>2</v>
+      </c>
+      <c r="F2337">
+        <v>0.1</v>
+      </c>
+      <c r="G2337">
+        <v>0</v>
+      </c>
+      <c r="H2337">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2338" spans="2:15">
+      <c r="D2338">
+        <v>3</v>
+      </c>
+      <c r="F2338">
+        <v>0.1</v>
+      </c>
+      <c r="G2338">
+        <v>0.2</v>
+      </c>
+      <c r="H2338">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="2339" spans="2:15">
+      <c r="B2339" s="1">
+        <v>0.44236111111111109</v>
+      </c>
+      <c r="C2339" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2339">
+        <v>1</v>
+      </c>
+      <c r="F2339">
+        <v>0.1</v>
+      </c>
+      <c r="G2339">
+        <v>0</v>
+      </c>
+      <c r="H2339">
+        <v>0</v>
+      </c>
+      <c r="L2339">
+        <v>10.7</v>
+      </c>
+      <c r="M2339">
+        <v>94</v>
+      </c>
+      <c r="N2339">
+        <v>0.67</v>
+      </c>
+      <c r="O2339">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="2340" spans="2:15">
+      <c r="D2340">
+        <v>2</v>
+      </c>
+      <c r="F2340">
+        <v>0.1</v>
+      </c>
+      <c r="G2340">
+        <v>0</v>
+      </c>
+      <c r="H2340">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2341" spans="2:15">
+      <c r="D2341">
+        <v>3</v>
+      </c>
+      <c r="F2341">
+        <v>0.1</v>
+      </c>
+      <c r="G2341">
+        <v>0</v>
+      </c>
+      <c r="H2341">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2342" spans="2:15">
+      <c r="B2342" s="1">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="C2342" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2342">
+        <v>1</v>
+      </c>
+      <c r="F2342">
+        <v>0.1</v>
+      </c>
+      <c r="G2342">
+        <v>0.2</v>
+      </c>
+      <c r="H2342">
+        <v>0.5</v>
+      </c>
+      <c r="L2342">
+        <v>10.5</v>
+      </c>
+      <c r="M2342">
+        <v>97.5</v>
+      </c>
+      <c r="N2342">
+        <v>1.22</v>
+      </c>
+      <c r="O2342">
+        <v>0.69</v>
+      </c>
+    </row>
+    <row r="2343" spans="2:15">
+      <c r="D2343">
+        <v>2</v>
+      </c>
+      <c r="F2343">
+        <v>0.1</v>
+      </c>
+      <c r="G2343">
+        <v>0</v>
+      </c>
+      <c r="H2343">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2344" spans="2:15">
+      <c r="D2344">
+        <v>3</v>
+      </c>
+      <c r="F2344">
+        <v>0.1</v>
+      </c>
+      <c r="G2344">
+        <v>0</v>
+      </c>
+      <c r="H2344">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2345" spans="2:15">
+      <c r="B2345" s="1">
+        <v>0.46875</v>
+      </c>
+      <c r="C2345" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D2345">
+        <v>1</v>
+      </c>
+      <c r="F2345">
+        <v>0.1</v>
+      </c>
+      <c r="G2345">
+        <v>0</v>
+      </c>
+      <c r="H2345">
+        <v>0</v>
+      </c>
+      <c r="L2345">
+        <v>10.7</v>
+      </c>
+      <c r="M2345">
+        <v>98.3</v>
+      </c>
+      <c r="N2345">
+        <v>1.02</v>
+      </c>
+      <c r="O2345">
+        <v>0.61</v>
+      </c>
+    </row>
+    <row r="2346" spans="2:15">
+      <c r="D2346">
+        <v>2</v>
+      </c>
+      <c r="F2346">
+        <v>0.1</v>
+      </c>
+      <c r="G2346">
+        <v>0</v>
+      </c>
+      <c r="H2346">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2347" spans="2:15">
+      <c r="D2347">
+        <v>3</v>
+      </c>
+      <c r="F2347">
+        <v>0.1</v>
+      </c>
+      <c r="G2347">
+        <v>0</v>
+      </c>
+      <c r="H2347">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2348" spans="2:15">
+      <c r="B2348" s="1">
+        <v>0.48125000000000001</v>
+      </c>
+      <c r="C2348" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2348">
+        <v>1</v>
+      </c>
+      <c r="F2348">
+        <v>0.1</v>
+      </c>
+      <c r="G2348">
+        <v>0</v>
+      </c>
+      <c r="H2348">
+        <v>0</v>
+      </c>
+      <c r="L2348">
+        <v>10.9</v>
+      </c>
+      <c r="M2348">
+        <v>104.4</v>
+      </c>
+      <c r="N2348">
+        <v>0.6</v>
+      </c>
+      <c r="O2348">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="2349" spans="2:15">
+      <c r="D2349">
+        <v>2</v>
+      </c>
+      <c r="F2349">
+        <v>0.1</v>
+      </c>
+      <c r="G2349">
+        <v>0</v>
+      </c>
+      <c r="H2349">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2350" spans="2:15">
+      <c r="D2350">
+        <v>3</v>
+      </c>
+      <c r="F2350">
+        <v>0.1</v>
+      </c>
+      <c r="G2350">
+        <v>0</v>
+      </c>
+      <c r="H2350">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2351" spans="2:15">
+      <c r="B2351" s="1">
+        <v>0.48680555555555555</v>
+      </c>
+      <c r="C2351" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2351">
+        <v>1</v>
+      </c>
+      <c r="F2351">
+        <v>0.1</v>
+      </c>
+      <c r="G2351">
+        <v>0</v>
+      </c>
+      <c r="H2351">
+        <v>0</v>
+      </c>
+      <c r="L2351">
+        <v>11</v>
+      </c>
+      <c r="M2351">
+        <v>109.9</v>
+      </c>
+      <c r="N2351">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="O2351">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="2352" spans="2:15">
+      <c r="D2352">
+        <v>2</v>
+      </c>
+      <c r="F2352">
+        <v>0.1</v>
+      </c>
+      <c r="G2352">
+        <v>0</v>
+      </c>
+      <c r="H2352">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2353" spans="1:19">
+      <c r="D2353">
+        <v>3</v>
+      </c>
+      <c r="F2353">
+        <v>0.1</v>
+      </c>
+      <c r="G2353">
+        <v>0</v>
+      </c>
+      <c r="H2353">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2354" spans="1:19">
+      <c r="B2354" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="C2354" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2354">
+        <v>1</v>
+      </c>
+      <c r="F2354">
+        <v>0.1</v>
+      </c>
+      <c r="G2354">
+        <v>0</v>
+      </c>
+      <c r="H2354">
+        <v>0</v>
+      </c>
+      <c r="L2354">
+        <v>12.3</v>
+      </c>
+      <c r="M2354">
+        <v>100.3</v>
+      </c>
+      <c r="N2354">
+        <v>0.81</v>
+      </c>
+      <c r="O2354">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="2355" spans="1:19">
+      <c r="D2355">
+        <v>2</v>
+      </c>
+      <c r="F2355">
+        <v>0.1</v>
+      </c>
+      <c r="G2355">
+        <v>0</v>
+      </c>
+      <c r="H2355">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2356" spans="1:19">
+      <c r="D2356">
+        <v>3</v>
+      </c>
+      <c r="F2356">
+        <v>0.1</v>
+      </c>
+      <c r="G2356">
+        <v>0</v>
+      </c>
+      <c r="H2356">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2357" spans="1:19">
+      <c r="B2357" s="1">
+        <v>0.52152777777777781</v>
+      </c>
+      <c r="C2357" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2357">
+        <v>1</v>
+      </c>
+      <c r="F2357">
+        <v>0.1</v>
+      </c>
+      <c r="G2357">
+        <v>0</v>
+      </c>
+      <c r="H2357">
+        <v>0</v>
+      </c>
+      <c r="L2357">
+        <v>10.9</v>
+      </c>
+      <c r="M2357">
+        <v>98.7</v>
+      </c>
+      <c r="N2357">
+        <v>4.0599999999999996</v>
+      </c>
+      <c r="O2357">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="2358" spans="1:19">
+      <c r="D2358">
+        <v>2</v>
+      </c>
+      <c r="F2358">
+        <v>0.1</v>
+      </c>
+      <c r="G2358">
+        <v>0</v>
+      </c>
+      <c r="H2358">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2359" spans="1:19">
+      <c r="D2359">
+        <v>3</v>
+      </c>
+      <c r="F2359">
+        <v>0.1</v>
+      </c>
+      <c r="G2359">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="H2359">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="2360" spans="1:19">
+      <c r="B2360" s="1">
+        <v>0.52916666666666667</v>
+      </c>
+      <c r="C2360" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D2360">
+        <v>1</v>
+      </c>
+      <c r="F2360">
+        <v>0.1</v>
+      </c>
+      <c r="G2360">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="H2360">
+        <v>0.18</v>
+      </c>
+      <c r="L2360">
+        <v>10.7</v>
+      </c>
+      <c r="M2360">
+        <v>103.8</v>
+      </c>
+      <c r="N2360">
+        <v>7.49</v>
+      </c>
+      <c r="O2360">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="2361" spans="1:19">
+      <c r="D2361">
+        <v>2</v>
+      </c>
+      <c r="F2361">
+        <v>0.1</v>
+      </c>
+      <c r="G2361">
+        <v>0</v>
+      </c>
+      <c r="H2361">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2362" spans="1:19">
+      <c r="D2362">
+        <v>3</v>
+      </c>
+      <c r="F2362">
+        <v>0.1</v>
+      </c>
+      <c r="G2362">
+        <v>0.15</v>
+      </c>
+      <c r="H2362">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="2363" spans="1:19">
+      <c r="B2363" s="1">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C2363" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D2363">
+        <v>1</v>
+      </c>
+      <c r="F2363">
+        <v>0.1</v>
+      </c>
+      <c r="G2363">
+        <v>1.39</v>
+      </c>
+      <c r="H2363">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="L2363">
+        <v>13.2</v>
+      </c>
+      <c r="M2363">
+        <v>85.6</v>
+      </c>
+      <c r="N2363">
+        <v>30.49</v>
+      </c>
+      <c r="O2363">
+        <v>2.15</v>
+      </c>
+    </row>
+    <row r="2364" spans="1:19">
+      <c r="C2364" s="3"/>
+      <c r="D2364">
+        <v>2</v>
+      </c>
+      <c r="F2364">
+        <v>0.1</v>
+      </c>
+      <c r="G2364">
+        <v>1.83</v>
+      </c>
+      <c r="H2364">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="2365" spans="1:19">
+      <c r="D2365">
+        <v>3</v>
+      </c>
+      <c r="F2365">
+        <v>0.1</v>
+      </c>
+      <c r="G2365">
+        <v>0.8</v>
+      </c>
+      <c r="H2365">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="2366" spans="1:19" s="19" customFormat="1">
+      <c r="E2366" s="36"/>
+    </row>
+    <row r="2367" spans="1:19">
+      <c r="A2367" t="s">
+        <v>367</v>
+      </c>
+      <c r="C2367" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2367">
+        <v>1</v>
+      </c>
+      <c r="E2367" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2367">
+        <v>0.1</v>
+      </c>
+      <c r="G2367">
+        <v>0</v>
+      </c>
+      <c r="H2367">
+        <v>0</v>
+      </c>
+      <c r="L2367">
+        <v>12</v>
+      </c>
+      <c r="M2367">
+        <v>94</v>
+      </c>
+      <c r="N2367">
+        <v>3.05</v>
+      </c>
+      <c r="O2367">
+        <v>2.04</v>
+      </c>
+      <c r="P2367" t="s">
+        <v>368</v>
+      </c>
+      <c r="Q2367" t="s">
+        <v>369</v>
+      </c>
+      <c r="R2367" t="s">
+        <v>186</v>
+      </c>
+      <c r="S2367" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="2368" spans="1:19">
+      <c r="D2368">
+        <v>2</v>
+      </c>
+      <c r="F2368">
+        <v>0.1</v>
+      </c>
+      <c r="G2368">
+        <v>0</v>
+      </c>
+      <c r="H2368">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2369" spans="3:18">
+      <c r="D2369">
+        <v>3</v>
+      </c>
+      <c r="F2369">
+        <v>0.1</v>
+      </c>
+      <c r="G2369">
+        <v>0</v>
+      </c>
+      <c r="H2369">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2370" spans="3:18">
+      <c r="C2370" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2370">
+        <v>1</v>
+      </c>
+      <c r="F2370">
+        <v>0.1</v>
+      </c>
+      <c r="G2370">
+        <v>0</v>
+      </c>
+      <c r="H2370">
+        <v>0</v>
+      </c>
+      <c r="L2370">
+        <v>13.3</v>
+      </c>
+      <c r="M2370">
+        <v>93.5</v>
+      </c>
+      <c r="N2370">
+        <v>4.09</v>
+      </c>
+      <c r="O2370">
+        <v>0.31</v>
+      </c>
+      <c r="R2370" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="2371" spans="3:18">
+      <c r="D2371">
+        <v>2</v>
+      </c>
+      <c r="F2371">
+        <v>0.1</v>
+      </c>
+      <c r="G2371">
+        <v>0</v>
+      </c>
+      <c r="H2371">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2372" spans="3:18">
+      <c r="D2372">
+        <v>3</v>
+      </c>
+      <c r="F2372">
+        <v>0.1</v>
+      </c>
+      <c r="G2372">
+        <v>0</v>
+      </c>
+      <c r="H2372">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2373" spans="3:18">
+      <c r="C2373" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2373">
+        <v>1</v>
+      </c>
+      <c r="F2373">
+        <v>0.1</v>
+      </c>
+      <c r="G2373">
+        <v>0</v>
+      </c>
+      <c r="H2373">
+        <v>0</v>
+      </c>
+      <c r="L2373">
+        <v>12.5</v>
+      </c>
+      <c r="M2373">
+        <v>99.7</v>
+      </c>
+      <c r="N2373">
+        <v>1.27</v>
+      </c>
+      <c r="O2373">
+        <v>0.25</v>
+      </c>
+      <c r="R2373" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="2374" spans="3:18">
+      <c r="D2374">
+        <v>2</v>
+      </c>
+      <c r="F2374">
+        <v>0.1</v>
+      </c>
+      <c r="G2374">
+        <v>0</v>
+      </c>
+      <c r="H2374">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2375" spans="3:18">
+      <c r="D2375">
+        <v>3</v>
+      </c>
+      <c r="F2375">
+        <v>0.1</v>
+      </c>
+      <c r="G2375">
+        <v>0</v>
+      </c>
+      <c r="H2375">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2376" spans="3:18">
+      <c r="C2376" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D2376">
+        <v>1</v>
+      </c>
+      <c r="F2376">
+        <v>0.1</v>
+      </c>
+      <c r="G2376">
+        <v>0</v>
+      </c>
+      <c r="H2376">
+        <v>0</v>
+      </c>
+      <c r="L2376">
+        <v>12.8</v>
+      </c>
+      <c r="M2376">
+        <v>92.1</v>
+      </c>
+      <c r="N2376">
+        <v>3.01</v>
+      </c>
+      <c r="O2376">
+        <v>0.46</v>
+      </c>
+      <c r="R2376" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2377" spans="3:18">
+      <c r="D2377">
+        <v>2</v>
+      </c>
+      <c r="F2377">
+        <v>0.1</v>
+      </c>
+      <c r="G2377">
+        <v>0</v>
+      </c>
+      <c r="H2377">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2378" spans="3:18">
+      <c r="D2378">
+        <v>3</v>
+      </c>
+      <c r="F2378">
+        <v>0.1</v>
+      </c>
+      <c r="G2378">
+        <v>0</v>
+      </c>
+      <c r="H2378">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2379" spans="3:18">
+      <c r="C2379" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2379">
+        <v>1</v>
+      </c>
+      <c r="F2379">
+        <v>0.1</v>
+      </c>
+      <c r="G2379">
+        <v>0</v>
+      </c>
+      <c r="H2379">
+        <v>0</v>
+      </c>
+      <c r="L2379">
+        <v>12.3</v>
+      </c>
+      <c r="M2379">
+        <v>102.2</v>
+      </c>
+      <c r="N2379">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="O2379">
+        <v>0.25</v>
+      </c>
+      <c r="R2379" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="2380" spans="3:18">
+      <c r="D2380">
+        <v>2</v>
+      </c>
+      <c r="F2380">
+        <v>0.1</v>
+      </c>
+      <c r="G2380">
+        <v>0</v>
+      </c>
+      <c r="H2380">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2381" spans="3:18">
+      <c r="D2381">
+        <v>3</v>
+      </c>
+      <c r="F2381">
+        <v>0.1</v>
+      </c>
+      <c r="G2381">
+        <v>0</v>
+      </c>
+      <c r="H2381">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2382" spans="3:18">
+      <c r="C2382" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2382">
+        <v>1</v>
+      </c>
+      <c r="F2382">
+        <v>0.1</v>
+      </c>
+      <c r="G2382">
+        <v>0</v>
+      </c>
+      <c r="H2382">
+        <v>0</v>
+      </c>
+      <c r="L2382">
+        <v>11.7</v>
+      </c>
+      <c r="M2382">
+        <v>94.5</v>
+      </c>
+      <c r="N2382">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="O2382">
+        <v>0.35</v>
+      </c>
+      <c r="R2382" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="2383" spans="3:18">
+      <c r="D2383">
+        <v>2</v>
+      </c>
+      <c r="F2383">
+        <v>0.1</v>
+      </c>
+      <c r="G2383">
+        <v>0</v>
+      </c>
+      <c r="H2383">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2384" spans="3:18">
+      <c r="D2384">
+        <v>3</v>
+      </c>
+      <c r="F2384">
+        <v>0.1</v>
+      </c>
+      <c r="G2384">
+        <v>0</v>
+      </c>
+      <c r="H2384">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2385" spans="1:18">
+      <c r="C2385" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2385">
+        <v>1</v>
+      </c>
+      <c r="F2385">
+        <v>0.1</v>
+      </c>
+      <c r="G2385">
+        <v>0</v>
+      </c>
+      <c r="H2385">
+        <v>0</v>
+      </c>
+      <c r="L2385">
+        <v>12.2</v>
+      </c>
+      <c r="M2385">
+        <v>92.5</v>
+      </c>
+      <c r="N2385">
+        <v>1.92</v>
+      </c>
+      <c r="O2385">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="R2385" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="2386" spans="1:18">
+      <c r="D2386">
+        <v>2</v>
+      </c>
+      <c r="F2386">
+        <v>0.1</v>
+      </c>
+      <c r="G2386">
+        <v>0</v>
+      </c>
+      <c r="H2386">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2387" spans="1:18">
+      <c r="D2387">
+        <v>3</v>
+      </c>
+      <c r="F2387">
+        <v>0.1</v>
+      </c>
+      <c r="G2387">
+        <v>0</v>
+      </c>
+      <c r="H2387">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2388" spans="1:18">
+      <c r="C2388" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2388">
+        <v>1</v>
+      </c>
+      <c r="F2388">
+        <v>0.1</v>
+      </c>
+      <c r="G2388">
+        <v>0</v>
+      </c>
+      <c r="H2388">
+        <v>0</v>
+      </c>
+      <c r="L2388">
+        <v>11.2</v>
+      </c>
+      <c r="M2388">
+        <v>91.5</v>
+      </c>
+      <c r="N2388">
+        <v>5.43</v>
+      </c>
+      <c r="O2388">
+        <v>0.73</v>
+      </c>
+      <c r="R2388" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2389" spans="1:18">
+      <c r="D2389">
+        <v>2</v>
+      </c>
+      <c r="F2389">
+        <v>0.1</v>
+      </c>
+      <c r="G2389">
+        <v>0</v>
+      </c>
+      <c r="H2389">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2390" spans="1:18">
+      <c r="D2390">
+        <v>3</v>
+      </c>
+      <c r="F2390">
+        <v>0.1</v>
+      </c>
+      <c r="G2390">
+        <v>0</v>
+      </c>
+      <c r="H2390">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2391" spans="1:18">
+      <c r="C2391" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D2391">
+        <v>1</v>
+      </c>
+      <c r="F2391">
+        <v>0.1</v>
+      </c>
+      <c r="G2391">
+        <v>0</v>
+      </c>
+      <c r="H2391">
+        <v>0</v>
+      </c>
+      <c r="L2391">
+        <v>12</v>
+      </c>
+      <c r="M2391">
+        <v>90.2</v>
+      </c>
+      <c r="N2391">
+        <v>6.84</v>
+      </c>
+      <c r="O2391">
+        <v>0.79</v>
+      </c>
+      <c r="R2391" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2392" spans="1:18">
+      <c r="D2392">
+        <v>2</v>
+      </c>
+      <c r="F2392">
+        <v>0.1</v>
+      </c>
+      <c r="G2392">
+        <v>0</v>
+      </c>
+      <c r="H2392">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2393" spans="1:18">
+      <c r="D2393">
+        <v>3</v>
+      </c>
+      <c r="F2393">
+        <v>0.1</v>
+      </c>
+      <c r="G2393">
+        <v>0</v>
+      </c>
+      <c r="H2393">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2394" spans="1:18">
+      <c r="C2394" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D2394">
+        <v>1</v>
+      </c>
+      <c r="F2394">
+        <v>0.1</v>
+      </c>
+      <c r="G2394">
+        <v>0</v>
+      </c>
+      <c r="H2394">
+        <v>0</v>
+      </c>
+      <c r="L2394">
+        <v>13.9</v>
+      </c>
+      <c r="M2394">
+        <v>88.8</v>
+      </c>
+      <c r="N2394">
+        <v>10.119999999999999</v>
+      </c>
+      <c r="O2394">
+        <v>0.96</v>
+      </c>
+      <c r="R2394" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2395" spans="1:18">
+      <c r="C2395" s="3"/>
+      <c r="D2395">
+        <v>2</v>
+      </c>
+      <c r="F2395">
+        <v>0.1</v>
+      </c>
+      <c r="G2395">
+        <v>0</v>
+      </c>
+      <c r="H2395">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2396" spans="1:18">
+      <c r="D2396">
+        <v>3</v>
+      </c>
+      <c r="F2396">
+        <v>0.1</v>
+      </c>
+      <c r="G2396">
+        <v>0</v>
+      </c>
+      <c r="H2396">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2397" spans="1:18" s="19" customFormat="1">
+      <c r="E2397" s="36"/>
+    </row>
+    <row r="2398" spans="1:18">
+      <c r="A2398" s="16">
+        <v>45665</v>
+      </c>
+      <c r="B2398" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="C2398" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2398">
+        <v>1</v>
+      </c>
+      <c r="E2398" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2398">
+        <v>0.1</v>
+      </c>
+      <c r="G2398">
+        <v>0</v>
+      </c>
+      <c r="H2398">
+        <v>0</v>
+      </c>
+      <c r="L2398">
+        <v>11.6</v>
+      </c>
+      <c r="M2398">
+        <v>98.2</v>
+      </c>
+      <c r="N2398">
+        <v>1.71</v>
+      </c>
+      <c r="O2398">
+        <v>0.36</v>
+      </c>
+      <c r="P2398" t="s">
+        <v>275</v>
+      </c>
+      <c r="Q2398" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="2399" spans="1:18">
+      <c r="D2399">
+        <v>2</v>
+      </c>
+      <c r="F2399">
+        <v>0.1</v>
+      </c>
+      <c r="G2399">
+        <v>0</v>
+      </c>
+      <c r="H2399">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2400" spans="1:18">
+      <c r="D2400">
+        <v>3</v>
+      </c>
+      <c r="F2400">
+        <v>0.1</v>
+      </c>
+      <c r="G2400">
+        <v>0</v>
+      </c>
+      <c r="H2400">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2401" spans="2:15">
+      <c r="B2401" s="1">
+        <v>0.52013888888888893</v>
+      </c>
+      <c r="C2401" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2401">
+        <v>1</v>
+      </c>
+      <c r="F2401">
+        <v>0.1</v>
+      </c>
+      <c r="G2401">
+        <v>0</v>
+      </c>
+      <c r="H2401">
+        <v>0</v>
+      </c>
+      <c r="L2401">
+        <v>11.8</v>
+      </c>
+      <c r="M2401">
+        <v>94</v>
+      </c>
+      <c r="N2401">
+        <v>5.0599999999999996</v>
+      </c>
+      <c r="O2401">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="2402" spans="2:15">
+      <c r="D2402">
+        <v>2</v>
+      </c>
+      <c r="F2402">
+        <v>0.1</v>
+      </c>
+      <c r="G2402">
+        <v>0</v>
+      </c>
+      <c r="H2402">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2403" spans="2:15">
+      <c r="D2403">
+        <v>3</v>
+      </c>
+      <c r="F2403">
+        <v>0.1</v>
+      </c>
+      <c r="G2403">
+        <v>0</v>
+      </c>
+      <c r="H2403">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2404" spans="2:15">
+      <c r="B2404" s="1">
+        <v>0.53055555555555556</v>
+      </c>
+      <c r="C2404" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2404">
+        <v>1</v>
+      </c>
+      <c r="F2404">
+        <v>24.86</v>
+      </c>
+      <c r="G2404">
+        <v>0.45</v>
+      </c>
+      <c r="H2404">
+        <v>55.24</v>
+      </c>
+      <c r="L2404">
+        <v>11.1</v>
+      </c>
+      <c r="M2404">
+        <v>97.9</v>
+      </c>
+      <c r="N2404">
+        <v>4.6900000000000004</v>
+      </c>
+      <c r="O2404">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="2405" spans="2:15">
+      <c r="D2405">
+        <v>2</v>
+      </c>
+      <c r="F2405">
+        <v>16.260000000000002</v>
+      </c>
+      <c r="G2405">
+        <v>0</v>
+      </c>
+      <c r="H2405">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2406" spans="2:15">
+      <c r="D2406">
+        <v>3</v>
+      </c>
+      <c r="F2406">
+        <v>0.1</v>
+      </c>
+      <c r="G2406">
+        <v>0.45</v>
+      </c>
+      <c r="H2406">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="2407" spans="2:15">
+      <c r="B2407" s="1">
+        <v>0.54583333333333328</v>
+      </c>
+      <c r="C2407" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D2407">
+        <v>1</v>
+      </c>
+      <c r="F2407">
+        <v>28.78</v>
+      </c>
+      <c r="G2407">
+        <v>1.29</v>
+      </c>
+      <c r="H2407">
+        <v>22.31</v>
+      </c>
+      <c r="L2407">
+        <v>10.7</v>
+      </c>
+      <c r="M2407">
+        <v>95.8</v>
+      </c>
+      <c r="N2407">
+        <v>14.83</v>
+      </c>
+      <c r="O2407">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="2408" spans="2:15">
+      <c r="D2408">
+        <v>2</v>
+      </c>
+      <c r="F2408">
+        <v>0.1</v>
+      </c>
+      <c r="G2408">
+        <v>1.39</v>
+      </c>
+      <c r="H2408">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="2409" spans="2:15">
+      <c r="D2409">
+        <v>3</v>
+      </c>
+      <c r="F2409">
+        <v>0.1</v>
+      </c>
+      <c r="G2409">
+        <v>0.5</v>
+      </c>
+      <c r="H2409">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="2410" spans="2:15">
+      <c r="B2410" s="1">
+        <v>0.55833333333333335</v>
+      </c>
+      <c r="C2410" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2410">
+        <v>1</v>
+      </c>
+      <c r="F2410">
+        <v>0.1</v>
+      </c>
+      <c r="G2410">
+        <v>1.63</v>
+      </c>
+      <c r="H2410">
+        <v>0.06</v>
+      </c>
+      <c r="L2410">
+        <v>10.9</v>
+      </c>
+      <c r="M2410">
+        <v>97.3</v>
+      </c>
+      <c r="N2410">
+        <v>8.4</v>
+      </c>
+      <c r="O2410">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="2411" spans="2:15">
+      <c r="D2411">
+        <v>2</v>
+      </c>
+      <c r="F2411">
+        <v>0.1</v>
+      </c>
+      <c r="G2411">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="H2411">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="2412" spans="2:15">
+      <c r="D2412">
+        <v>3</v>
+      </c>
+      <c r="F2412">
+        <v>0.1</v>
+      </c>
+      <c r="G2412">
+        <v>2.86</v>
+      </c>
+      <c r="H2412">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="2413" spans="2:15">
+      <c r="B2413" s="1">
+        <v>0.56388888888888888</v>
+      </c>
+      <c r="C2413" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2413">
+        <v>1</v>
+      </c>
+      <c r="F2413">
+        <v>0.1</v>
+      </c>
+      <c r="G2413">
+        <v>4.1900000000000004</v>
+      </c>
+      <c r="H2413">
+        <v>0.02</v>
+      </c>
+      <c r="L2413">
+        <v>10.7</v>
+      </c>
+      <c r="M2413">
+        <v>96.7</v>
+      </c>
+      <c r="N2413">
+        <v>46.47</v>
+      </c>
+      <c r="O2413">
+        <v>2.46</v>
+      </c>
+    </row>
+    <row r="2414" spans="2:15">
+      <c r="D2414">
+        <v>2</v>
+      </c>
+      <c r="F2414">
+        <v>0.1</v>
+      </c>
+      <c r="G2414">
+        <v>3.85</v>
+      </c>
+      <c r="H2414">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="2415" spans="2:15">
+      <c r="D2415">
+        <v>3</v>
+      </c>
+      <c r="F2415">
+        <v>0.1</v>
+      </c>
+      <c r="G2415">
+        <v>2.6</v>
+      </c>
+      <c r="H2415">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="2416" spans="2:15">
+      <c r="B2416" s="1">
+        <v>0.57638888888888884</v>
+      </c>
+      <c r="C2416" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2416">
+        <v>1</v>
+      </c>
+      <c r="F2416">
+        <v>0.1</v>
+      </c>
+      <c r="G2416">
+        <v>3.85</v>
+      </c>
+      <c r="H2416">
+        <v>0.02</v>
+      </c>
+      <c r="L2416">
+        <v>11</v>
+      </c>
+      <c r="M2416">
+        <v>100</v>
+      </c>
+      <c r="N2416">
+        <v>38.33</v>
+      </c>
+      <c r="O2416">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="2417" spans="1:18">
+      <c r="D2417">
+        <v>2</v>
+      </c>
+      <c r="F2417">
+        <v>3.25</v>
+      </c>
+      <c r="G2417">
+        <v>4.59</v>
+      </c>
+      <c r="H2417">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="2418" spans="1:18">
+      <c r="D2418">
+        <v>3</v>
+      </c>
+      <c r="F2418">
+        <v>8.5</v>
+      </c>
+      <c r="G2418">
+        <v>4.83</v>
+      </c>
+      <c r="H2418">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="2419" spans="1:18">
+      <c r="B2419" s="1">
+        <v>0.58888888888888891</v>
+      </c>
+      <c r="C2419" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2419">
+        <v>1</v>
+      </c>
+      <c r="F2419">
+        <v>8.5</v>
+      </c>
+      <c r="G2419">
+        <v>3.06</v>
+      </c>
+      <c r="H2419">
+        <v>2.77</v>
+      </c>
+      <c r="L2419">
+        <v>11.5</v>
+      </c>
+      <c r="M2419">
+        <v>96.2</v>
+      </c>
+      <c r="N2419">
+        <v>19.7</v>
+      </c>
+      <c r="O2419">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="2420" spans="1:18">
+      <c r="D2420">
+        <v>2</v>
+      </c>
+      <c r="F2420">
+        <v>17.82</v>
+      </c>
+      <c r="G2420">
+        <v>2.72</v>
+      </c>
+      <c r="H2420">
+        <v>5.55</v>
+      </c>
+    </row>
+    <row r="2421" spans="1:18">
+      <c r="D2421">
+        <v>3</v>
+      </c>
+      <c r="F2421">
+        <v>323.44</v>
+      </c>
+      <c r="G2421">
+        <v>3.45</v>
+      </c>
+      <c r="H2421">
+        <v>93.75</v>
+      </c>
+    </row>
+    <row r="2422" spans="1:18">
+      <c r="B2422" s="1">
+        <v>0.59861111111111109</v>
+      </c>
+      <c r="C2422" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D2422">
+        <v>1</v>
+      </c>
+      <c r="F2422">
+        <v>0.1</v>
+      </c>
+      <c r="G2422">
+        <v>3.36</v>
+      </c>
+      <c r="H2422">
+        <v>0.02</v>
+      </c>
+      <c r="L2422">
+        <v>12</v>
+      </c>
+      <c r="M2422">
+        <v>100.2</v>
+      </c>
+      <c r="N2422">
+        <v>15.93</v>
+      </c>
+      <c r="O2422">
+        <v>2.11</v>
+      </c>
+    </row>
+    <row r="2423" spans="1:18">
+      <c r="D2423">
+        <v>2</v>
+      </c>
+      <c r="F2423">
+        <v>0.1</v>
+      </c>
+      <c r="G2423">
+        <v>3.21</v>
+      </c>
+      <c r="H2423">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="2424" spans="1:18">
+      <c r="D2424">
+        <v>3</v>
+      </c>
+      <c r="F2424">
+        <v>0.1</v>
+      </c>
+      <c r="G2424">
+        <v>3.8</v>
+      </c>
+      <c r="H2424">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="2425" spans="1:18">
+      <c r="B2425" s="1">
+        <v>0.61250000000000004</v>
+      </c>
+      <c r="C2425" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D2425">
+        <v>1</v>
+      </c>
+      <c r="F2425">
+        <v>0.1</v>
+      </c>
+      <c r="G2425">
+        <v>1.98</v>
+      </c>
+      <c r="H2425">
+        <v>0.05</v>
+      </c>
+      <c r="L2425">
+        <v>13</v>
+      </c>
+      <c r="M2425">
+        <v>92.9</v>
+      </c>
+      <c r="N2425">
+        <v>7.11</v>
+      </c>
+      <c r="O2425">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="2426" spans="1:18">
+      <c r="C2426" s="3"/>
+      <c r="D2426">
+        <v>2</v>
+      </c>
+      <c r="F2426">
+        <v>0.1</v>
+      </c>
+      <c r="G2426">
+        <v>1.63</v>
+      </c>
+      <c r="H2426">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="2427" spans="1:18">
+      <c r="D2427">
+        <v>3</v>
+      </c>
+      <c r="F2427">
+        <v>0.1</v>
+      </c>
+      <c r="G2427">
+        <v>1.54</v>
+      </c>
+      <c r="H2427">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="2428" spans="1:18" s="19" customFormat="1">
+      <c r="E2428" s="36"/>
+    </row>
+    <row r="2429" spans="1:18">
+      <c r="A2429" s="16">
+        <v>45755</v>
+      </c>
+      <c r="B2429" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="C2429" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2429">
+        <v>1</v>
+      </c>
+      <c r="E2429" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2429">
+        <v>0.1</v>
+      </c>
+      <c r="G2429">
+        <v>0</v>
+      </c>
+      <c r="H2429">
+        <v>0</v>
+      </c>
+      <c r="L2429">
+        <v>10.3</v>
+      </c>
+      <c r="M2429">
+        <v>92.3</v>
+      </c>
+      <c r="N2429">
+        <v>2.6</v>
+      </c>
+      <c r="O2429">
+        <v>0.27</v>
+      </c>
+      <c r="P2429" t="s">
+        <v>187</v>
+      </c>
+      <c r="Q2429" t="s">
+        <v>372</v>
+      </c>
+      <c r="R2429" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="2430" spans="1:18">
+      <c r="D2430">
+        <v>2</v>
+      </c>
+      <c r="F2430">
+        <v>0.1</v>
+      </c>
+      <c r="G2430">
+        <v>0</v>
+      </c>
+      <c r="H2430">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2431" spans="1:18">
+      <c r="D2431">
+        <v>3</v>
+      </c>
+      <c r="F2431">
+        <v>0.1</v>
+      </c>
+      <c r="G2431">
+        <v>0</v>
+      </c>
+      <c r="H2431">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2432" spans="1:18">
+      <c r="B2432" s="1">
+        <v>0.51875000000000004</v>
+      </c>
+      <c r="C2432" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2432">
+        <v>1</v>
+      </c>
+      <c r="F2432">
+        <v>22.52</v>
+      </c>
+      <c r="G2432">
+        <v>22.22</v>
+      </c>
+      <c r="H2432">
+        <v>10.14</v>
+      </c>
+      <c r="L2432">
+        <v>10.5</v>
+      </c>
+      <c r="M2432">
+        <v>88.8</v>
+      </c>
+      <c r="N2432">
+        <v>1.57</v>
+      </c>
+      <c r="O2432">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="R2432" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="2433" spans="2:18">
+      <c r="D2433">
+        <v>2</v>
+      </c>
+      <c r="F2433">
+        <v>0.1</v>
+      </c>
+      <c r="G2433">
+        <v>0.05</v>
+      </c>
+      <c r="H2433">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2434" spans="2:18">
+      <c r="D2434">
+        <v>3</v>
+      </c>
+      <c r="F2434">
+        <v>0.1</v>
+      </c>
+      <c r="G2434">
+        <v>0</v>
+      </c>
+      <c r="H2434">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2435" spans="2:18">
+      <c r="B2435" s="1">
+        <v>0.5395833333333333</v>
+      </c>
+      <c r="C2435" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2435">
+        <v>1</v>
+      </c>
+      <c r="F2435">
+        <v>0.1</v>
+      </c>
+      <c r="G2435">
+        <v>0.5</v>
+      </c>
+      <c r="H2435">
+        <v>0.2</v>
+      </c>
+      <c r="L2435">
+        <v>10.3</v>
+      </c>
+      <c r="M2435">
+        <v>97</v>
+      </c>
+      <c r="N2435">
+        <v>1.34</v>
+      </c>
+      <c r="O2435">
+        <v>0.11</v>
+      </c>
+      <c r="R2435" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="2436" spans="2:18">
+      <c r="D2436">
+        <v>2</v>
+      </c>
+      <c r="F2436">
+        <v>0.1</v>
+      </c>
+      <c r="G2436">
+        <v>0.75</v>
+      </c>
+      <c r="H2436">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="2437" spans="2:18">
+      <c r="D2437">
+        <v>3</v>
+      </c>
+      <c r="F2437">
+        <v>0.1</v>
+      </c>
+      <c r="G2437">
+        <v>0</v>
+      </c>
+      <c r="H2437">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2438" spans="2:18">
+      <c r="B2438" s="1">
+        <v>0.55208333333333337</v>
+      </c>
+      <c r="C2438" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D2438">
+        <v>1</v>
+      </c>
+      <c r="F2438">
+        <v>0.1</v>
+      </c>
+      <c r="G2438">
+        <v>1.59</v>
+      </c>
+      <c r="H2438">
+        <v>0.06</v>
+      </c>
+      <c r="L2438">
+        <v>11.3</v>
+      </c>
+      <c r="M2438">
+        <v>95.9</v>
+      </c>
+      <c r="N2438">
+        <v>23</v>
+      </c>
+      <c r="O2438">
+        <v>0.71</v>
+      </c>
+      <c r="R2438" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="2439" spans="2:18">
+      <c r="D2439">
+        <v>2</v>
+      </c>
+      <c r="F2439">
+        <v>0.1</v>
+      </c>
+      <c r="G2439">
+        <v>0.4</v>
+      </c>
+      <c r="H2439">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="2440" spans="2:18">
+      <c r="D2440">
+        <v>3</v>
+      </c>
+      <c r="F2440">
+        <v>0.1</v>
+      </c>
+      <c r="G2440">
+        <v>0</v>
+      </c>
+      <c r="H2440">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2441" spans="2:18">
+      <c r="B2441" s="1">
+        <v>0.57152777777777775</v>
+      </c>
+      <c r="C2441" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2441">
+        <v>1</v>
+      </c>
+      <c r="F2441">
+        <v>0.1</v>
+      </c>
+      <c r="G2441">
+        <v>0</v>
+      </c>
+      <c r="H2441">
+        <v>0</v>
+      </c>
+      <c r="L2441">
+        <v>10.3</v>
+      </c>
+      <c r="M2441">
+        <v>101.9</v>
+      </c>
+      <c r="N2441">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="O2441">
+        <v>0.25</v>
+      </c>
+      <c r="R2441" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="2442" spans="2:18">
+      <c r="D2442">
+        <v>2</v>
+      </c>
+      <c r="F2442">
+        <v>0.1</v>
+      </c>
+      <c r="G2442">
+        <v>0</v>
+      </c>
+      <c r="H2442">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2443" spans="2:18">
+      <c r="D2443">
+        <v>3</v>
+      </c>
+      <c r="F2443">
+        <v>0.1</v>
+      </c>
+      <c r="G2443">
+        <v>0</v>
+      </c>
+      <c r="H2443">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2444" spans="2:18">
+      <c r="B2444" s="1">
+        <v>0.58611111111111114</v>
+      </c>
+      <c r="C2444" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2444">
+        <v>1</v>
+      </c>
+      <c r="F2444">
+        <v>0.1</v>
+      </c>
+      <c r="G2444">
+        <v>0</v>
+      </c>
+      <c r="H2444">
+        <v>0</v>
+      </c>
+      <c r="L2444">
+        <v>9.6</v>
+      </c>
+      <c r="M2444">
+        <v>102.1</v>
+      </c>
+      <c r="N2444">
+        <v>11.91</v>
+      </c>
+      <c r="O2444">
+        <v>0.71</v>
+      </c>
+      <c r="R2444" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="2445" spans="2:18">
+      <c r="D2445">
+        <v>2</v>
+      </c>
+      <c r="F2445">
+        <v>0.1</v>
+      </c>
+      <c r="G2445">
+        <v>0.3</v>
+      </c>
+      <c r="H2445">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="2446" spans="2:18">
+      <c r="D2446">
+        <v>3</v>
+      </c>
+      <c r="F2446">
+        <v>0.1</v>
+      </c>
+      <c r="G2446">
+        <v>0</v>
+      </c>
+      <c r="H2446">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2447" spans="2:18">
+      <c r="B2447" s="1">
+        <v>0.59722222222222221</v>
+      </c>
+      <c r="C2447" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2447">
+        <v>1</v>
+      </c>
+      <c r="F2447">
+        <v>0.1</v>
+      </c>
+      <c r="G2447">
+        <v>0</v>
+      </c>
+      <c r="H2447">
+        <v>0</v>
+      </c>
+      <c r="L2447">
+        <v>10.1</v>
+      </c>
+      <c r="M2447">
+        <v>99.9</v>
+      </c>
+      <c r="N2447">
+        <v>4.45</v>
+      </c>
+      <c r="O2447">
+        <v>0.21</v>
+      </c>
+      <c r="R2447" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="2448" spans="2:18">
+      <c r="D2448">
+        <v>2</v>
+      </c>
+      <c r="F2448">
+        <v>0.1</v>
+      </c>
+      <c r="G2448">
+        <v>0</v>
+      </c>
+      <c r="H2448">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2449" spans="1:19">
+      <c r="D2449">
+        <v>3</v>
+      </c>
+      <c r="F2449">
+        <v>0.1</v>
+      </c>
+      <c r="G2449">
+        <v>0</v>
+      </c>
+      <c r="H2449">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2450" spans="1:19">
+      <c r="B2450" s="1">
+        <v>0.60763888888888884</v>
+      </c>
+      <c r="C2450" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2450">
+        <v>1</v>
+      </c>
+      <c r="F2450">
+        <v>0.1</v>
+      </c>
+      <c r="G2450">
+        <v>0</v>
+      </c>
+      <c r="H2450">
+        <v>0</v>
+      </c>
+      <c r="L2450">
+        <v>10.6</v>
+      </c>
+      <c r="M2450">
+        <v>97.5</v>
+      </c>
+      <c r="N2450">
+        <v>13.45</v>
+      </c>
+      <c r="O2450">
+        <v>0.41</v>
+      </c>
+      <c r="R2450" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="2451" spans="1:19">
+      <c r="D2451">
+        <v>2</v>
+      </c>
+      <c r="F2451">
+        <v>0.1</v>
+      </c>
+      <c r="G2451">
+        <v>0</v>
+      </c>
+      <c r="H2451">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2452" spans="1:19">
+      <c r="D2452">
+        <v>3</v>
+      </c>
+      <c r="F2452">
+        <v>0.1</v>
+      </c>
+      <c r="G2452">
+        <v>0</v>
+      </c>
+      <c r="H2452">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2453" spans="1:19">
+      <c r="B2453" s="1">
+        <v>0.6166666666666667</v>
+      </c>
+      <c r="C2453" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D2453">
+        <v>1</v>
+      </c>
+      <c r="F2453">
+        <v>0.1</v>
+      </c>
+      <c r="G2453">
+        <v>0</v>
+      </c>
+      <c r="H2453">
+        <v>0</v>
+      </c>
+      <c r="L2453">
+        <v>11.1</v>
+      </c>
+      <c r="M2453">
+        <v>101.4</v>
+      </c>
+      <c r="N2453">
+        <v>3.43</v>
+      </c>
+      <c r="O2453">
+        <v>0.32</v>
+      </c>
+      <c r="R2453" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="2454" spans="1:19">
+      <c r="D2454">
+        <v>2</v>
+      </c>
+      <c r="F2454">
+        <v>0.1</v>
+      </c>
+      <c r="G2454">
+        <v>0</v>
+      </c>
+      <c r="H2454">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2455" spans="1:19">
+      <c r="D2455">
+        <v>3</v>
+      </c>
+      <c r="F2455">
+        <v>0.1</v>
+      </c>
+      <c r="G2455">
+        <v>0</v>
+      </c>
+      <c r="H2455">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2456" spans="1:19">
+      <c r="B2456" s="1">
+        <v>0.625</v>
+      </c>
+      <c r="C2456" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D2456">
+        <v>1</v>
+      </c>
+      <c r="F2456">
+        <v>0.1</v>
+      </c>
+      <c r="G2456">
+        <v>0</v>
+      </c>
+      <c r="H2456">
+        <v>0</v>
+      </c>
+      <c r="L2456">
+        <v>11.3</v>
+      </c>
+      <c r="M2456">
+        <v>94.7</v>
+      </c>
+      <c r="N2456">
+        <v>1.47</v>
+      </c>
+      <c r="O2456">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="R2456" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="2457" spans="1:19">
+      <c r="C2457" s="3"/>
+      <c r="D2457">
+        <v>2</v>
+      </c>
+      <c r="F2457">
+        <v>0.1</v>
+      </c>
+      <c r="G2457">
+        <v>0</v>
+      </c>
+      <c r="H2457">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2458" spans="1:19">
+      <c r="D2458">
+        <v>3</v>
+      </c>
+      <c r="F2458">
+        <v>0.1</v>
+      </c>
+      <c r="G2458">
+        <v>0</v>
+      </c>
+      <c r="H2458">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2459" spans="1:19" s="19" customFormat="1">
+      <c r="E2459" s="36"/>
+    </row>
+    <row r="2460" spans="1:19">
+      <c r="A2460" s="16">
+        <v>45816</v>
+      </c>
+      <c r="B2460" s="1">
+        <v>0.50208333333333333</v>
+      </c>
+      <c r="C2460" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2460">
+        <v>1</v>
+      </c>
+      <c r="E2460" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2460">
+        <v>0.1</v>
+      </c>
+      <c r="G2460">
+        <v>0</v>
+      </c>
+      <c r="H2460">
+        <v>0</v>
+      </c>
+      <c r="L2460">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="M2460">
+        <v>97.2</v>
+      </c>
+      <c r="N2460">
+        <v>1.93</v>
+      </c>
+      <c r="O2460">
+        <v>0.2</v>
+      </c>
+      <c r="P2460" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q2460" t="s">
+        <v>194</v>
+      </c>
+      <c r="R2460" t="s">
+        <v>221</v>
+      </c>
+      <c r="S2460" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="2461" spans="1:19">
+      <c r="D2461">
+        <v>2</v>
+      </c>
+      <c r="F2461">
+        <v>0.1</v>
+      </c>
+      <c r="G2461">
+        <v>0</v>
+      </c>
+      <c r="H2461">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2462" spans="1:19">
+      <c r="D2462">
+        <v>3</v>
+      </c>
+      <c r="F2462">
+        <v>0.1</v>
+      </c>
+      <c r="G2462">
+        <v>0</v>
+      </c>
+      <c r="H2462">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2463" spans="1:19">
+      <c r="B2463" s="1">
+        <v>0.52152777777777781</v>
+      </c>
+      <c r="C2463" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2463">
+        <v>1</v>
+      </c>
+      <c r="F2463">
+        <v>0.25</v>
+      </c>
+      <c r="G2463">
+        <v>0.9</v>
+      </c>
+      <c r="H2463">
+        <v>6.94</v>
+      </c>
+      <c r="L2463">
+        <v>10.9</v>
+      </c>
+      <c r="M2463">
+        <v>87.7</v>
+      </c>
+      <c r="N2463">
+        <v>2.36</v>
+      </c>
+      <c r="O2463">
+        <v>0.12</v>
+      </c>
+      <c r="R2463" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="2464" spans="1:19">
+      <c r="D2464">
+        <v>2</v>
+      </c>
+      <c r="F2464">
+        <v>0.1</v>
+      </c>
+      <c r="G2464">
+        <v>0.5</v>
+      </c>
+      <c r="H2464">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="2465" spans="2:18">
+      <c r="D2465">
+        <v>3</v>
+      </c>
+      <c r="F2465">
+        <v>0.1</v>
+      </c>
+      <c r="G2465">
+        <v>0.1</v>
+      </c>
+      <c r="H2465">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2466" spans="2:18">
+      <c r="B2466" s="1">
+        <v>0.54027777777777775</v>
+      </c>
+      <c r="C2466" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2466">
+        <v>1</v>
+      </c>
+      <c r="F2466">
+        <v>22.52</v>
+      </c>
+      <c r="G2466">
+        <v>0.65</v>
+      </c>
+      <c r="H2466">
+        <v>34.64</v>
+      </c>
+      <c r="L2466">
+        <v>10.6</v>
+      </c>
+      <c r="M2466">
+        <v>97.6</v>
+      </c>
+      <c r="N2466">
+        <v>0.92</v>
+      </c>
+      <c r="O2466">
+        <v>0.08</v>
+      </c>
+      <c r="R2466" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="2467" spans="2:18">
+      <c r="D2467">
+        <v>2</v>
+      </c>
+      <c r="F2467">
+        <v>0.1</v>
+      </c>
+      <c r="G2467">
+        <v>0.15</v>
+      </c>
+      <c r="H2467">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="2468" spans="2:18">
+      <c r="D2468">
+        <v>3</v>
+      </c>
+      <c r="F2468">
+        <v>0.1</v>
+      </c>
+      <c r="G2468">
+        <v>0</v>
+      </c>
+      <c r="H2468">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2469" spans="2:18">
+      <c r="B2469" s="1">
+        <v>0.55277777777777781</v>
+      </c>
+      <c r="C2469" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D2469">
+        <v>1</v>
+      </c>
+      <c r="F2469">
+        <v>0.1</v>
+      </c>
+      <c r="G2469">
+        <v>0.3</v>
+      </c>
+      <c r="H2469">
+        <v>0.33</v>
+      </c>
+      <c r="L2469">
+        <v>11</v>
+      </c>
+      <c r="M2469">
+        <v>98.2</v>
+      </c>
+      <c r="N2469">
+        <v>5.42</v>
+      </c>
+      <c r="O2469">
+        <v>0.44</v>
+      </c>
+      <c r="R2469" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="2470" spans="2:18">
+      <c r="D2470">
+        <v>2</v>
+      </c>
+      <c r="F2470">
+        <v>0.1</v>
+      </c>
+      <c r="G2470">
+        <v>0</v>
+      </c>
+      <c r="H2470">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2471" spans="2:18">
+      <c r="D2471">
+        <v>3</v>
+      </c>
+      <c r="F2471">
+        <v>3.25</v>
+      </c>
+      <c r="G2471">
+        <v>0</v>
+      </c>
+      <c r="H2471">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2472" spans="2:18">
+      <c r="B2472" s="1">
+        <v>0.56180555555555556</v>
+      </c>
+      <c r="C2472" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2472">
+        <v>1</v>
+      </c>
+      <c r="F2472">
+        <v>0.1</v>
+      </c>
+      <c r="G2472">
+        <v>0</v>
+      </c>
+      <c r="H2472">
+        <v>0</v>
+      </c>
+      <c r="L2472">
+        <v>10.8</v>
+      </c>
+      <c r="M2472">
+        <v>97.7</v>
+      </c>
+      <c r="N2472">
+        <v>1.95</v>
+      </c>
+      <c r="O2472">
+        <v>0.15</v>
+      </c>
+      <c r="R2472" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="2473" spans="2:18">
+      <c r="D2473">
+        <v>2</v>
+      </c>
+      <c r="F2473">
+        <v>0.1</v>
+      </c>
+      <c r="G2473">
+        <v>0</v>
+      </c>
+      <c r="H2473">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2474" spans="2:18">
+      <c r="D2474">
+        <v>3</v>
+      </c>
+      <c r="F2474">
+        <v>0.1</v>
+      </c>
+      <c r="G2474">
+        <v>0</v>
+      </c>
+      <c r="H2474">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2475" spans="2:18">
+      <c r="B2475" s="1">
+        <v>0.56805555555555554</v>
+      </c>
+      <c r="C2475" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2475">
+        <v>1</v>
+      </c>
+      <c r="F2475">
+        <v>0.1</v>
+      </c>
+      <c r="G2475">
+        <v>0</v>
+      </c>
+      <c r="H2475">
+        <v>0</v>
+      </c>
+      <c r="L2475">
+        <v>10.5</v>
+      </c>
+      <c r="M2475">
+        <v>105.4</v>
+      </c>
+      <c r="N2475">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="O2475">
+        <v>0.11</v>
+      </c>
+      <c r="R2475" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="2476" spans="2:18">
+      <c r="D2476">
+        <v>2</v>
+      </c>
+      <c r="F2476">
+        <v>0.1</v>
+      </c>
+      <c r="G2476">
+        <v>0</v>
+      </c>
+      <c r="H2476">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2477" spans="2:18">
+      <c r="D2477">
+        <v>3</v>
+      </c>
+      <c r="F2477">
+        <v>0.1</v>
+      </c>
+      <c r="G2477">
+        <v>0</v>
+      </c>
+      <c r="H2477">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2478" spans="2:18">
+      <c r="B2478" s="1">
+        <v>0.58402777777777781</v>
+      </c>
+      <c r="C2478" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2478">
+        <v>1</v>
+      </c>
+      <c r="F2478">
+        <v>0.1</v>
+      </c>
+      <c r="G2478">
+        <v>0</v>
+      </c>
+      <c r="H2478">
+        <v>0</v>
+      </c>
+      <c r="M2478" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="R2478" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="2479" spans="2:18">
+      <c r="D2479">
+        <v>2</v>
+      </c>
+      <c r="F2479">
+        <v>0.1</v>
+      </c>
+      <c r="G2479">
+        <v>0</v>
+      </c>
+      <c r="H2479">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2480" spans="2:18">
+      <c r="D2480">
+        <v>3</v>
+      </c>
+      <c r="F2480">
+        <v>0.1</v>
+      </c>
+      <c r="G2480">
+        <v>0</v>
+      </c>
+      <c r="H2480">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2481" spans="1:19">
+      <c r="B2481" s="1">
+        <v>0.59652777777777777</v>
+      </c>
+      <c r="C2481" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2481">
+        <v>1</v>
+      </c>
+      <c r="F2481">
+        <v>0.1</v>
+      </c>
+      <c r="G2481">
+        <v>0</v>
+      </c>
+      <c r="H2481">
+        <v>0</v>
+      </c>
+      <c r="R2481" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="2482" spans="1:19">
+      <c r="D2482">
+        <v>2</v>
+      </c>
+      <c r="F2482">
+        <v>0.1</v>
+      </c>
+      <c r="G2482">
+        <v>0.3</v>
+      </c>
+      <c r="H2482">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="2483" spans="1:19">
+      <c r="D2483">
+        <v>3</v>
+      </c>
+      <c r="F2483">
+        <v>0.1</v>
+      </c>
+      <c r="G2483">
+        <v>0.1</v>
+      </c>
+      <c r="H2483">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2484" spans="1:19">
+      <c r="B2484" s="1">
+        <v>0.60486111111111107</v>
+      </c>
+      <c r="C2484" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D2484">
+        <v>1</v>
+      </c>
+      <c r="F2484">
+        <v>0.1</v>
+      </c>
+      <c r="G2484">
+        <v>0</v>
+      </c>
+      <c r="H2484">
+        <v>0</v>
+      </c>
+      <c r="R2484" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="2485" spans="1:19">
+      <c r="D2485">
+        <v>2</v>
+      </c>
+      <c r="F2485">
+        <v>0.1</v>
+      </c>
+      <c r="G2485">
+        <v>0</v>
+      </c>
+      <c r="H2485">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2486" spans="1:19">
+      <c r="D2486">
+        <v>3</v>
+      </c>
+      <c r="F2486">
+        <v>0.1</v>
+      </c>
+      <c r="G2486">
+        <v>0</v>
+      </c>
+      <c r="H2486">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2487" spans="1:19">
+      <c r="B2487" s="1">
+        <v>0.62152777777777779</v>
+      </c>
+      <c r="C2487" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D2487">
+        <v>1</v>
+      </c>
+      <c r="F2487">
+        <v>0.1</v>
+      </c>
+      <c r="G2487">
+        <v>0</v>
+      </c>
+      <c r="H2487">
+        <v>0</v>
+      </c>
+      <c r="R2487" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="2488" spans="1:19">
+      <c r="C2488" s="3"/>
+      <c r="D2488">
+        <v>2</v>
+      </c>
+      <c r="F2488">
+        <v>0.1</v>
+      </c>
+      <c r="G2488">
+        <v>0</v>
+      </c>
+      <c r="H2488">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2489" spans="1:19">
+      <c r="D2489">
+        <v>3</v>
+      </c>
+      <c r="F2489">
+        <v>0.1</v>
+      </c>
+      <c r="G2489">
+        <v>0</v>
+      </c>
+      <c r="H2489">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2490" spans="1:19" s="19" customFormat="1">
+      <c r="E2490" s="36"/>
+    </row>
+    <row r="2491" spans="1:19">
+      <c r="A2491" s="16">
+        <v>45908</v>
+      </c>
+      <c r="B2491" s="1">
+        <v>0.62569444444444444</v>
+      </c>
+      <c r="C2491" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2491">
+        <v>1</v>
+      </c>
+      <c r="E2491" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2491">
+        <v>0.1</v>
+      </c>
+      <c r="G2491">
+        <v>0.95</v>
+      </c>
+      <c r="H2491">
+        <v>0.1</v>
+      </c>
+      <c r="L2491">
+        <v>11.4</v>
+      </c>
+      <c r="M2491">
+        <v>88.5</v>
+      </c>
+      <c r="N2491">
+        <v>4.47</v>
+      </c>
+      <c r="O2491">
+        <v>0.15</v>
+      </c>
+      <c r="P2491" t="s">
+        <v>191</v>
+      </c>
+      <c r="Q2491" t="s">
+        <v>360</v>
+      </c>
+      <c r="R2491" t="s">
+        <v>266</v>
+      </c>
+      <c r="S2491" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="2492" spans="1:19">
+      <c r="D2492">
+        <v>2</v>
+      </c>
+      <c r="F2492">
+        <v>0.1</v>
+      </c>
+      <c r="G2492">
+        <v>0</v>
+      </c>
+      <c r="H2492">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2493" spans="1:19">
+      <c r="D2493">
+        <v>3</v>
+      </c>
+      <c r="F2493">
+        <v>0.1</v>
+      </c>
+      <c r="G2493">
+        <v>0</v>
+      </c>
+      <c r="H2493">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2494" spans="1:19">
+      <c r="B2494" s="1">
+        <v>0.64652777777777781</v>
+      </c>
+      <c r="C2494" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2494">
+        <v>1</v>
+      </c>
+      <c r="F2494">
+        <v>0.1</v>
+      </c>
+      <c r="G2494">
+        <v>0</v>
+      </c>
+      <c r="H2494">
+        <v>0</v>
+      </c>
+      <c r="L2494">
+        <v>10.4</v>
+      </c>
+      <c r="M2494">
+        <v>101.5</v>
+      </c>
+      <c r="N2494">
+        <v>7.22</v>
+      </c>
+      <c r="O2494">
+        <v>0.26</v>
+      </c>
+      <c r="R2494" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="2495" spans="1:19">
+      <c r="D2495">
+        <v>2</v>
+      </c>
+      <c r="F2495">
+        <v>0.1</v>
+      </c>
+      <c r="G2495">
+        <v>0</v>
+      </c>
+      <c r="H2495">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2496" spans="1:19">
+      <c r="D2496">
+        <v>3</v>
+      </c>
+      <c r="F2496">
+        <v>0.1</v>
+      </c>
+      <c r="G2496">
+        <v>0.25</v>
+      </c>
+      <c r="H2496">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="2497" spans="2:18">
+      <c r="B2497" s="1">
+        <v>0.66041666666666665</v>
+      </c>
+      <c r="C2497" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2497">
+        <v>1</v>
+      </c>
+      <c r="F2497">
+        <v>0.1</v>
+      </c>
+      <c r="G2497">
+        <v>0.35</v>
+      </c>
+      <c r="H2497">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="L2497">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="M2497">
+        <v>100.1</v>
+      </c>
+      <c r="N2497">
+        <v>5.34</v>
+      </c>
+      <c r="O2497">
+        <v>0.31</v>
+      </c>
+      <c r="R2497" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="2498" spans="2:18">
+      <c r="D2498">
+        <v>2</v>
+      </c>
+      <c r="F2498">
+        <v>0.1</v>
+      </c>
+      <c r="G2498">
+        <v>0</v>
+      </c>
+      <c r="H2498">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2499" spans="2:18">
+      <c r="D2499">
+        <v>3</v>
+      </c>
+      <c r="F2499">
+        <v>0.1</v>
+      </c>
+      <c r="G2499">
+        <v>0</v>
+      </c>
+      <c r="H2499">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2500" spans="2:18">
+      <c r="B2500" s="1">
+        <v>0.67777777777777781</v>
+      </c>
+      <c r="C2500" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D2500">
+        <v>1</v>
+      </c>
+      <c r="F2500">
+        <v>0.1</v>
+      </c>
+      <c r="G2500">
+        <v>0</v>
+      </c>
+      <c r="H2500">
+        <v>0</v>
+      </c>
+      <c r="L2500">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="M2500">
+        <v>101.2</v>
+      </c>
+      <c r="N2500">
+        <v>7.59</v>
+      </c>
+      <c r="O2500">
+        <v>0.43</v>
+      </c>
+      <c r="R2500" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="2501" spans="2:18">
+      <c r="D2501">
+        <v>2</v>
+      </c>
+      <c r="F2501">
+        <v>0.1</v>
+      </c>
+      <c r="G2501">
+        <v>0</v>
+      </c>
+      <c r="H2501">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2502" spans="2:18">
+      <c r="D2502">
+        <v>3</v>
+      </c>
+      <c r="F2502">
+        <v>0.1</v>
+      </c>
+      <c r="G2502">
+        <v>0</v>
+      </c>
+      <c r="H2502">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2503" spans="2:18">
+      <c r="B2503" s="1">
+        <v>0.6875</v>
+      </c>
+      <c r="C2503" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2503">
+        <v>1</v>
+      </c>
+      <c r="F2503">
+        <v>0.1</v>
+      </c>
+      <c r="G2503">
+        <v>0</v>
+      </c>
+      <c r="H2503">
+        <v>0</v>
+      </c>
+      <c r="L2503">
+        <v>9.5</v>
+      </c>
+      <c r="M2503">
+        <v>105.3</v>
+      </c>
+      <c r="N2503">
+        <v>12.24</v>
+      </c>
+      <c r="O2503">
+        <v>6.52</v>
+      </c>
+      <c r="R2503" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="2504" spans="2:18">
+      <c r="D2504">
+        <v>2</v>
+      </c>
+      <c r="F2504">
+        <v>0.1</v>
+      </c>
+      <c r="G2504">
+        <v>0</v>
+      </c>
+      <c r="H2504">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2505" spans="2:18">
+      <c r="D2505">
+        <v>3</v>
+      </c>
+      <c r="F2505">
+        <v>0.1</v>
+      </c>
+      <c r="G2505">
+        <v>0</v>
+      </c>
+      <c r="H2505">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2506" spans="2:18">
+      <c r="B2506" s="1">
+        <v>0.70625000000000004</v>
+      </c>
+      <c r="C2506" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2506">
+        <v>1</v>
+      </c>
+      <c r="F2506">
+        <v>0.1</v>
+      </c>
+      <c r="G2506">
+        <v>0</v>
+      </c>
+      <c r="H2506">
+        <v>0</v>
+      </c>
+      <c r="L2506">
+        <v>9.1</v>
+      </c>
+      <c r="M2506">
+        <v>106.7</v>
+      </c>
+      <c r="N2506">
+        <v>14.56</v>
+      </c>
+      <c r="O2506">
+        <v>0.78</v>
+      </c>
+      <c r="R2506" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="2507" spans="2:18">
+      <c r="D2507">
+        <v>2</v>
+      </c>
+      <c r="F2507">
+        <v>0.1</v>
+      </c>
+      <c r="G2507">
+        <v>0</v>
+      </c>
+      <c r="H2507">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2508" spans="2:18">
+      <c r="D2508">
+        <v>3</v>
+      </c>
+      <c r="F2508">
+        <v>0.1</v>
+      </c>
+      <c r="G2508">
+        <v>0</v>
+      </c>
+      <c r="H2508">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2509" spans="2:18">
+      <c r="B2509" s="1">
+        <v>0.72361111111111109</v>
+      </c>
+      <c r="C2509" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2509">
+        <v>1</v>
+      </c>
+      <c r="F2509">
+        <v>0.1</v>
+      </c>
+      <c r="G2509">
+        <v>0</v>
+      </c>
+      <c r="H2509">
+        <v>0</v>
+      </c>
+      <c r="L2509">
+        <v>9.6</v>
+      </c>
+      <c r="M2509">
+        <v>99.8</v>
+      </c>
+      <c r="N2509">
+        <v>9.14</v>
+      </c>
+      <c r="O2509">
+        <v>1.42</v>
+      </c>
+      <c r="R2509" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="2510" spans="2:18">
+      <c r="D2510">
+        <v>2</v>
+      </c>
+      <c r="F2510">
+        <v>0.1</v>
+      </c>
+      <c r="G2510">
+        <v>0</v>
+      </c>
+      <c r="H2510">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2511" spans="2:18">
+      <c r="D2511">
+        <v>3</v>
+      </c>
+      <c r="F2511">
+        <v>0.1</v>
+      </c>
+      <c r="G2511">
+        <v>0</v>
+      </c>
+      <c r="H2511">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2512" spans="2:18">
+      <c r="B2512" s="1">
+        <v>0.74027777777777781</v>
+      </c>
+      <c r="C2512" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2512">
+        <v>1</v>
+      </c>
+      <c r="F2512">
+        <v>0.1</v>
+      </c>
+      <c r="G2512">
+        <v>0</v>
+      </c>
+      <c r="H2512">
+        <v>0</v>
+      </c>
+      <c r="L2512">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="M2512">
+        <v>101.1</v>
+      </c>
+      <c r="N2512">
+        <v>4.03</v>
+      </c>
+      <c r="O2512">
+        <v>0.16</v>
+      </c>
+      <c r="R2512" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="2513" spans="1:18">
+      <c r="D2513">
+        <v>2</v>
+      </c>
+      <c r="F2513">
+        <v>0.1</v>
+      </c>
+      <c r="G2513">
+        <v>0</v>
+      </c>
+      <c r="H2513">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2514" spans="1:18">
+      <c r="D2514">
+        <v>3</v>
+      </c>
+      <c r="F2514">
+        <v>0.1</v>
+      </c>
+      <c r="G2514">
+        <v>0</v>
+      </c>
+      <c r="H2514">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2515" spans="1:18">
+      <c r="B2515" s="1">
+        <v>0.67222222222222228</v>
+      </c>
+      <c r="C2515" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D2515">
+        <v>1</v>
+      </c>
+      <c r="F2515">
+        <v>0.1</v>
+      </c>
+      <c r="G2515">
+        <v>0</v>
+      </c>
+      <c r="H2515">
+        <v>0</v>
+      </c>
+      <c r="L2515">
+        <v>10.5</v>
+      </c>
+      <c r="M2515">
+        <v>90.9</v>
+      </c>
+      <c r="N2515">
+        <v>3.03</v>
+      </c>
+      <c r="O2515">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="R2515" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="2516" spans="1:18">
+      <c r="D2516">
+        <v>2</v>
+      </c>
+      <c r="F2516">
+        <v>0.1</v>
+      </c>
+      <c r="G2516">
+        <v>0</v>
+      </c>
+      <c r="H2516">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2517" spans="1:18">
+      <c r="D2517">
+        <v>3</v>
+      </c>
+      <c r="F2517">
+        <v>0.1</v>
+      </c>
+      <c r="G2517">
+        <v>0</v>
+      </c>
+      <c r="H2517">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2518" spans="1:18">
+      <c r="B2518" s="1">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="C2518" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D2518">
+        <v>1</v>
+      </c>
+      <c r="F2518">
+        <v>0.1</v>
+      </c>
+      <c r="G2518">
+        <v>1</v>
+      </c>
+      <c r="H2518">
+        <v>0.1</v>
+      </c>
+      <c r="L2518">
+        <v>11.1</v>
+      </c>
+      <c r="M2518">
+        <v>96.6</v>
+      </c>
+      <c r="N2518">
+        <v>1.33</v>
+      </c>
+      <c r="O2518">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="R2518" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2519" spans="1:18">
+      <c r="C2519" s="3"/>
+      <c r="D2519">
+        <v>2</v>
+      </c>
+      <c r="F2519">
+        <v>0.1</v>
+      </c>
+      <c r="G2519">
+        <v>1</v>
+      </c>
+      <c r="H2519">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="2520" spans="1:18">
+      <c r="D2520">
+        <v>3</v>
+      </c>
+      <c r="F2520">
+        <v>0.1</v>
+      </c>
+      <c r="G2520">
+        <v>0.05</v>
+      </c>
+      <c r="H2520">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2521" spans="1:18" s="19" customFormat="1">
+      <c r="E2521" s="36"/>
+    </row>
+    <row r="2522" spans="1:18">
+      <c r="A2522" s="16" t="s">
+        <v>377</v>
+      </c>
+      <c r="B2522" s="1">
+        <v>0.53402777777777777</v>
+      </c>
+      <c r="C2522" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2522">
+        <v>1</v>
+      </c>
+      <c r="E2522" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2522">
+        <v>0.1</v>
+      </c>
+      <c r="G2522">
+        <v>0</v>
+      </c>
+      <c r="H2522">
+        <v>0</v>
+      </c>
+      <c r="L2522">
+        <v>10.6</v>
+      </c>
+      <c r="M2522">
+        <v>97.3</v>
+      </c>
+      <c r="N2522">
+        <v>1.34</v>
+      </c>
+      <c r="O2522">
+        <v>0.13</v>
+      </c>
+      <c r="P2522" t="s">
+        <v>378</v>
+      </c>
+      <c r="Q2522" t="s">
+        <v>360</v>
+      </c>
+      <c r="R2522" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="2523" spans="1:18">
+      <c r="D2523">
+        <v>2</v>
+      </c>
+      <c r="F2523">
+        <v>0.1</v>
+      </c>
+      <c r="G2523">
+        <v>0</v>
+      </c>
+      <c r="H2523">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2524" spans="1:18">
+      <c r="D2524">
+        <v>3</v>
+      </c>
+      <c r="F2524">
+        <v>0.1</v>
+      </c>
+      <c r="G2524">
+        <v>0</v>
+      </c>
+      <c r="H2524">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2525" spans="1:18">
+      <c r="B2525" s="1">
+        <v>0.54861111111111116</v>
+      </c>
+      <c r="C2525" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2525">
+        <v>1</v>
+      </c>
+      <c r="F2525">
+        <v>0.1</v>
+      </c>
+      <c r="G2525">
+        <v>0</v>
+      </c>
+      <c r="H2525">
+        <v>0</v>
+      </c>
+      <c r="L2525">
+        <v>13</v>
+      </c>
+      <c r="M2525">
+        <v>91.6</v>
+      </c>
+      <c r="N2525">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="O2525">
+        <v>0.04</v>
+      </c>
+      <c r="R2525" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="2526" spans="1:18">
+      <c r="D2526">
+        <v>2</v>
+      </c>
+      <c r="F2526">
+        <v>0.1</v>
+      </c>
+      <c r="G2526">
+        <v>0</v>
+      </c>
+      <c r="H2526">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2527" spans="1:18">
+      <c r="D2527">
+        <v>3</v>
+      </c>
+      <c r="F2527">
+        <v>0.1</v>
+      </c>
+      <c r="G2527">
+        <v>0</v>
+      </c>
+      <c r="H2527">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2528" spans="1:18">
+      <c r="B2528" s="1">
+        <v>0.56111111111111112</v>
+      </c>
+      <c r="C2528" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2528">
+        <v>1</v>
+      </c>
+      <c r="F2528">
+        <v>0.1</v>
+      </c>
+      <c r="G2528">
+        <v>0</v>
+      </c>
+      <c r="H2528">
+        <v>0</v>
+      </c>
+      <c r="L2528">
+        <v>10.9</v>
+      </c>
+      <c r="M2528">
+        <v>95.2</v>
+      </c>
+      <c r="N2528">
+        <v>1.34</v>
+      </c>
+      <c r="O2528">
+        <v>0.05</v>
+      </c>
+      <c r="R2528" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="2529" spans="2:18">
+      <c r="D2529">
+        <v>2</v>
+      </c>
+      <c r="F2529">
+        <v>0.1</v>
+      </c>
+      <c r="G2529">
+        <v>0</v>
+      </c>
+      <c r="H2529">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2530" spans="2:18">
+      <c r="D2530">
+        <v>3</v>
+      </c>
+      <c r="F2530">
+        <v>0.1</v>
+      </c>
+      <c r="G2530">
+        <v>0</v>
+      </c>
+      <c r="H2530">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2531" spans="2:18">
+      <c r="B2531" s="1">
+        <v>0.56805555555555554</v>
+      </c>
+      <c r="C2531" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D2531">
+        <v>1</v>
+      </c>
+      <c r="F2531">
+        <v>0.1</v>
+      </c>
+      <c r="G2531">
+        <v>1.39</v>
+      </c>
+      <c r="H2531">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="L2531">
+        <v>11.4</v>
+      </c>
+      <c r="M2531">
+        <v>97.6</v>
+      </c>
+      <c r="N2531">
+        <v>5.15</v>
+      </c>
+      <c r="O2531">
+        <v>0.63</v>
+      </c>
+      <c r="R2531" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="2532" spans="2:18">
+      <c r="D2532">
+        <v>2</v>
+      </c>
+      <c r="F2532">
+        <v>0.1</v>
+      </c>
+      <c r="G2532">
+        <v>1.78</v>
+      </c>
+      <c r="H2532">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="2533" spans="2:18">
+      <c r="D2533">
+        <v>3</v>
+      </c>
+      <c r="F2533">
+        <v>0.1</v>
+      </c>
+      <c r="G2533">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="H2533">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="2534" spans="2:18">
+      <c r="B2534" s="1">
+        <v>0.59166666666666667</v>
+      </c>
+      <c r="C2534" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2534">
+        <v>1</v>
+      </c>
+      <c r="F2534">
+        <v>0.1</v>
+      </c>
+      <c r="G2534">
+        <v>0.2</v>
+      </c>
+      <c r="H2534">
+        <v>0.5</v>
+      </c>
+      <c r="L2534">
+        <v>10.6</v>
+      </c>
+      <c r="M2534">
+        <v>109.7</v>
+      </c>
+      <c r="N2534">
+        <v>3.16</v>
+      </c>
+      <c r="O2534">
+        <v>0.3</v>
+      </c>
+      <c r="R2534" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="2535" spans="2:18">
+      <c r="D2535">
+        <v>2</v>
+      </c>
+      <c r="F2535">
+        <v>0.1</v>
+      </c>
+      <c r="G2535">
+        <v>0.1</v>
+      </c>
+      <c r="H2535">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2536" spans="2:18">
+      <c r="D2536">
+        <v>3</v>
+      </c>
+      <c r="F2536">
+        <v>0.1</v>
+      </c>
+      <c r="G2536">
+        <v>0.7</v>
+      </c>
+      <c r="H2536">
+        <v>0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="2537" spans="2:18">
+      <c r="B2537" s="1">
+        <v>0.60138888888888886</v>
+      </c>
+      <c r="C2537" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2537">
+        <v>1</v>
+      </c>
+      <c r="F2537">
+        <v>0.1</v>
+      </c>
+      <c r="G2537">
+        <v>0</v>
+      </c>
+      <c r="H2537">
+        <v>0</v>
+      </c>
+      <c r="L2537">
+        <v>11.2</v>
+      </c>
+      <c r="M2537">
+        <v>101.7</v>
+      </c>
+      <c r="N2537">
+        <v>0.82</v>
+      </c>
+      <c r="O2537">
+        <v>0.04</v>
+      </c>
+      <c r="R2537" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="2538" spans="2:18">
+      <c r="D2538">
+        <v>2</v>
+      </c>
+      <c r="F2538">
+        <v>0.1</v>
+      </c>
+      <c r="G2538">
+        <v>0</v>
+      </c>
+      <c r="H2538">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2539" spans="2:18">
+      <c r="D2539">
+        <v>3</v>
+      </c>
+      <c r="F2539">
+        <v>0.1</v>
+      </c>
+      <c r="G2539">
+        <v>0.3</v>
+      </c>
+      <c r="H2539">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="2540" spans="2:18">
+      <c r="B2540" s="1">
+        <v>0.61041666666666672</v>
+      </c>
+      <c r="C2540" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2540">
+        <v>1</v>
+      </c>
+      <c r="F2540">
+        <v>0.1</v>
+      </c>
+      <c r="G2540">
+        <v>0.35</v>
+      </c>
+      <c r="H2540">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="L2540">
+        <v>11.6</v>
+      </c>
+      <c r="M2540">
+        <v>104</v>
+      </c>
+      <c r="N2540">
+        <v>2.95</v>
+      </c>
+      <c r="O2540">
+        <v>0.8</v>
+      </c>
+      <c r="R2540" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="2541" spans="2:18">
+      <c r="D2541">
+        <v>2</v>
+      </c>
+      <c r="F2541">
+        <v>0.1</v>
+      </c>
+      <c r="G2541">
+        <v>0</v>
+      </c>
+      <c r="H2541">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2542" spans="2:18">
+      <c r="D2542">
+        <v>3</v>
+      </c>
+      <c r="F2542">
+        <v>0.1</v>
+      </c>
+      <c r="G2542">
+        <v>0</v>
+      </c>
+      <c r="H2542">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2543" spans="2:18">
+      <c r="B2543" s="1">
+        <v>0.62708333333333333</v>
+      </c>
+      <c r="C2543" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2543">
+        <v>1</v>
+      </c>
+      <c r="F2543">
+        <v>0.1</v>
+      </c>
+      <c r="G2543">
+        <v>0</v>
+      </c>
+      <c r="H2543">
+        <v>0</v>
+      </c>
+      <c r="L2543">
+        <v>12</v>
+      </c>
+      <c r="M2543">
+        <v>99.6</v>
+      </c>
+      <c r="N2543">
+        <v>0.84</v>
+      </c>
+      <c r="O2543">
+        <v>0.06</v>
+      </c>
+      <c r="R2543" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="2544" spans="2:18">
+      <c r="D2544">
+        <v>2</v>
+      </c>
+      <c r="F2544">
+        <v>0.1</v>
+      </c>
+      <c r="G2544">
+        <v>0</v>
+      </c>
+      <c r="H2544">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2545" spans="1:18">
+      <c r="D2545">
+        <v>3</v>
+      </c>
+      <c r="F2545">
+        <v>0.1</v>
+      </c>
+      <c r="G2545">
+        <v>0</v>
+      </c>
+      <c r="H2545">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2546" spans="1:18">
+      <c r="B2546" s="1">
+        <v>0.50902777777777775</v>
+      </c>
+      <c r="C2546" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D2546">
+        <v>1</v>
+      </c>
+      <c r="F2546">
+        <v>0.1</v>
+      </c>
+      <c r="G2546">
+        <v>0</v>
+      </c>
+      <c r="H2546">
+        <v>0</v>
+      </c>
+      <c r="L2546">
+        <v>11.3</v>
+      </c>
+      <c r="M2546">
+        <v>98.4</v>
+      </c>
+      <c r="N2546">
+        <v>0.88</v>
+      </c>
+      <c r="O2546">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="R2546" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="2547" spans="1:18">
+      <c r="D2547">
+        <v>2</v>
+      </c>
+      <c r="F2547">
+        <v>0.1</v>
+      </c>
+      <c r="G2547">
+        <v>0</v>
+      </c>
+      <c r="H2547">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2548" spans="1:18">
+      <c r="D2548">
+        <v>3</v>
+      </c>
+      <c r="F2548">
+        <v>0.1</v>
+      </c>
+      <c r="G2548">
+        <v>0</v>
+      </c>
+      <c r="H2548">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2549" spans="1:18">
+      <c r="B2549" s="1">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="C2549" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D2549">
+        <v>1</v>
+      </c>
+      <c r="F2549">
+        <v>0.1</v>
+      </c>
+      <c r="G2549">
+        <v>0</v>
+      </c>
+      <c r="H2549">
+        <v>0</v>
+      </c>
+      <c r="L2549">
+        <v>10.8</v>
+      </c>
+      <c r="M2549">
+        <v>93.1</v>
+      </c>
+      <c r="N2549">
+        <v>0.95</v>
+      </c>
+      <c r="O2549">
+        <v>0.04</v>
+      </c>
+      <c r="R2549" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="2550" spans="1:18">
+      <c r="C2550" s="3"/>
+      <c r="D2550">
+        <v>2</v>
+      </c>
+      <c r="F2550">
+        <v>0.1</v>
+      </c>
+      <c r="G2550">
+        <v>0</v>
+      </c>
+      <c r="H2550">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2551" spans="1:18">
+      <c r="D2551">
+        <v>3</v>
+      </c>
+      <c r="F2551">
+        <v>0.1</v>
+      </c>
+      <c r="G2551">
+        <v>0</v>
+      </c>
+      <c r="H2551">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2552" spans="1:18" s="19" customFormat="1">
+      <c r="E2552" s="36"/>
+    </row>
+    <row r="2553" spans="1:18">
+      <c r="A2553" t="s">
+        <v>380</v>
+      </c>
+      <c r="B2553" s="1">
+        <v>0.50069444444444444</v>
+      </c>
+      <c r="C2553" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2553">
+        <v>1</v>
+      </c>
+      <c r="E2553" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2553">
+        <v>0.1</v>
+      </c>
+      <c r="G2553">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="H2553">
+        <v>0.09</v>
+      </c>
+      <c r="L2553">
+        <v>12.7</v>
+      </c>
+      <c r="M2553">
+        <v>98.1</v>
+      </c>
+      <c r="N2553">
+        <v>2</v>
+      </c>
+      <c r="O2553">
+        <v>0.12</v>
+      </c>
+      <c r="P2553" t="s">
+        <v>202</v>
+      </c>
+      <c r="Q2553" t="s">
+        <v>381</v>
+      </c>
+      <c r="R2553" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="2554" spans="1:18">
+      <c r="D2554">
+        <v>2</v>
+      </c>
+      <c r="F2554">
+        <v>0.1</v>
+      </c>
+      <c r="G2554">
+        <v>0.5</v>
+      </c>
+      <c r="H2554">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="2555" spans="1:18">
+      <c r="D2555">
+        <v>3</v>
+      </c>
+      <c r="F2555">
+        <v>0.1</v>
+      </c>
+      <c r="G2555">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="H2555">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="2556" spans="1:18">
+      <c r="B2556" s="1">
+        <v>0.52222222222222225</v>
+      </c>
+      <c r="C2556" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2556">
+        <v>1</v>
+      </c>
+      <c r="F2556">
+        <v>0.1</v>
+      </c>
+      <c r="G2556">
+        <v>1.34</v>
+      </c>
+      <c r="H2556">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="L2556">
+        <v>11.6</v>
+      </c>
+      <c r="M2556">
+        <v>95.1</v>
+      </c>
+      <c r="N2556">
+        <v>2.7</v>
+      </c>
+      <c r="O2556">
+        <v>0.13</v>
+      </c>
+      <c r="R2556" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="2557" spans="1:18">
+      <c r="D2557">
+        <v>2</v>
+      </c>
+      <c r="F2557">
+        <v>0.1</v>
+      </c>
+      <c r="G2557">
+        <v>1.39</v>
+      </c>
+      <c r="H2557">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="2558" spans="1:18">
+      <c r="D2558">
+        <v>3</v>
+      </c>
+      <c r="F2558">
+        <v>0.1</v>
+      </c>
+      <c r="G2558">
+        <v>0.45</v>
+      </c>
+      <c r="H2558">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="2559" spans="1:18">
+      <c r="B2559" s="1">
+        <v>0.54513888888888884</v>
+      </c>
+      <c r="C2559" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2559">
+        <v>1</v>
+      </c>
+      <c r="F2559">
+        <v>295.41000000000003</v>
+      </c>
+      <c r="G2559">
+        <v>2.86</v>
+      </c>
+      <c r="H2559">
+        <v>103.29</v>
+      </c>
+      <c r="L2559">
+        <v>11.6</v>
+      </c>
+      <c r="M2559">
+        <v>102.5</v>
+      </c>
+      <c r="N2559">
+        <v>1.49</v>
+      </c>
+      <c r="O2559">
+        <v>0.19</v>
+      </c>
+      <c r="R2559" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="2560" spans="1:18">
+      <c r="D2560">
+        <v>2</v>
+      </c>
+      <c r="F2560">
+        <v>193.42</v>
+      </c>
+      <c r="G2560">
+        <v>1.68</v>
+      </c>
+      <c r="H2560">
+        <v>115.13</v>
+      </c>
+    </row>
+    <row r="2561" spans="2:18">
+      <c r="D2561">
+        <v>3</v>
+      </c>
+      <c r="F2561">
+        <v>395.06</v>
+      </c>
+      <c r="G2561">
+        <v>2.91</v>
+      </c>
+      <c r="H2561">
+        <v>135.75</v>
+      </c>
+    </row>
+    <row r="2562" spans="2:18">
+      <c r="B2562" s="1">
+        <v>0.55694444444444446</v>
+      </c>
+      <c r="C2562" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D2562">
+        <v>1</v>
+      </c>
+      <c r="F2562">
+        <v>1.75</v>
+      </c>
+      <c r="G2562">
+        <v>1.54</v>
+      </c>
+      <c r="H2562">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="L2562">
+        <v>12.5</v>
+      </c>
+      <c r="M2562">
+        <v>103.2</v>
+      </c>
+      <c r="N2562">
+        <v>2.7</v>
+      </c>
+      <c r="O2562">
+        <v>0.13</v>
+      </c>
+      <c r="R2562" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="2563" spans="2:18">
+      <c r="D2563">
+        <v>2</v>
+      </c>
+      <c r="F2563">
+        <v>6.25</v>
+      </c>
+      <c r="G2563">
+        <v>0</v>
+      </c>
+      <c r="H2563">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2564" spans="2:18">
+      <c r="D2564">
+        <v>3</v>
+      </c>
+      <c r="F2564">
+        <v>1</v>
+      </c>
+      <c r="G2564">
+        <v>0.3</v>
+      </c>
+      <c r="H2564">
+        <v>3.33</v>
+      </c>
+    </row>
+    <row r="2565" spans="2:18">
+      <c r="B2565" s="1">
+        <v>0.56597222222222221</v>
+      </c>
+      <c r="C2565" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2565">
+        <v>1</v>
+      </c>
+      <c r="F2565">
+        <v>0.1</v>
+      </c>
+      <c r="G2565">
+        <v>0</v>
+      </c>
+      <c r="H2565">
+        <v>0</v>
+      </c>
+      <c r="L2565">
+        <v>12</v>
+      </c>
+      <c r="M2565">
+        <v>107</v>
+      </c>
+      <c r="N2565">
+        <v>4.99</v>
+      </c>
+      <c r="O2565">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="R2565" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="2566" spans="2:18">
+      <c r="D2566">
+        <v>2</v>
+      </c>
+      <c r="F2566">
+        <v>0.1</v>
+      </c>
+      <c r="G2566">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="H2566">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="2567" spans="2:18">
+      <c r="D2567">
+        <v>3</v>
+      </c>
+      <c r="F2567">
+        <v>0.1</v>
+      </c>
+      <c r="G2567">
+        <v>0.5</v>
+      </c>
+      <c r="H2567">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="2568" spans="2:18">
+      <c r="B2568" s="1">
+        <v>0.57013888888888886</v>
+      </c>
+      <c r="C2568" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2568">
+        <v>1</v>
+      </c>
+      <c r="F2568">
+        <v>0.1</v>
+      </c>
+      <c r="G2568">
+        <v>0.8</v>
+      </c>
+      <c r="H2568">
+        <v>0.12</v>
+      </c>
+      <c r="L2568">
+        <v>10.9</v>
+      </c>
+      <c r="M2568">
+        <v>102.5</v>
+      </c>
+      <c r="N2568">
+        <v>2.5299999999999998</v>
+      </c>
+      <c r="O2568">
+        <v>0.25</v>
+      </c>
+      <c r="R2568" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="2569" spans="2:18">
+      <c r="D2569">
+        <v>2</v>
+      </c>
+      <c r="F2569">
+        <v>0.1</v>
+      </c>
+      <c r="G2569">
+        <v>0.3</v>
+      </c>
+      <c r="H2569">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="2570" spans="2:18">
+      <c r="D2570">
+        <v>3</v>
+      </c>
+      <c r="F2570">
+        <v>0.1</v>
+      </c>
+      <c r="G2570">
+        <v>1.19</v>
+      </c>
+      <c r="H2570">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="2571" spans="2:18">
+      <c r="B2571" s="1">
+        <v>0.58472222222222225</v>
+      </c>
+      <c r="C2571" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2571">
+        <v>1</v>
+      </c>
+      <c r="F2571">
+        <v>0.1</v>
+      </c>
+      <c r="G2571">
+        <v>0</v>
+      </c>
+      <c r="H2571">
+        <v>0</v>
+      </c>
+      <c r="L2571">
+        <v>13</v>
+      </c>
+      <c r="M2571">
+        <v>100.6</v>
+      </c>
+      <c r="N2571">
+        <v>1.23</v>
+      </c>
+      <c r="O2571">
+        <v>0.01</v>
+      </c>
+      <c r="R2571" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="2572" spans="2:18">
+      <c r="D2572">
+        <v>2</v>
+      </c>
+      <c r="F2572">
+        <v>0.1</v>
+      </c>
+      <c r="G2572">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="H2572">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="2573" spans="2:18">
+      <c r="D2573">
+        <v>3</v>
+      </c>
+      <c r="F2573">
+        <v>0.1</v>
+      </c>
+      <c r="G2573">
+        <v>0.2</v>
+      </c>
+      <c r="H2573">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="2574" spans="2:18">
+      <c r="B2574" s="1"/>
+      <c r="C2574" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2574">
+        <v>1</v>
+      </c>
+      <c r="F2574">
+        <v>0.1</v>
+      </c>
+      <c r="G2574">
+        <v>0</v>
+      </c>
+      <c r="H2574">
+        <v>0</v>
+      </c>
+      <c r="L2574">
+        <v>11.8</v>
+      </c>
+      <c r="M2574">
+        <v>101.9</v>
+      </c>
+      <c r="N2574">
+        <v>0.92</v>
+      </c>
+      <c r="O2574">
+        <v>0.19</v>
+      </c>
+      <c r="R2574" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="2575" spans="2:18">
+      <c r="D2575">
+        <v>2</v>
+      </c>
+      <c r="F2575">
+        <v>0.1</v>
+      </c>
+      <c r="G2575">
+        <v>0.35</v>
+      </c>
+      <c r="H2575">
+        <v>0.28000000000000003</v>
+      </c>
+    </row>
+    <row r="2576" spans="2:18">
+      <c r="D2576">
+        <v>3</v>
+      </c>
+      <c r="F2576">
+        <v>0.1</v>
+      </c>
+      <c r="G2576">
+        <v>0</v>
+      </c>
+      <c r="H2576">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2577" spans="1:18">
+      <c r="C2577" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D2577">
+        <v>1</v>
+      </c>
+      <c r="F2577">
+        <v>0.1</v>
+      </c>
+      <c r="G2577">
+        <v>0</v>
+      </c>
+      <c r="H2577">
+        <v>0</v>
+      </c>
+      <c r="L2577">
+        <v>11.3</v>
+      </c>
+      <c r="M2577">
+        <v>100.3</v>
+      </c>
+      <c r="N2577">
+        <v>0.73</v>
+      </c>
+      <c r="O2577">
+        <v>0.08</v>
+      </c>
+      <c r="R2577" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="2578" spans="1:18">
+      <c r="D2578">
+        <v>2</v>
+      </c>
+      <c r="F2578">
+        <v>0.1</v>
+      </c>
+      <c r="G2578">
+        <v>0</v>
+      </c>
+      <c r="H2578">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2579" spans="1:18">
+      <c r="D2579">
+        <v>3</v>
+      </c>
+      <c r="F2579">
+        <v>0.1</v>
+      </c>
+      <c r="G2579">
+        <v>0</v>
+      </c>
+      <c r="H2579">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2580" spans="1:18">
+      <c r="C2580" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D2580">
+        <v>1</v>
+      </c>
+      <c r="F2580">
+        <v>0.1</v>
+      </c>
+      <c r="G2580">
+        <v>0</v>
+      </c>
+      <c r="H2580">
+        <v>0</v>
+      </c>
+      <c r="L2580">
+        <v>11.7</v>
+      </c>
+      <c r="M2580">
+        <v>94.7</v>
+      </c>
+      <c r="N2580">
+        <v>0.99</v>
+      </c>
+      <c r="O2580">
+        <v>0.01</v>
+      </c>
+      <c r="R2580" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="2581" spans="1:18">
+      <c r="C2581" s="3"/>
+      <c r="D2581">
+        <v>2</v>
+      </c>
+      <c r="F2581">
+        <v>0.1</v>
+      </c>
+      <c r="G2581">
+        <v>0</v>
+      </c>
+      <c r="H2581">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2582" spans="1:18">
+      <c r="D2582">
+        <v>3</v>
+      </c>
+      <c r="F2582">
+        <v>0.1</v>
+      </c>
+      <c r="G2582">
+        <v>0</v>
+      </c>
+      <c r="H2582">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2583" spans="1:18" s="19" customFormat="1">
+      <c r="E2583" s="36"/>
+    </row>
+    <row r="2584" spans="1:18">
+      <c r="A2584" t="s">
+        <v>384</v>
+      </c>
+      <c r="B2584" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="C2584" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2584">
+        <v>1</v>
+      </c>
+      <c r="E2584" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2584">
+        <v>0.1</v>
+      </c>
+      <c r="G2584">
+        <v>0</v>
+      </c>
+      <c r="H2584">
+        <v>0</v>
+      </c>
+      <c r="L2584">
+        <v>11.7</v>
+      </c>
+      <c r="M2584">
+        <v>97.3</v>
+      </c>
+      <c r="N2584">
+        <v>1.75</v>
+      </c>
+      <c r="O2584">
+        <v>0.39</v>
+      </c>
+      <c r="P2584" t="s">
+        <v>385</v>
+      </c>
+      <c r="Q2584" t="s">
+        <v>386</v>
+      </c>
+      <c r="R2584" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="2585" spans="1:18">
+      <c r="D2585">
+        <v>2</v>
+      </c>
+      <c r="F2585">
+        <v>211.22</v>
+      </c>
+      <c r="G2585">
+        <v>0.45</v>
+      </c>
+      <c r="H2585">
+        <v>478.26</v>
+      </c>
+    </row>
+    <row r="2586" spans="1:18">
+      <c r="D2586">
+        <v>3</v>
+      </c>
+      <c r="F2586">
+        <v>0.1</v>
+      </c>
+      <c r="G2586">
+        <v>0.2</v>
+      </c>
+      <c r="H2586">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="2587" spans="1:18">
+      <c r="C2587" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2587">
+        <v>1</v>
+      </c>
+      <c r="F2587">
+        <v>0.1</v>
+      </c>
+      <c r="G2587">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="H2587">
+        <v>0.18</v>
+      </c>
+      <c r="L2587">
+        <v>11.6</v>
+      </c>
+      <c r="M2587">
+        <v>93.2</v>
+      </c>
+      <c r="N2587">
+        <v>3.06</v>
+      </c>
+      <c r="O2587">
+        <v>0.08</v>
+      </c>
+      <c r="R2587" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="2588" spans="1:18">
+      <c r="D2588">
+        <v>2</v>
+      </c>
+      <c r="F2588">
+        <v>0.1</v>
+      </c>
+      <c r="G2588">
+        <v>0.5</v>
+      </c>
+      <c r="H2588">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="2589" spans="1:18">
+      <c r="D2589">
+        <v>3</v>
+      </c>
+      <c r="F2589">
+        <v>0.1</v>
+      </c>
+      <c r="G2589">
+        <v>0</v>
+      </c>
+      <c r="H2589">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2590" spans="1:18">
+      <c r="C2590" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2590">
+        <v>1</v>
+      </c>
+      <c r="F2590">
+        <v>0.1</v>
+      </c>
+      <c r="G2590">
+        <v>0</v>
+      </c>
+      <c r="H2590">
+        <v>0</v>
+      </c>
+      <c r="L2590">
+        <v>11.4</v>
+      </c>
+      <c r="M2590">
+        <v>95.6</v>
+      </c>
+      <c r="N2590">
+        <v>0.82</v>
+      </c>
+      <c r="O2590">
+        <v>0.1</v>
+      </c>
+      <c r="R2590" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="2591" spans="1:18">
+      <c r="D2591">
+        <v>2</v>
+      </c>
+      <c r="F2591">
+        <v>0.1</v>
+      </c>
+      <c r="G2591">
+        <v>0</v>
+      </c>
+      <c r="H2591">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2592" spans="1:18">
+      <c r="D2592">
+        <v>3</v>
+      </c>
+      <c r="F2592">
+        <v>0.1</v>
+      </c>
+      <c r="G2592">
+        <v>0</v>
+      </c>
+      <c r="H2592">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2593" spans="3:18">
+      <c r="C2593" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D2593">
+        <v>1</v>
+      </c>
+      <c r="F2593">
+        <v>0.1</v>
+      </c>
+      <c r="G2593">
+        <v>0</v>
+      </c>
+      <c r="H2593">
+        <v>0</v>
+      </c>
+      <c r="L2593">
+        <v>11.1</v>
+      </c>
+      <c r="M2593">
+        <v>102.8</v>
+      </c>
+      <c r="N2593">
+        <v>1.5</v>
+      </c>
+      <c r="O2593">
+        <v>0.18</v>
+      </c>
+      <c r="R2593" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="2594" spans="3:18">
+      <c r="D2594">
+        <v>2</v>
+      </c>
+      <c r="F2594">
+        <v>0.1</v>
+      </c>
+      <c r="G2594">
+        <v>0</v>
+      </c>
+      <c r="H2594">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2595" spans="3:18">
+      <c r="D2595">
+        <v>3</v>
+      </c>
+      <c r="F2595">
+        <v>0.1</v>
+      </c>
+      <c r="G2595">
+        <v>0</v>
+      </c>
+      <c r="H2595">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2596" spans="3:18">
+      <c r="C2596" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2596">
+        <v>1</v>
+      </c>
+      <c r="F2596">
+        <v>0.1</v>
+      </c>
+      <c r="G2596">
+        <v>0</v>
+      </c>
+      <c r="H2596">
+        <v>0</v>
+      </c>
+      <c r="L2596">
+        <v>11.7</v>
+      </c>
+      <c r="M2596">
+        <v>122.4</v>
+      </c>
+      <c r="N2596">
+        <v>0.98</v>
+      </c>
+      <c r="O2596">
+        <v>0.06</v>
+      </c>
+      <c r="R2596" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="2597" spans="3:18">
+      <c r="D2597">
+        <v>2</v>
+      </c>
+      <c r="F2597">
+        <v>0.1</v>
+      </c>
+      <c r="G2597">
+        <v>0</v>
+      </c>
+      <c r="H2597">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2598" spans="3:18">
+      <c r="D2598">
+        <v>3</v>
+      </c>
+      <c r="F2598">
+        <v>0.1</v>
+      </c>
+      <c r="G2598">
+        <v>0</v>
+      </c>
+      <c r="H2598">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2599" spans="3:18">
+      <c r="C2599" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2599">
+        <v>1</v>
+      </c>
+      <c r="F2599">
+        <v>0.1</v>
+      </c>
+      <c r="G2599">
+        <v>0</v>
+      </c>
+      <c r="H2599">
+        <v>0</v>
+      </c>
+      <c r="L2599">
+        <v>11.3</v>
+      </c>
+      <c r="M2599">
+        <v>101.7</v>
+      </c>
+      <c r="N2599">
+        <v>0.72</v>
+      </c>
+      <c r="O2599">
+        <v>0.08</v>
+      </c>
+      <c r="R2599" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="2600" spans="3:18">
+      <c r="D2600">
+        <v>2</v>
+      </c>
+      <c r="F2600">
+        <v>0.1</v>
+      </c>
+      <c r="G2600">
+        <v>0.1</v>
+      </c>
+      <c r="H2600">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2601" spans="3:18">
+      <c r="D2601">
+        <v>3</v>
+      </c>
+      <c r="F2601">
+        <v>0.1</v>
+      </c>
+      <c r="G2601">
+        <v>0.05</v>
+      </c>
+      <c r="H2601">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2602" spans="3:18">
+      <c r="C2602" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2602">
+        <v>1</v>
+      </c>
+      <c r="F2602">
+        <v>0.1</v>
+      </c>
+      <c r="G2602">
+        <v>0</v>
+      </c>
+      <c r="H2602">
+        <v>0</v>
+      </c>
+      <c r="L2602">
+        <v>12.9</v>
+      </c>
+      <c r="M2602">
+        <v>104.8</v>
+      </c>
+      <c r="N2602">
+        <v>0.96</v>
+      </c>
+      <c r="O2602">
+        <v>0.2</v>
+      </c>
+      <c r="R2602" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="2603" spans="3:18">
+      <c r="D2603">
+        <v>2</v>
+      </c>
+      <c r="F2603">
+        <v>0.1</v>
+      </c>
+      <c r="G2603">
+        <v>0.45</v>
+      </c>
+      <c r="H2603">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="2604" spans="3:18">
+      <c r="D2604">
+        <v>3</v>
+      </c>
+      <c r="F2604">
+        <v>0.1</v>
+      </c>
+      <c r="G2604">
+        <v>0.45</v>
+      </c>
+      <c r="H2604">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="2605" spans="3:18">
+      <c r="C2605" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2605">
+        <v>1</v>
+      </c>
+      <c r="F2605">
+        <v>0.1</v>
+      </c>
+      <c r="G2605">
+        <v>1.63</v>
+      </c>
+      <c r="H2605">
+        <v>0.06</v>
+      </c>
+      <c r="L2605">
+        <v>12.6</v>
+      </c>
+      <c r="M2605">
+        <v>100.8</v>
+      </c>
+      <c r="N2605">
+        <v>0.63</v>
+      </c>
+      <c r="O2605">
+        <v>0.09</v>
+      </c>
+      <c r="R2605" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="2606" spans="3:18">
+      <c r="D2606">
+        <v>2</v>
+      </c>
+      <c r="F2606">
+        <v>58.52</v>
+      </c>
+      <c r="G2606">
+        <v>1.98</v>
+      </c>
+      <c r="H2606">
+        <v>29.55</v>
+      </c>
+    </row>
+    <row r="2607" spans="3:18">
+      <c r="D2607">
+        <v>3</v>
+      </c>
+      <c r="F2607">
+        <v>17.04</v>
+      </c>
+      <c r="G2607">
+        <v>2.4700000000000002</v>
+      </c>
+      <c r="H2607">
+        <v>6.89</v>
+      </c>
+    </row>
+    <row r="2608" spans="3:18">
+      <c r="C2608" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D2608">
+        <v>1</v>
+      </c>
+      <c r="F2608">
+        <v>0.1</v>
+      </c>
+      <c r="G2608">
+        <v>2.13</v>
+      </c>
+      <c r="H2608">
+        <v>0.04</v>
+      </c>
+      <c r="L2608">
+        <v>11.6</v>
+      </c>
+      <c r="M2608">
+        <v>104.4</v>
+      </c>
+      <c r="N2608">
+        <v>1.51</v>
+      </c>
+      <c r="O2608">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="R2608" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="2609" spans="1:18">
+      <c r="D2609">
+        <v>2</v>
+      </c>
+      <c r="F2609">
+        <v>1.75</v>
+      </c>
+      <c r="G2609">
+        <v>1.98</v>
+      </c>
+      <c r="H2609">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="2610" spans="1:18">
+      <c r="D2610">
+        <v>3</v>
+      </c>
+      <c r="F2610">
+        <v>13.13</v>
+      </c>
+      <c r="G2610">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="H2610">
+        <v>6.46</v>
+      </c>
+    </row>
+    <row r="2611" spans="1:18">
+      <c r="C2611" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D2611">
+        <v>1</v>
+      </c>
+      <c r="R2611" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="2612" spans="1:18">
+      <c r="C2612" s="3"/>
+      <c r="D2612">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2613" spans="1:18">
+      <c r="D2613">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2614" spans="1:18" s="19" customFormat="1">
+      <c r="E2614" s="36"/>
+      <c r="O2614" s="39" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="2615" spans="1:18">
+      <c r="A2615" t="s">
+        <v>387</v>
+      </c>
+      <c r="C2615" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2615">
+        <v>1</v>
+      </c>
+      <c r="E2615" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2615">
+        <v>0.1</v>
+      </c>
+      <c r="G2615">
+        <v>0</v>
+      </c>
+      <c r="H2615">
+        <v>0</v>
+      </c>
+      <c r="P2615" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="2616" spans="1:18">
+      <c r="D2616">
+        <v>2</v>
+      </c>
+      <c r="F2616">
+        <v>0.1</v>
+      </c>
+      <c r="G2616">
+        <v>0</v>
+      </c>
+      <c r="H2616">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2617" spans="1:18">
+      <c r="D2617">
+        <v>3</v>
+      </c>
+      <c r="F2617">
+        <v>0.1</v>
+      </c>
+      <c r="G2617">
+        <v>0</v>
+      </c>
+      <c r="H2617">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2618" spans="1:18">
+      <c r="C2618" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2618">
+        <v>1</v>
+      </c>
+      <c r="F2618">
+        <v>0.1</v>
+      </c>
+      <c r="G2618">
+        <v>0</v>
+      </c>
+      <c r="H2618">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2619" spans="1:18">
+      <c r="D2619">
+        <v>2</v>
+      </c>
+      <c r="F2619">
+        <v>0.1</v>
+      </c>
+      <c r="G2619">
+        <v>0</v>
+      </c>
+      <c r="H2619">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2620" spans="1:18">
+      <c r="D2620">
+        <v>3</v>
+      </c>
+      <c r="F2620">
+        <v>0.1</v>
+      </c>
+      <c r="G2620">
+        <v>0</v>
+      </c>
+      <c r="H2620">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2621" spans="1:18">
+      <c r="C2621" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2621">
+        <v>1</v>
+      </c>
+      <c r="F2621">
+        <v>0.1</v>
+      </c>
+      <c r="G2621">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="H2621">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="2622" spans="1:18">
+      <c r="D2622">
+        <v>2</v>
+      </c>
+      <c r="F2622">
+        <v>0.1</v>
+      </c>
+      <c r="G2622">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="H2622">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="2623" spans="1:18">
+      <c r="D2623">
+        <v>3</v>
+      </c>
+      <c r="F2623">
+        <v>0.1</v>
+      </c>
+      <c r="G2623">
+        <v>2.37</v>
+      </c>
+      <c r="H2623">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="2624" spans="1:18">
+      <c r="C2624" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D2624">
+        <v>1</v>
+      </c>
+      <c r="F2624">
+        <v>0.1</v>
+      </c>
+      <c r="G2624">
+        <v>0.05</v>
+      </c>
+      <c r="H2624">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2625" spans="3:8">
+      <c r="D2625">
+        <v>2</v>
+      </c>
+      <c r="F2625">
+        <v>0.1</v>
+      </c>
+      <c r="G2625">
+        <v>0</v>
+      </c>
+      <c r="H2625">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2626" spans="3:8">
+      <c r="D2626">
+        <v>3</v>
+      </c>
+      <c r="F2626">
+        <v>0.1</v>
+      </c>
+      <c r="G2626">
+        <v>0.2</v>
+      </c>
+      <c r="H2626">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="2627" spans="3:8">
+      <c r="C2627" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2627">
+        <v>1</v>
+      </c>
+      <c r="F2627">
+        <v>0.1</v>
+      </c>
+      <c r="G2627">
+        <v>0</v>
+      </c>
+      <c r="H2627">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2628" spans="3:8">
+      <c r="D2628">
+        <v>2</v>
+      </c>
+      <c r="F2628">
+        <v>0.1</v>
+      </c>
+      <c r="G2628">
+        <v>0</v>
+      </c>
+      <c r="H2628">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2629" spans="3:8">
+      <c r="D2629">
+        <v>3</v>
+      </c>
+      <c r="F2629">
+        <v>0.1</v>
+      </c>
+      <c r="G2629">
+        <v>0</v>
+      </c>
+      <c r="H2629">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2630" spans="3:8">
+      <c r="C2630" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2630">
+        <v>1</v>
+      </c>
+      <c r="F2630">
+        <v>0.1</v>
+      </c>
+      <c r="G2630">
+        <v>0</v>
+      </c>
+      <c r="H2630">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2631" spans="3:8">
+      <c r="D2631">
+        <v>2</v>
+      </c>
+      <c r="F2631">
+        <v>0.1</v>
+      </c>
+      <c r="G2631">
+        <v>0</v>
+      </c>
+      <c r="H2631">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2632" spans="3:8">
+      <c r="D2632">
+        <v>3</v>
+      </c>
+      <c r="F2632">
+        <v>0.1</v>
+      </c>
+      <c r="G2632">
+        <v>0</v>
+      </c>
+      <c r="H2632">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2633" spans="3:8">
+      <c r="C2633" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2633">
+        <v>1</v>
+      </c>
+      <c r="F2633">
+        <v>0.1</v>
+      </c>
+      <c r="G2633">
+        <v>0</v>
+      </c>
+      <c r="H2633">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2634" spans="3:8">
+      <c r="D2634">
+        <v>2</v>
+      </c>
+      <c r="F2634">
+        <v>0.1</v>
+      </c>
+      <c r="G2634">
+        <v>0</v>
+      </c>
+      <c r="H2634">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2635" spans="3:8">
+      <c r="D2635">
+        <v>3</v>
+      </c>
+      <c r="F2635">
+        <v>0.1</v>
+      </c>
+      <c r="G2635">
+        <v>0</v>
+      </c>
+      <c r="H2635">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2636" spans="3:8">
+      <c r="C2636" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2636">
+        <v>1</v>
+      </c>
+      <c r="F2636">
+        <v>0.1</v>
+      </c>
+      <c r="G2636">
+        <v>2.52</v>
+      </c>
+      <c r="H2636">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="2637" spans="3:8">
+      <c r="D2637">
+        <v>2</v>
+      </c>
+      <c r="F2637">
+        <v>0.1</v>
+      </c>
+      <c r="G2637">
+        <v>0</v>
+      </c>
+      <c r="H2637">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2638" spans="3:8">
+      <c r="D2638">
+        <v>3</v>
+      </c>
+      <c r="F2638">
+        <v>0.1</v>
+      </c>
+      <c r="G2638">
+        <v>0</v>
+      </c>
+      <c r="H2638">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2639" spans="3:8">
+      <c r="C2639" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D2639">
+        <v>1</v>
+      </c>
+      <c r="F2639">
+        <v>0.1</v>
+      </c>
+      <c r="G2639">
+        <v>0</v>
+      </c>
+      <c r="H2639">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2640" spans="3:8">
+      <c r="D2640">
+        <v>2</v>
+      </c>
+      <c r="F2640">
+        <v>0.1</v>
+      </c>
+      <c r="G2640">
+        <v>0</v>
+      </c>
+      <c r="H2640">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2641" spans="1:16">
+      <c r="D2641">
+        <v>3</v>
+      </c>
+      <c r="F2641">
+        <v>0.1</v>
+      </c>
+      <c r="G2641">
+        <v>0</v>
+      </c>
+      <c r="H2641">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2642" spans="1:16">
+      <c r="C2642" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D2642">
+        <v>1</v>
+      </c>
+      <c r="F2642">
+        <v>0.1</v>
+      </c>
+      <c r="G2642">
+        <v>0</v>
+      </c>
+      <c r="H2642">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2643" spans="1:16">
+      <c r="C2643" s="3"/>
+      <c r="D2643">
+        <v>2</v>
+      </c>
+      <c r="F2643">
+        <v>0.1</v>
+      </c>
+      <c r="G2643">
+        <v>0</v>
+      </c>
+      <c r="H2643">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2644" spans="1:16">
+      <c r="D2644">
+        <v>3</v>
+      </c>
+      <c r="F2644">
+        <v>0.1</v>
+      </c>
+      <c r="G2644">
+        <v>0</v>
+      </c>
+      <c r="H2644">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2645" spans="1:16" s="19" customFormat="1">
+      <c r="E2645" s="36"/>
+    </row>
+    <row r="2646" spans="1:16">
+      <c r="A2646" t="s">
+        <v>388</v>
+      </c>
+      <c r="C2646" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2646">
+        <v>1</v>
+      </c>
+      <c r="E2646" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2646">
+        <v>0.1</v>
+      </c>
+      <c r="G2646">
+        <v>0</v>
+      </c>
+      <c r="H2646">
+        <v>0</v>
+      </c>
+      <c r="P2646" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="2647" spans="1:16">
+      <c r="D2647">
+        <v>2</v>
+      </c>
+      <c r="F2647">
+        <v>0.1</v>
+      </c>
+      <c r="G2647">
+        <v>0</v>
+      </c>
+      <c r="H2647">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2648" spans="1:16">
+      <c r="D2648">
+        <v>3</v>
+      </c>
+      <c r="F2648">
+        <v>0.1</v>
+      </c>
+      <c r="G2648">
+        <v>0</v>
+      </c>
+      <c r="H2648">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2649" spans="1:16">
+      <c r="C2649" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2649">
+        <v>1</v>
+      </c>
+      <c r="F2649">
+        <v>0.1</v>
+      </c>
+      <c r="G2649">
+        <v>0</v>
+      </c>
+      <c r="H2649">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2650" spans="1:16">
+      <c r="D2650">
+        <v>2</v>
+      </c>
+      <c r="F2650">
+        <v>0.1</v>
+      </c>
+      <c r="G2650">
+        <v>0</v>
+      </c>
+      <c r="H2650">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2651" spans="1:16">
+      <c r="D2651">
+        <v>3</v>
+      </c>
+      <c r="F2651">
+        <v>0.1</v>
+      </c>
+      <c r="G2651">
+        <v>0</v>
+      </c>
+      <c r="H2651">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2652" spans="1:16">
+      <c r="C2652" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2652">
+        <v>1</v>
+      </c>
+      <c r="F2652">
+        <v>0.1</v>
+      </c>
+      <c r="G2652">
+        <v>0</v>
+      </c>
+      <c r="H2652">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2653" spans="1:16">
+      <c r="D2653">
+        <v>2</v>
+      </c>
+      <c r="F2653">
+        <v>0.1</v>
+      </c>
+      <c r="G2653">
+        <v>0.25</v>
+      </c>
+      <c r="H2653">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="2654" spans="1:16">
+      <c r="D2654">
+        <v>3</v>
+      </c>
+      <c r="F2654">
+        <v>0.1</v>
+      </c>
+      <c r="G2654">
+        <v>0.3</v>
+      </c>
+      <c r="H2654">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="2655" spans="1:16">
+      <c r="C2655" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D2655">
+        <v>1</v>
+      </c>
+      <c r="F2655">
+        <v>0.1</v>
+      </c>
+      <c r="G2655">
+        <v>0.65</v>
+      </c>
+      <c r="H2655">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="2656" spans="1:16">
+      <c r="D2656">
+        <v>2</v>
+      </c>
+      <c r="F2656">
+        <v>0.1</v>
+      </c>
+      <c r="G2656">
+        <v>0</v>
+      </c>
+      <c r="H2656">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2657" spans="3:8">
+      <c r="D2657">
+        <v>3</v>
+      </c>
+      <c r="F2657">
+        <v>0.1</v>
+      </c>
+      <c r="G2657">
+        <v>0</v>
+      </c>
+      <c r="H2657">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2658" spans="3:8">
+      <c r="C2658" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2658">
+        <v>1</v>
+      </c>
+      <c r="F2658">
+        <v>0.1</v>
+      </c>
+      <c r="G2658">
+        <v>1.29</v>
+      </c>
+      <c r="H2658">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="2659" spans="3:8">
+      <c r="D2659">
+        <v>2</v>
+      </c>
+      <c r="F2659">
+        <v>0.1</v>
+      </c>
+      <c r="G2659">
+        <v>1.19</v>
+      </c>
+      <c r="H2659">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="2660" spans="3:8">
+      <c r="D2660">
+        <v>3</v>
+      </c>
+      <c r="F2660">
+        <v>0.1</v>
+      </c>
+      <c r="G2660">
+        <v>1.24</v>
+      </c>
+      <c r="H2660">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="2661" spans="3:8">
+      <c r="C2661" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2661">
+        <v>1</v>
+      </c>
+      <c r="F2661">
+        <v>13.17</v>
+      </c>
+      <c r="G2661">
+        <v>0.7</v>
+      </c>
+      <c r="H2661">
+        <v>18.75</v>
+      </c>
+    </row>
+    <row r="2662" spans="3:8">
+      <c r="D2662">
+        <v>2</v>
+      </c>
+      <c r="F2662">
+        <v>10.78</v>
+      </c>
+      <c r="G2662">
+        <v>1.19</v>
+      </c>
+      <c r="H2662">
+        <v>9.0500000000000007</v>
+      </c>
+    </row>
+    <row r="2663" spans="3:8">
+      <c r="D2663">
+        <v>3</v>
+      </c>
+      <c r="F2663">
+        <v>0.1</v>
+      </c>
+      <c r="G2663">
+        <v>1</v>
+      </c>
+      <c r="H2663">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="2664" spans="3:8">
+      <c r="C2664" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2664">
+        <v>1</v>
+      </c>
+      <c r="F2664">
+        <v>0.1</v>
+      </c>
+      <c r="G2664">
+        <v>0</v>
+      </c>
+      <c r="H2664">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2665" spans="3:8">
+      <c r="D2665">
+        <v>2</v>
+      </c>
+      <c r="F2665">
+        <v>0.1</v>
+      </c>
+      <c r="G2665">
+        <v>0</v>
+      </c>
+      <c r="H2665">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2666" spans="3:8">
+      <c r="D2666">
+        <v>3</v>
+      </c>
+      <c r="F2666">
+        <v>0.1</v>
+      </c>
+      <c r="G2666">
+        <v>0</v>
+      </c>
+      <c r="H2666">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2667" spans="3:8">
+      <c r="C2667" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2667">
+        <v>1</v>
+      </c>
+      <c r="F2667">
+        <v>0.1</v>
+      </c>
+      <c r="G2667">
+        <v>0</v>
+      </c>
+      <c r="H2667">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2668" spans="3:8">
+      <c r="D2668">
+        <v>2</v>
+      </c>
+      <c r="F2668">
+        <v>0.1</v>
+      </c>
+      <c r="G2668">
+        <v>0</v>
+      </c>
+      <c r="H2668">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2669" spans="3:8">
+      <c r="D2669">
+        <v>3</v>
+      </c>
+      <c r="F2669">
+        <v>0.1</v>
+      </c>
+      <c r="G2669">
+        <v>0</v>
+      </c>
+      <c r="H2669">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2670" spans="3:8">
+      <c r="C2670" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D2670">
+        <v>1</v>
+      </c>
+      <c r="F2670">
+        <v>0.1</v>
+      </c>
+      <c r="G2670">
+        <v>0</v>
+      </c>
+      <c r="H2670">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2671" spans="3:8">
+      <c r="D2671">
+        <v>2</v>
+      </c>
+      <c r="F2671">
+        <v>0.1</v>
+      </c>
+      <c r="G2671">
+        <v>0</v>
+      </c>
+      <c r="H2671">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2672" spans="3:8">
+      <c r="D2672">
+        <v>3</v>
+      </c>
+      <c r="F2672">
+        <v>0.1</v>
+      </c>
+      <c r="G2672">
+        <v>0</v>
+      </c>
+      <c r="H2672">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2673" spans="1:16">
+      <c r="C2673" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D2673">
+        <v>1</v>
+      </c>
+      <c r="F2673">
+        <v>0.1</v>
+      </c>
+      <c r="G2673">
+        <v>0</v>
+      </c>
+      <c r="H2673">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2674" spans="1:16">
+      <c r="C2674" s="3"/>
+      <c r="D2674">
+        <v>2</v>
+      </c>
+      <c r="F2674">
+        <v>0.1</v>
+      </c>
+      <c r="G2674">
+        <v>0</v>
+      </c>
+      <c r="H2674">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2675" spans="1:16">
+      <c r="D2675">
+        <v>3</v>
+      </c>
+      <c r="F2675">
+        <v>0.1</v>
+      </c>
+      <c r="G2675">
+        <v>0</v>
+      </c>
+      <c r="H2675">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2676" spans="1:16" s="19" customFormat="1">
+      <c r="E2676" s="36"/>
+    </row>
+    <row r="2677" spans="1:16">
+      <c r="A2677" t="s">
+        <v>389</v>
+      </c>
+      <c r="C2677" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2677">
+        <v>1</v>
+      </c>
+      <c r="E2677" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2677">
+        <v>0.1</v>
+      </c>
+      <c r="G2677">
+        <v>0</v>
+      </c>
+      <c r="H2677">
+        <v>0</v>
+      </c>
+      <c r="P2677" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="2678" spans="1:16">
+      <c r="D2678">
+        <v>2</v>
+      </c>
+      <c r="F2678">
+        <v>0.1</v>
+      </c>
+      <c r="G2678">
+        <v>0</v>
+      </c>
+      <c r="H2678">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2679" spans="1:16">
+      <c r="D2679">
+        <v>3</v>
+      </c>
+      <c r="F2679">
+        <v>0.1</v>
+      </c>
+      <c r="G2679">
+        <v>0</v>
+      </c>
+      <c r="H2679">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2680" spans="1:16">
+      <c r="C2680" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2680">
+        <v>1</v>
+      </c>
+      <c r="F2680">
+        <v>0.1</v>
+      </c>
+      <c r="G2680">
+        <v>0</v>
+      </c>
+      <c r="H2680">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2681" spans="1:16">
+      <c r="D2681">
+        <v>2</v>
+      </c>
+      <c r="F2681">
+        <v>0.1</v>
+      </c>
+      <c r="G2681">
+        <v>0</v>
+      </c>
+      <c r="H2681">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2682" spans="1:16">
+      <c r="D2682">
+        <v>3</v>
+      </c>
+      <c r="F2682">
+        <v>0.1</v>
+      </c>
+      <c r="G2682">
+        <v>0</v>
+      </c>
+      <c r="H2682">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2683" spans="1:16">
+      <c r="C2683" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2683">
+        <v>1</v>
+      </c>
+      <c r="F2683">
+        <v>0.1</v>
+      </c>
+      <c r="G2683">
+        <v>0</v>
+      </c>
+      <c r="H2683">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2684" spans="1:16">
+      <c r="D2684">
+        <v>2</v>
+      </c>
+      <c r="F2684">
+        <v>0.1</v>
+      </c>
+      <c r="G2684">
+        <v>0</v>
+      </c>
+      <c r="H2684">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2685" spans="1:16">
+      <c r="D2685">
+        <v>3</v>
+      </c>
+      <c r="F2685">
+        <v>0.1</v>
+      </c>
+      <c r="G2685">
+        <v>0</v>
+      </c>
+      <c r="H2685">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2686" spans="1:16">
+      <c r="C2686" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D2686">
+        <v>1</v>
+      </c>
+      <c r="F2686">
+        <v>0.1</v>
+      </c>
+      <c r="G2686">
+        <v>0</v>
+      </c>
+      <c r="H2686">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2687" spans="1:16">
+      <c r="D2687">
+        <v>2</v>
+      </c>
+      <c r="F2687">
+        <v>0.1</v>
+      </c>
+      <c r="G2687">
+        <v>0</v>
+      </c>
+      <c r="H2687">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2688" spans="1:16">
+      <c r="D2688">
+        <v>3</v>
+      </c>
+      <c r="F2688">
+        <v>0.1</v>
+      </c>
+      <c r="G2688">
+        <v>0</v>
+      </c>
+      <c r="H2688">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2689" spans="3:8">
+      <c r="C2689" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2689">
+        <v>1</v>
+      </c>
+      <c r="F2689">
+        <v>0.1</v>
+      </c>
+      <c r="G2689">
+        <v>0</v>
+      </c>
+      <c r="H2689">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2690" spans="3:8">
+      <c r="D2690">
+        <v>2</v>
+      </c>
+      <c r="F2690">
+        <v>0.1</v>
+      </c>
+      <c r="G2690">
+        <v>0</v>
+      </c>
+      <c r="H2690">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2691" spans="3:8">
+      <c r="D2691">
+        <v>3</v>
+      </c>
+      <c r="F2691">
+        <v>0.1</v>
+      </c>
+      <c r="G2691">
+        <v>0</v>
+      </c>
+      <c r="H2691">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2692" spans="3:8">
+      <c r="C2692" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2692">
+        <v>1</v>
+      </c>
+      <c r="F2692">
+        <v>0.1</v>
+      </c>
+      <c r="G2692">
+        <v>0.35</v>
+      </c>
+      <c r="H2692">
+        <v>0.28000000000000003</v>
+      </c>
+    </row>
+    <row r="2693" spans="3:8">
+      <c r="D2693">
+        <v>2</v>
+      </c>
+      <c r="F2693">
+        <v>0.1</v>
+      </c>
+      <c r="G2693">
+        <v>0</v>
+      </c>
+      <c r="H2693">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2694" spans="3:8">
+      <c r="D2694">
+        <v>3</v>
+      </c>
+      <c r="F2694">
+        <v>31.91</v>
+      </c>
+      <c r="G2694">
+        <v>2.42</v>
+      </c>
+      <c r="H2694">
+        <v>13.18</v>
+      </c>
+    </row>
+    <row r="2695" spans="3:8">
+      <c r="C2695" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2695">
+        <v>1</v>
+      </c>
+      <c r="F2695">
+        <v>0.1</v>
+      </c>
+      <c r="G2695">
+        <v>0</v>
+      </c>
+      <c r="H2695">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2696" spans="3:8">
+      <c r="D2696">
+        <v>2</v>
+      </c>
+      <c r="F2696">
+        <v>0.1</v>
+      </c>
+      <c r="G2696">
+        <v>0</v>
+      </c>
+      <c r="H2696">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2697" spans="3:8">
+      <c r="D2697">
+        <v>3</v>
+      </c>
+      <c r="F2697">
+        <v>0.1</v>
+      </c>
+      <c r="G2697">
+        <v>0</v>
+      </c>
+      <c r="H2697">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2698" spans="3:8">
+      <c r="C2698" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2698">
+        <v>1</v>
+      </c>
+      <c r="F2698">
+        <v>0.1</v>
+      </c>
+      <c r="G2698">
+        <v>0</v>
+      </c>
+      <c r="H2698">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2699" spans="3:8">
+      <c r="D2699">
+        <v>2</v>
+      </c>
+      <c r="F2699">
+        <v>0.1</v>
+      </c>
+      <c r="G2699">
+        <v>0</v>
+      </c>
+      <c r="H2699">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2700" spans="3:8">
+      <c r="D2700">
+        <v>3</v>
+      </c>
+      <c r="F2700">
+        <v>0.1</v>
+      </c>
+      <c r="G2700">
+        <v>0.35</v>
+      </c>
+      <c r="H2700">
+        <v>0.28000000000000003</v>
+      </c>
+    </row>
+    <row r="2701" spans="3:8">
+      <c r="C2701" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D2701">
+        <v>1</v>
+      </c>
+      <c r="F2701">
+        <v>0.1</v>
+      </c>
+      <c r="G2701">
+        <v>2.13</v>
+      </c>
+      <c r="H2701">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="2702" spans="3:8">
+      <c r="D2702">
+        <v>2</v>
+      </c>
+      <c r="F2702">
+        <v>0.1</v>
+      </c>
+      <c r="G2702">
+        <v>0.65</v>
+      </c>
+      <c r="H2702">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="2703" spans="3:8">
+      <c r="D2703">
+        <v>3</v>
+      </c>
+      <c r="F2703">
+        <v>0.1</v>
+      </c>
+      <c r="G2703">
+        <v>3.31</v>
+      </c>
+      <c r="H2703">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="2704" spans="3:8">
+      <c r="C2704" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D2704">
+        <v>1</v>
+      </c>
+      <c r="F2704">
+        <v>0.1</v>
+      </c>
+      <c r="G2704">
+        <v>0</v>
+      </c>
+      <c r="H2704">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2705" spans="3:8">
+      <c r="C2705" s="3"/>
+      <c r="D2705">
+        <v>2</v>
+      </c>
+      <c r="F2705">
+        <v>0.1</v>
+      </c>
+      <c r="G2705">
+        <v>0</v>
+      </c>
+      <c r="H2705">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2706" spans="3:8">
+      <c r="D2706">
+        <v>3</v>
+      </c>
+      <c r="F2706">
+        <v>0.1</v>
+      </c>
+      <c r="G2706">
+        <v>0</v>
+      </c>
+      <c r="H2706">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2707" spans="3:8" s="19" customFormat="1">
+      <c r="E2707" s="36"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/talt_cyano/talt_cyano_digitized.xlsx
+++ b/data/talt_cyano/talt_cyano_digitized.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29212"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29225"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="20435" documentId="11_0B1D56BE9CDCCE836B02CE7A5FB0D4A9BBFD1C62" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ED0097AE-E8BF-4194-85E9-A632FE632A20}"/>
+  <xr:revisionPtr revIDLastSave="20831" documentId="11_0B1D56BE9CDCCE836B02CE7A5FB0D4A9BBFD1C62" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CE9692C1-B11D-466F-9214-9CC4539DAEFC}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1854" uniqueCount="390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1878" uniqueCount="393">
   <si>
     <t>Date</t>
   </si>
@@ -1197,10 +1197,19 @@
     <t xml:space="preserve">18/08/2025 </t>
   </si>
   <si>
+    <t xml:space="preserve">0.34	</t>
+  </si>
+  <si>
     <t xml:space="preserve">20/08/2025 </t>
   </si>
   <si>
     <t xml:space="preserve">22/08/2025 </t>
+  </si>
+  <si>
+    <t>25/08/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29/08/2025 </t>
   </si>
 </sst>
 </file>
@@ -1758,7 +1767,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S2707"/>
+  <dimension ref="A1:S2769"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.7109375" customWidth="1"/>
@@ -68701,6 +68710,9 @@
       <c r="A2615" t="s">
         <v>387</v>
       </c>
+      <c r="B2615" s="1">
+        <v>0.43541666666666667</v>
+      </c>
       <c r="C2615" s="3" t="s">
         <v>20</v>
       </c>
@@ -68719,6 +68731,18 @@
       <c r="H2615">
         <v>0</v>
       </c>
+      <c r="L2615">
+        <v>11.3</v>
+      </c>
+      <c r="M2615">
+        <v>98.4</v>
+      </c>
+      <c r="N2615">
+        <v>1.01</v>
+      </c>
+      <c r="O2615" t="s">
+        <v>388</v>
+      </c>
       <c r="P2615" t="s">
         <v>319</v>
       </c>
@@ -68752,6 +68776,9 @@
       </c>
     </row>
     <row r="2618" spans="1:18">
+      <c r="B2618" s="1">
+        <v>0.45694444444444443</v>
+      </c>
       <c r="C2618" s="3" t="s">
         <v>25</v>
       </c>
@@ -68767,6 +68794,18 @@
       <c r="H2618">
         <v>0</v>
       </c>
+      <c r="L2618">
+        <v>12.6</v>
+      </c>
+      <c r="M2618">
+        <v>88.4</v>
+      </c>
+      <c r="N2618">
+        <v>2.84</v>
+      </c>
+      <c r="O2618">
+        <v>0.17</v>
+      </c>
     </row>
     <row r="2619" spans="1:18">
       <c r="D2619">
@@ -68797,6 +68836,9 @@
       </c>
     </row>
     <row r="2621" spans="1:18">
+      <c r="B2621" s="1">
+        <v>0.47430555555555554</v>
+      </c>
       <c r="C2621" s="3" t="s">
         <v>27</v>
       </c>
@@ -68812,6 +68854,18 @@
       <c r="H2621">
         <v>0.09</v>
       </c>
+      <c r="L2621">
+        <v>11.3</v>
+      </c>
+      <c r="M2621">
+        <v>99</v>
+      </c>
+      <c r="N2621">
+        <v>2.12</v>
+      </c>
+      <c r="O2621">
+        <v>0.22</v>
+      </c>
     </row>
     <row r="2622" spans="1:18">
       <c r="D2622">
@@ -68842,6 +68896,9 @@
       </c>
     </row>
     <row r="2624" spans="1:18">
+      <c r="B2624" s="1">
+        <v>0.49236111111111114</v>
+      </c>
       <c r="C2624" s="3" t="s">
         <v>58</v>
       </c>
@@ -68857,8 +68914,20 @@
       <c r="H2624">
         <v>2</v>
       </c>
-    </row>
-    <row r="2625" spans="3:8">
+      <c r="L2624">
+        <v>11.7</v>
+      </c>
+      <c r="M2624">
+        <v>90.6</v>
+      </c>
+      <c r="N2624">
+        <v>7.08</v>
+      </c>
+      <c r="O2624">
+        <v>4.43</v>
+      </c>
+    </row>
+    <row r="2625" spans="2:15">
       <c r="D2625">
         <v>2</v>
       </c>
@@ -68872,7 +68941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2626" spans="3:8">
+    <row r="2626" spans="2:15">
       <c r="D2626">
         <v>3</v>
       </c>
@@ -68886,7 +68955,10 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="2627" spans="3:8">
+    <row r="2627" spans="2:15">
+      <c r="B2627" s="1">
+        <v>0.50694444444444442</v>
+      </c>
       <c r="C2627" s="3" t="s">
         <v>29</v>
       </c>
@@ -68902,8 +68974,20 @@
       <c r="H2627">
         <v>0</v>
       </c>
-    </row>
-    <row r="2628" spans="3:8">
+      <c r="L2627">
+        <v>11.8</v>
+      </c>
+      <c r="M2627">
+        <v>111.2</v>
+      </c>
+      <c r="N2627">
+        <v>0.86</v>
+      </c>
+      <c r="O2627">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="2628" spans="2:15">
       <c r="D2628">
         <v>2</v>
       </c>
@@ -68917,7 +69001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2629" spans="3:8">
+    <row r="2629" spans="2:15">
       <c r="D2629">
         <v>3</v>
       </c>
@@ -68931,7 +69015,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2630" spans="3:8">
+    <row r="2630" spans="2:15">
+      <c r="B2630" s="1">
+        <v>0.51597222222222228</v>
+      </c>
       <c r="C2630" s="3" t="s">
         <v>30</v>
       </c>
@@ -68947,8 +69034,20 @@
       <c r="H2630">
         <v>0</v>
       </c>
-    </row>
-    <row r="2631" spans="3:8">
+      <c r="L2630">
+        <v>11.9</v>
+      </c>
+      <c r="M2630">
+        <v>105</v>
+      </c>
+      <c r="N2630">
+        <v>0.54</v>
+      </c>
+      <c r="O2630">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="2631" spans="2:15">
       <c r="D2631">
         <v>2</v>
       </c>
@@ -68962,7 +69061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2632" spans="3:8">
+    <row r="2632" spans="2:15">
       <c r="D2632">
         <v>3</v>
       </c>
@@ -68976,7 +69075,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2633" spans="3:8">
+    <row r="2633" spans="2:15">
+      <c r="B2633" s="1">
+        <v>0.52916666666666667</v>
+      </c>
       <c r="C2633" s="3" t="s">
         <v>31</v>
       </c>
@@ -68992,8 +69094,20 @@
       <c r="H2633">
         <v>0</v>
       </c>
-    </row>
-    <row r="2634" spans="3:8">
+      <c r="L2633">
+        <v>12.3</v>
+      </c>
+      <c r="M2633">
+        <v>102.9</v>
+      </c>
+      <c r="N2633">
+        <v>0.31</v>
+      </c>
+      <c r="O2633">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="2634" spans="2:15">
       <c r="D2634">
         <v>2</v>
       </c>
@@ -69007,7 +69121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2635" spans="3:8">
+    <row r="2635" spans="2:15">
       <c r="D2635">
         <v>3</v>
       </c>
@@ -69021,7 +69135,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2636" spans="3:8">
+    <row r="2636" spans="2:15">
+      <c r="B2636" s="1">
+        <v>0.54305555555555551</v>
+      </c>
       <c r="C2636" s="3" t="s">
         <v>32</v>
       </c>
@@ -69037,8 +69154,20 @@
       <c r="H2636">
         <v>0.03</v>
       </c>
-    </row>
-    <row r="2637" spans="3:8">
+      <c r="L2636">
+        <v>11.9</v>
+      </c>
+      <c r="M2636">
+        <v>100.4</v>
+      </c>
+      <c r="N2636">
+        <v>0.87</v>
+      </c>
+      <c r="O2636">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="2637" spans="2:15">
       <c r="D2637">
         <v>2</v>
       </c>
@@ -69052,7 +69181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2638" spans="3:8">
+    <row r="2638" spans="2:15">
       <c r="D2638">
         <v>3</v>
       </c>
@@ -69066,7 +69195,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2639" spans="3:8">
+    <row r="2639" spans="2:15">
+      <c r="B2639" s="1">
+        <v>0.56666666666666665</v>
+      </c>
       <c r="C2639" s="3" t="s">
         <v>41</v>
       </c>
@@ -69082,8 +69214,20 @@
       <c r="H2639">
         <v>0</v>
       </c>
-    </row>
-    <row r="2640" spans="3:8">
+      <c r="L2639">
+        <v>12.5</v>
+      </c>
+      <c r="M2639">
+        <v>103.4</v>
+      </c>
+      <c r="N2639">
+        <v>1.34</v>
+      </c>
+      <c r="O2639">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="2640" spans="2:15">
       <c r="D2640">
         <v>2</v>
       </c>
@@ -69112,6 +69256,9 @@
       </c>
     </row>
     <row r="2642" spans="1:16">
+      <c r="B2642" s="1">
+        <v>0.5756944444444444</v>
+      </c>
       <c r="C2642" s="3" t="s">
         <v>34</v>
       </c>
@@ -69126,6 +69273,18 @@
       </c>
       <c r="H2642">
         <v>0</v>
+      </c>
+      <c r="L2642">
+        <v>13.2</v>
+      </c>
+      <c r="M2642">
+        <v>94.1</v>
+      </c>
+      <c r="N2642">
+        <v>2.4700000000000002</v>
+      </c>
+      <c r="O2642">
+        <v>0.27</v>
       </c>
     </row>
     <row r="2643" spans="1:16">
@@ -69162,7 +69321,10 @@
     </row>
     <row r="2646" spans="1:16">
       <c r="A2646" t="s">
-        <v>388</v>
+        <v>389</v>
+      </c>
+      <c r="B2646" s="1">
+        <v>0.48958333333333331</v>
       </c>
       <c r="C2646" s="3" t="s">
         <v>20</v>
@@ -69182,6 +69344,18 @@
       <c r="H2646">
         <v>0</v>
       </c>
+      <c r="L2646">
+        <v>10.8</v>
+      </c>
+      <c r="M2646">
+        <v>90.6</v>
+      </c>
+      <c r="N2646">
+        <v>4.1500000000000004</v>
+      </c>
+      <c r="O2646">
+        <v>0.08</v>
+      </c>
       <c r="P2646" t="s">
         <v>147</v>
       </c>
@@ -69215,6 +69389,9 @@
       </c>
     </row>
     <row r="2649" spans="1:16">
+      <c r="B2649" s="1">
+        <v>0.50069444444444444</v>
+      </c>
       <c r="C2649" s="3" t="s">
         <v>25</v>
       </c>
@@ -69230,6 +69407,18 @@
       <c r="H2649">
         <v>0</v>
       </c>
+      <c r="L2649">
+        <v>10.8</v>
+      </c>
+      <c r="M2649">
+        <v>95.8</v>
+      </c>
+      <c r="N2649">
+        <v>4.93</v>
+      </c>
+      <c r="O2649">
+        <v>0.15</v>
+      </c>
     </row>
     <row r="2650" spans="1:16">
       <c r="D2650">
@@ -69260,6 +69449,9 @@
       </c>
     </row>
     <row r="2652" spans="1:16">
+      <c r="B2652" s="1">
+        <v>0.51597222222222228</v>
+      </c>
       <c r="C2652" s="3" t="s">
         <v>27</v>
       </c>
@@ -69275,6 +69467,18 @@
       <c r="H2652">
         <v>0</v>
       </c>
+      <c r="L2652">
+        <v>9.9</v>
+      </c>
+      <c r="M2652">
+        <v>97.1</v>
+      </c>
+      <c r="N2652">
+        <v>10.51</v>
+      </c>
+      <c r="O2652">
+        <v>0.28000000000000003</v>
+      </c>
     </row>
     <row r="2653" spans="1:16">
       <c r="D2653">
@@ -69305,6 +69509,9 @@
       </c>
     </row>
     <row r="2655" spans="1:16">
+      <c r="B2655" s="1">
+        <v>0.52569444444444446</v>
+      </c>
       <c r="C2655" s="3" t="s">
         <v>58</v>
       </c>
@@ -69320,6 +69527,18 @@
       <c r="H2655">
         <v>0.15</v>
       </c>
+      <c r="L2655">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="M2655">
+        <v>99.3</v>
+      </c>
+      <c r="N2655">
+        <v>13.22</v>
+      </c>
+      <c r="O2655">
+        <v>0.91</v>
+      </c>
     </row>
     <row r="2656" spans="1:16">
       <c r="D2656">
@@ -69335,7 +69554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2657" spans="3:8">
+    <row r="2657" spans="2:15">
       <c r="D2657">
         <v>3</v>
       </c>
@@ -69349,7 +69568,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2658" spans="3:8">
+    <row r="2658" spans="2:15">
+      <c r="B2658" s="1">
+        <v>0.53611111111111109</v>
+      </c>
       <c r="C2658" s="3" t="s">
         <v>29</v>
       </c>
@@ -69365,8 +69587,20 @@
       <c r="H2658">
         <v>7.0000000000000007E-2</v>
       </c>
-    </row>
-    <row r="2659" spans="3:8">
+      <c r="L2658">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="M2658">
+        <v>101.3</v>
+      </c>
+      <c r="N2658">
+        <v>15.49</v>
+      </c>
+      <c r="O2658">
+        <v>2.31</v>
+      </c>
+    </row>
+    <row r="2659" spans="2:15">
       <c r="D2659">
         <v>2</v>
       </c>
@@ -69380,7 +69614,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="2660" spans="3:8">
+    <row r="2660" spans="2:15">
       <c r="D2660">
         <v>3</v>
       </c>
@@ -69394,7 +69628,10 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="2661" spans="3:8">
+    <row r="2661" spans="2:15">
+      <c r="B2661" s="1">
+        <v>0.54652777777777772</v>
+      </c>
       <c r="C2661" s="3" t="s">
         <v>30</v>
       </c>
@@ -69410,8 +69647,20 @@
       <c r="H2661">
         <v>18.75</v>
       </c>
-    </row>
-    <row r="2662" spans="3:8">
+      <c r="L2661">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="M2661">
+        <v>96.7</v>
+      </c>
+      <c r="N2661">
+        <v>20.260000000000002</v>
+      </c>
+      <c r="O2661">
+        <v>3.07</v>
+      </c>
+    </row>
+    <row r="2662" spans="2:15">
       <c r="D2662">
         <v>2</v>
       </c>
@@ -69425,7 +69674,7 @@
         <v>9.0500000000000007</v>
       </c>
     </row>
-    <row r="2663" spans="3:8">
+    <row r="2663" spans="2:15">
       <c r="D2663">
         <v>3</v>
       </c>
@@ -69439,7 +69688,10 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="2664" spans="3:8">
+    <row r="2664" spans="2:15">
+      <c r="B2664" s="1">
+        <v>0.5541666666666667</v>
+      </c>
       <c r="C2664" s="3" t="s">
         <v>31</v>
       </c>
@@ -69455,8 +69707,20 @@
       <c r="H2664">
         <v>0</v>
       </c>
-    </row>
-    <row r="2665" spans="3:8">
+      <c r="L2664">
+        <v>12.6</v>
+      </c>
+      <c r="M2664">
+        <v>102.8</v>
+      </c>
+      <c r="N2664">
+        <v>3.31</v>
+      </c>
+      <c r="O2664">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="2665" spans="2:15">
       <c r="D2665">
         <v>2</v>
       </c>
@@ -69470,7 +69734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2666" spans="3:8">
+    <row r="2666" spans="2:15">
       <c r="D2666">
         <v>3</v>
       </c>
@@ -69484,7 +69748,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2667" spans="3:8">
+    <row r="2667" spans="2:15">
+      <c r="B2667" s="1">
+        <v>0.56111111111111112</v>
+      </c>
       <c r="C2667" s="3" t="s">
         <v>32</v>
       </c>
@@ -69500,8 +69767,20 @@
       <c r="H2667">
         <v>0</v>
       </c>
-    </row>
-    <row r="2668" spans="3:8">
+      <c r="L2667">
+        <v>10.4</v>
+      </c>
+      <c r="M2667">
+        <v>98.8</v>
+      </c>
+      <c r="N2667">
+        <v>9.1199999999999992</v>
+      </c>
+      <c r="O2667">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="2668" spans="2:15">
       <c r="D2668">
         <v>2</v>
       </c>
@@ -69515,7 +69794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2669" spans="3:8">
+    <row r="2669" spans="2:15">
       <c r="D2669">
         <v>3</v>
       </c>
@@ -69529,7 +69808,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2670" spans="3:8">
+    <row r="2670" spans="2:15">
+      <c r="B2670" s="1">
+        <v>0.57708333333333328</v>
+      </c>
       <c r="C2670" s="3" t="s">
         <v>41</v>
       </c>
@@ -69545,8 +69827,20 @@
       <c r="H2670">
         <v>0</v>
       </c>
-    </row>
-    <row r="2671" spans="3:8">
+      <c r="L2670">
+        <v>11.5</v>
+      </c>
+      <c r="M2670">
+        <v>105.1</v>
+      </c>
+      <c r="N2670">
+        <v>1.66</v>
+      </c>
+      <c r="O2670">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="2671" spans="2:15">
       <c r="D2671">
         <v>2</v>
       </c>
@@ -69560,7 +69854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2672" spans="3:8">
+    <row r="2672" spans="2:15">
       <c r="D2672">
         <v>3</v>
       </c>
@@ -69575,6 +69869,9 @@
       </c>
     </row>
     <row r="2673" spans="1:16">
+      <c r="B2673" s="1">
+        <v>0.58333333333333337</v>
+      </c>
       <c r="C2673" s="3" t="s">
         <v>34</v>
       </c>
@@ -69589,6 +69886,18 @@
       </c>
       <c r="H2673">
         <v>0</v>
+      </c>
+      <c r="L2673">
+        <v>11</v>
+      </c>
+      <c r="M2673">
+        <v>96.6</v>
+      </c>
+      <c r="N2673">
+        <v>1.94</v>
+      </c>
+      <c r="O2673">
+        <v>0.04</v>
       </c>
     </row>
     <row r="2674" spans="1:16">
@@ -69625,7 +69934,10 @@
     </row>
     <row r="2677" spans="1:16">
       <c r="A2677" t="s">
-        <v>389</v>
+        <v>390</v>
+      </c>
+      <c r="B2677" s="1">
+        <v>0.50069444444444444</v>
       </c>
       <c r="C2677" s="3" t="s">
         <v>20</v>
@@ -69645,6 +69957,18 @@
       <c r="H2677">
         <v>0</v>
       </c>
+      <c r="L2677">
+        <v>12.2</v>
+      </c>
+      <c r="M2677">
+        <v>95.7</v>
+      </c>
+      <c r="N2677">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="O2677">
+        <v>0.08</v>
+      </c>
       <c r="P2677" t="s">
         <v>157</v>
       </c>
@@ -69678,6 +70002,9 @@
       </c>
     </row>
     <row r="2680" spans="1:16">
+      <c r="B2680" s="1">
+        <v>0.5180555555555556</v>
+      </c>
       <c r="C2680" s="3" t="s">
         <v>25</v>
       </c>
@@ -69693,6 +70020,18 @@
       <c r="H2680">
         <v>0</v>
       </c>
+      <c r="L2680">
+        <v>11.3</v>
+      </c>
+      <c r="M2680">
+        <v>100.3</v>
+      </c>
+      <c r="N2680">
+        <v>1.94</v>
+      </c>
+      <c r="O2680">
+        <v>0.15</v>
+      </c>
     </row>
     <row r="2681" spans="1:16">
       <c r="D2681">
@@ -69723,6 +70062,9 @@
       </c>
     </row>
     <row r="2683" spans="1:16">
+      <c r="B2683" s="1">
+        <v>0.57152777777777775</v>
+      </c>
       <c r="C2683" s="3" t="s">
         <v>27</v>
       </c>
@@ -69738,6 +70080,18 @@
       <c r="H2683">
         <v>0</v>
       </c>
+      <c r="L2683">
+        <v>11.5</v>
+      </c>
+      <c r="M2683">
+        <v>92.8</v>
+      </c>
+      <c r="N2683">
+        <v>1.75</v>
+      </c>
+      <c r="O2683">
+        <v>0.06</v>
+      </c>
     </row>
     <row r="2684" spans="1:16">
       <c r="D2684">
@@ -69768,6 +70122,9 @@
       </c>
     </row>
     <row r="2686" spans="1:16">
+      <c r="B2686" s="1">
+        <v>0.58958333333333335</v>
+      </c>
       <c r="C2686" s="3" t="s">
         <v>58</v>
       </c>
@@ -69783,6 +70140,18 @@
       <c r="H2686">
         <v>0</v>
       </c>
+      <c r="L2686">
+        <v>10.9</v>
+      </c>
+      <c r="M2686">
+        <v>102.5</v>
+      </c>
+      <c r="N2686">
+        <v>1.41</v>
+      </c>
+      <c r="O2686">
+        <v>0.05</v>
+      </c>
     </row>
     <row r="2687" spans="1:16">
       <c r="D2687">
@@ -69812,7 +70181,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2689" spans="3:8">
+    <row r="2689" spans="2:15">
+      <c r="B2689" s="1">
+        <v>0.61319444444444449</v>
+      </c>
       <c r="C2689" s="3" t="s">
         <v>29</v>
       </c>
@@ -69828,8 +70200,20 @@
       <c r="H2689">
         <v>0</v>
       </c>
-    </row>
-    <row r="2690" spans="3:8">
+      <c r="L2689">
+        <v>10.7</v>
+      </c>
+      <c r="M2689">
+        <v>103.6</v>
+      </c>
+      <c r="N2689">
+        <v>4.34</v>
+      </c>
+      <c r="O2689">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="2690" spans="2:15">
       <c r="D2690">
         <v>2</v>
       </c>
@@ -69843,7 +70227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2691" spans="3:8">
+    <row r="2691" spans="2:15">
       <c r="D2691">
         <v>3</v>
       </c>
@@ -69857,7 +70241,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2692" spans="3:8">
+    <row r="2692" spans="2:15">
+      <c r="B2692" s="1">
+        <v>0.63194444444444442</v>
+      </c>
       <c r="C2692" s="3" t="s">
         <v>30</v>
       </c>
@@ -69873,8 +70260,20 @@
       <c r="H2692">
         <v>0.28000000000000003</v>
       </c>
-    </row>
-    <row r="2693" spans="3:8">
+      <c r="L2692">
+        <v>11</v>
+      </c>
+      <c r="M2692">
+        <v>104.3</v>
+      </c>
+      <c r="N2692">
+        <v>2.39</v>
+      </c>
+      <c r="O2692">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="2693" spans="2:15">
       <c r="D2693">
         <v>2</v>
       </c>
@@ -69888,7 +70287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2694" spans="3:8">
+    <row r="2694" spans="2:15">
       <c r="D2694">
         <v>3</v>
       </c>
@@ -69902,7 +70301,10 @@
         <v>13.18</v>
       </c>
     </row>
-    <row r="2695" spans="3:8">
+    <row r="2695" spans="2:15">
+      <c r="B2695" s="1">
+        <v>0.64513888888888893</v>
+      </c>
       <c r="C2695" s="3" t="s">
         <v>31</v>
       </c>
@@ -69918,8 +70320,20 @@
       <c r="H2695">
         <v>0</v>
       </c>
-    </row>
-    <row r="2696" spans="3:8">
+      <c r="L2695">
+        <v>12</v>
+      </c>
+      <c r="M2695">
+        <v>101.6</v>
+      </c>
+      <c r="N2695">
+        <v>1.49</v>
+      </c>
+      <c r="O2695">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="2696" spans="2:15">
       <c r="D2696">
         <v>2</v>
       </c>
@@ -69933,7 +70347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2697" spans="3:8">
+    <row r="2697" spans="2:15">
       <c r="D2697">
         <v>3</v>
       </c>
@@ -69947,7 +70361,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2698" spans="3:8">
+    <row r="2698" spans="2:15">
+      <c r="B2698" s="1">
+        <v>0.65833333333333333</v>
+      </c>
       <c r="C2698" s="3" t="s">
         <v>32</v>
       </c>
@@ -69963,8 +70380,20 @@
       <c r="H2698">
         <v>0</v>
       </c>
-    </row>
-    <row r="2699" spans="3:8">
+      <c r="L2698">
+        <v>11.6</v>
+      </c>
+      <c r="M2698">
+        <v>105.6</v>
+      </c>
+      <c r="N2698">
+        <v>1.98</v>
+      </c>
+      <c r="O2698">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="2699" spans="2:15">
       <c r="D2699">
         <v>2</v>
       </c>
@@ -69978,7 +70407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2700" spans="3:8">
+    <row r="2700" spans="2:15">
       <c r="D2700">
         <v>3</v>
       </c>
@@ -69992,7 +70421,10 @@
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="2701" spans="3:8">
+    <row r="2701" spans="2:15">
+      <c r="B2701" s="1">
+        <v>0.67222222222222228</v>
+      </c>
       <c r="C2701" s="3" t="s">
         <v>41</v>
       </c>
@@ -70008,8 +70440,20 @@
       <c r="H2701">
         <v>0.04</v>
       </c>
-    </row>
-    <row r="2702" spans="3:8">
+      <c r="L2701">
+        <v>12.6</v>
+      </c>
+      <c r="M2701">
+        <v>105.8</v>
+      </c>
+      <c r="N2701">
+        <v>6.63</v>
+      </c>
+      <c r="O2701">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="2702" spans="2:15">
       <c r="D2702">
         <v>2</v>
       </c>
@@ -70023,7 +70467,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="2703" spans="3:8">
+    <row r="2703" spans="2:15">
       <c r="D2703">
         <v>3</v>
       </c>
@@ -70037,7 +70481,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="2704" spans="3:8">
+    <row r="2704" spans="2:15">
       <c r="C2704" s="3" t="s">
         <v>34</v>
       </c>
@@ -70053,8 +70497,20 @@
       <c r="H2704">
         <v>0</v>
       </c>
-    </row>
-    <row r="2705" spans="3:8">
+      <c r="L2704">
+        <v>14.3</v>
+      </c>
+      <c r="M2704">
+        <v>106.6</v>
+      </c>
+      <c r="N2704">
+        <v>9.81</v>
+      </c>
+      <c r="O2704">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="2705" spans="1:15">
       <c r="C2705" s="3"/>
       <c r="D2705">
         <v>2</v>
@@ -70069,7 +70525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2706" spans="3:8">
+    <row r="2706" spans="1:15">
       <c r="D2706">
         <v>3</v>
       </c>
@@ -70083,8 +70539,1225 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2707" spans="3:8" s="19" customFormat="1">
+    <row r="2707" spans="1:15" s="19" customFormat="1">
       <c r="E2707" s="36"/>
+    </row>
+    <row r="2708" spans="1:15">
+      <c r="A2708" t="s">
+        <v>391</v>
+      </c>
+      <c r="B2708" s="1">
+        <v>0.55833333333333335</v>
+      </c>
+      <c r="C2708" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2708">
+        <v>1</v>
+      </c>
+      <c r="E2708" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2708">
+        <v>0.1</v>
+      </c>
+      <c r="G2708">
+        <v>0</v>
+      </c>
+      <c r="H2708">
+        <v>0</v>
+      </c>
+      <c r="L2708">
+        <v>12.5</v>
+      </c>
+      <c r="M2708">
+        <v>97.5</v>
+      </c>
+      <c r="N2708">
+        <v>0.98</v>
+      </c>
+      <c r="O2708">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="2709" spans="1:15">
+      <c r="D2709">
+        <v>2</v>
+      </c>
+      <c r="F2709">
+        <v>0.1</v>
+      </c>
+      <c r="G2709">
+        <v>0</v>
+      </c>
+      <c r="H2709">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2710" spans="1:15">
+      <c r="D2710">
+        <v>3</v>
+      </c>
+      <c r="F2710">
+        <v>0.1</v>
+      </c>
+      <c r="G2710">
+        <v>0</v>
+      </c>
+      <c r="H2710">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2711" spans="1:15">
+      <c r="B2711" s="1">
+        <v>0.57013888888888886</v>
+      </c>
+      <c r="C2711" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2711">
+        <v>1</v>
+      </c>
+      <c r="F2711">
+        <v>0.1</v>
+      </c>
+      <c r="G2711">
+        <v>0</v>
+      </c>
+      <c r="H2711">
+        <v>0</v>
+      </c>
+      <c r="L2711">
+        <v>11.7</v>
+      </c>
+      <c r="M2711">
+        <v>95.2</v>
+      </c>
+      <c r="N2711">
+        <v>3.69</v>
+      </c>
+      <c r="O2711">
+        <v>0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="2712" spans="1:15">
+      <c r="D2712">
+        <v>2</v>
+      </c>
+      <c r="F2712">
+        <v>0.1</v>
+      </c>
+      <c r="G2712">
+        <v>0</v>
+      </c>
+      <c r="H2712">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2713" spans="1:15">
+      <c r="D2713">
+        <v>3</v>
+      </c>
+      <c r="F2713">
+        <v>0.1</v>
+      </c>
+      <c r="G2713">
+        <v>0</v>
+      </c>
+      <c r="H2713">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2714" spans="1:15">
+      <c r="B2714" s="1">
+        <v>0.57986111111111116</v>
+      </c>
+      <c r="C2714" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2714">
+        <v>1</v>
+      </c>
+      <c r="F2714">
+        <v>0.1</v>
+      </c>
+      <c r="G2714">
+        <v>0</v>
+      </c>
+      <c r="H2714">
+        <v>0</v>
+      </c>
+      <c r="L2714">
+        <v>11.1</v>
+      </c>
+      <c r="M2714">
+        <v>100.1</v>
+      </c>
+      <c r="N2714">
+        <v>0.76</v>
+      </c>
+      <c r="O2714">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="2715" spans="1:15">
+      <c r="D2715">
+        <v>2</v>
+      </c>
+      <c r="F2715">
+        <v>0.1</v>
+      </c>
+      <c r="G2715">
+        <v>0</v>
+      </c>
+      <c r="H2715">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2716" spans="1:15">
+      <c r="D2716">
+        <v>3</v>
+      </c>
+      <c r="F2716">
+        <v>0.1</v>
+      </c>
+      <c r="G2716">
+        <v>0</v>
+      </c>
+      <c r="H2716">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2717" spans="1:15">
+      <c r="B2717" s="1">
+        <v>0.59097222222222223</v>
+      </c>
+      <c r="C2717" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D2717">
+        <v>1</v>
+      </c>
+      <c r="F2717">
+        <v>0.1</v>
+      </c>
+      <c r="G2717">
+        <v>0</v>
+      </c>
+      <c r="H2717">
+        <v>0</v>
+      </c>
+      <c r="L2717">
+        <v>11.5</v>
+      </c>
+      <c r="M2717">
+        <v>101.3</v>
+      </c>
+      <c r="N2717">
+        <v>0.64</v>
+      </c>
+      <c r="O2717">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="2718" spans="1:15">
+      <c r="D2718">
+        <v>2</v>
+      </c>
+      <c r="F2718">
+        <v>0.1</v>
+      </c>
+      <c r="G2718">
+        <v>0</v>
+      </c>
+      <c r="H2718">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2719" spans="1:15">
+      <c r="D2719">
+        <v>3</v>
+      </c>
+      <c r="F2719">
+        <v>0.1</v>
+      </c>
+      <c r="G2719">
+        <v>0</v>
+      </c>
+      <c r="H2719">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2720" spans="1:15">
+      <c r="B2720" s="1">
+        <v>0.60277777777777775</v>
+      </c>
+      <c r="C2720" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2720">
+        <v>1</v>
+      </c>
+      <c r="F2720">
+        <v>0.1</v>
+      </c>
+      <c r="G2720">
+        <v>0</v>
+      </c>
+      <c r="H2720">
+        <v>0</v>
+      </c>
+      <c r="L2720">
+        <v>11.4</v>
+      </c>
+      <c r="M2720">
+        <v>108.2</v>
+      </c>
+      <c r="N2720">
+        <v>0.68</v>
+      </c>
+      <c r="O2720">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="2721" spans="2:15">
+      <c r="D2721">
+        <v>2</v>
+      </c>
+      <c r="F2721">
+        <v>0.1</v>
+      </c>
+      <c r="G2721">
+        <v>0</v>
+      </c>
+      <c r="H2721">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2722" spans="2:15">
+      <c r="D2722">
+        <v>3</v>
+      </c>
+      <c r="F2722">
+        <v>0.1</v>
+      </c>
+      <c r="G2722">
+        <v>0</v>
+      </c>
+      <c r="H2722">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2723" spans="2:15">
+      <c r="B2723" s="1">
+        <v>0.60833333333333328</v>
+      </c>
+      <c r="C2723" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2723">
+        <v>1</v>
+      </c>
+      <c r="F2723">
+        <v>0.1</v>
+      </c>
+      <c r="G2723">
+        <v>0</v>
+      </c>
+      <c r="H2723">
+        <v>0</v>
+      </c>
+      <c r="L2723">
+        <v>11.3</v>
+      </c>
+      <c r="M2723">
+        <v>103.9</v>
+      </c>
+      <c r="N2723">
+        <v>0.67</v>
+      </c>
+      <c r="O2723">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="2724" spans="2:15">
+      <c r="D2724">
+        <v>2</v>
+      </c>
+      <c r="F2724">
+        <v>0.1</v>
+      </c>
+      <c r="G2724">
+        <v>0</v>
+      </c>
+      <c r="H2724">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2725" spans="2:15">
+      <c r="D2725">
+        <v>3</v>
+      </c>
+      <c r="F2725">
+        <v>0.1</v>
+      </c>
+      <c r="G2725">
+        <v>0</v>
+      </c>
+      <c r="H2725">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2726" spans="2:15">
+      <c r="B2726" s="1">
+        <v>0.61805555555555558</v>
+      </c>
+      <c r="C2726" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2726">
+        <v>1</v>
+      </c>
+      <c r="F2726">
+        <v>0.1</v>
+      </c>
+      <c r="G2726">
+        <v>0</v>
+      </c>
+      <c r="H2726">
+        <v>0</v>
+      </c>
+      <c r="L2726">
+        <v>12.9</v>
+      </c>
+      <c r="M2726">
+        <v>100.4</v>
+      </c>
+      <c r="N2726">
+        <v>0.23</v>
+      </c>
+      <c r="O2726">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="2727" spans="2:15">
+      <c r="D2727">
+        <v>2</v>
+      </c>
+      <c r="F2727">
+        <v>0.1</v>
+      </c>
+      <c r="G2727">
+        <v>0</v>
+      </c>
+      <c r="H2727">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2728" spans="2:15">
+      <c r="D2728">
+        <v>3</v>
+      </c>
+      <c r="F2728">
+        <v>0.1</v>
+      </c>
+      <c r="G2728">
+        <v>0</v>
+      </c>
+      <c r="H2728">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2729" spans="2:15">
+      <c r="B2729" s="1">
+        <v>0.63402777777777775</v>
+      </c>
+      <c r="C2729" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2729">
+        <v>1</v>
+      </c>
+      <c r="F2729">
+        <v>0.1</v>
+      </c>
+      <c r="G2729">
+        <v>0</v>
+      </c>
+      <c r="H2729">
+        <v>0</v>
+      </c>
+      <c r="L2729">
+        <v>11.6</v>
+      </c>
+      <c r="M2729">
+        <v>96.7</v>
+      </c>
+      <c r="N2729">
+        <v>1.28</v>
+      </c>
+      <c r="O2729">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="2730" spans="2:15">
+      <c r="D2730">
+        <v>2</v>
+      </c>
+      <c r="F2730">
+        <v>0.1</v>
+      </c>
+      <c r="G2730">
+        <v>0</v>
+      </c>
+      <c r="H2730">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2731" spans="2:15">
+      <c r="D2731">
+        <v>3</v>
+      </c>
+      <c r="F2731">
+        <v>0.1</v>
+      </c>
+      <c r="G2731">
+        <v>0</v>
+      </c>
+      <c r="H2731">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2732" spans="2:15">
+      <c r="B2732" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="C2732" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D2732">
+        <v>1</v>
+      </c>
+      <c r="F2732">
+        <v>0.1</v>
+      </c>
+      <c r="G2732">
+        <v>10.78</v>
+      </c>
+      <c r="H2732">
+        <v>0</v>
+      </c>
+      <c r="L2732">
+        <v>12.6</v>
+      </c>
+      <c r="M2732">
+        <v>101.4</v>
+      </c>
+      <c r="N2732">
+        <v>3.71</v>
+      </c>
+      <c r="O2732">
+        <v>2.68</v>
+      </c>
+    </row>
+    <row r="2733" spans="2:15">
+      <c r="D2733">
+        <v>2</v>
+      </c>
+      <c r="F2733">
+        <v>0</v>
+      </c>
+      <c r="G2733">
+        <v>9.01</v>
+      </c>
+      <c r="H2733">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="2734" spans="2:15">
+      <c r="D2734">
+        <v>3</v>
+      </c>
+      <c r="F2734">
+        <v>0.1</v>
+      </c>
+      <c r="G2734">
+        <v>3.01</v>
+      </c>
+      <c r="H2734">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="2735" spans="2:15">
+      <c r="B2735" s="1">
+        <v>0.66319444444444442</v>
+      </c>
+      <c r="C2735" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D2735">
+        <v>1</v>
+      </c>
+      <c r="F2735">
+        <v>0.1</v>
+      </c>
+      <c r="G2735">
+        <v>1.04</v>
+      </c>
+      <c r="H2735">
+        <v>0.09</v>
+      </c>
+      <c r="L2735">
+        <v>13.9</v>
+      </c>
+      <c r="M2735">
+        <v>98.9</v>
+      </c>
+      <c r="N2735">
+        <v>2.31</v>
+      </c>
+      <c r="O2735">
+        <v>1.69</v>
+      </c>
+    </row>
+    <row r="2736" spans="2:15">
+      <c r="C2736" s="3"/>
+      <c r="D2736">
+        <v>2</v>
+      </c>
+      <c r="F2736">
+        <v>0.1</v>
+      </c>
+      <c r="G2736">
+        <v>5.37</v>
+      </c>
+      <c r="H2736">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="2737" spans="1:15">
+      <c r="D2737">
+        <v>3</v>
+      </c>
+      <c r="F2737">
+        <v>0.1</v>
+      </c>
+      <c r="G2737">
+        <v>7.44</v>
+      </c>
+      <c r="H2737">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="2738" spans="1:15" s="19" customFormat="1">
+      <c r="E2738" s="36"/>
+    </row>
+    <row r="2739" spans="1:15">
+      <c r="A2739" t="s">
+        <v>392</v>
+      </c>
+      <c r="B2739" s="1">
+        <v>0.57152777777777775</v>
+      </c>
+      <c r="C2739" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2739">
+        <v>1</v>
+      </c>
+      <c r="F2739">
+        <v>0.1</v>
+      </c>
+      <c r="G2739">
+        <v>2.27</v>
+      </c>
+      <c r="H2739">
+        <v>0.04</v>
+      </c>
+      <c r="L2739">
+        <v>13.1</v>
+      </c>
+      <c r="M2739">
+        <v>96.8</v>
+      </c>
+      <c r="N2739">
+        <v>13.21</v>
+      </c>
+      <c r="O2739">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="2740" spans="1:15">
+      <c r="D2740">
+        <v>2</v>
+      </c>
+      <c r="F2740">
+        <v>0.1</v>
+      </c>
+      <c r="G2740">
+        <v>1.73</v>
+      </c>
+      <c r="H2740">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="2741" spans="1:15">
+      <c r="D2741">
+        <v>3</v>
+      </c>
+      <c r="F2741">
+        <v>0.1</v>
+      </c>
+      <c r="G2741">
+        <v>2.81</v>
+      </c>
+      <c r="H2741">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="2742" spans="1:15">
+      <c r="B2742" s="1">
+        <v>0.55277777777777781</v>
+      </c>
+      <c r="C2742" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2742">
+        <v>1</v>
+      </c>
+      <c r="F2742">
+        <v>0.1</v>
+      </c>
+      <c r="G2742">
+        <v>1.39</v>
+      </c>
+      <c r="H2742">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="L2742">
+        <v>12.9</v>
+      </c>
+      <c r="M2742">
+        <v>95.4</v>
+      </c>
+      <c r="N2742">
+        <v>21.71</v>
+      </c>
+      <c r="O2742">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="2743" spans="1:15">
+      <c r="D2743">
+        <v>2</v>
+      </c>
+      <c r="F2743">
+        <v>0.1</v>
+      </c>
+      <c r="G2743">
+        <v>1.04</v>
+      </c>
+      <c r="H2743">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="2744" spans="1:15">
+      <c r="D2744">
+        <v>3</v>
+      </c>
+      <c r="F2744">
+        <v>0.1</v>
+      </c>
+      <c r="G2744">
+        <v>2.27</v>
+      </c>
+      <c r="H2744">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="2745" spans="1:15">
+      <c r="B2745" s="1">
+        <v>0.53541666666666665</v>
+      </c>
+      <c r="C2745" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2745">
+        <v>1</v>
+      </c>
+      <c r="F2745">
+        <v>19.39</v>
+      </c>
+      <c r="G2745">
+        <v>0</v>
+      </c>
+      <c r="H2745">
+        <v>0</v>
+      </c>
+      <c r="L2745">
+        <v>11.8</v>
+      </c>
+      <c r="M2745">
+        <v>93.9</v>
+      </c>
+      <c r="N2745">
+        <v>13.29</v>
+      </c>
+      <c r="O2745">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="2746" spans="1:15">
+      <c r="D2746">
+        <v>2</v>
+      </c>
+      <c r="F2746">
+        <v>6.25</v>
+      </c>
+      <c r="G2746">
+        <v>0</v>
+      </c>
+      <c r="H2746">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2747" spans="1:15">
+      <c r="D2747">
+        <v>3</v>
+      </c>
+      <c r="F2747">
+        <v>0.1</v>
+      </c>
+      <c r="G2747">
+        <v>1</v>
+      </c>
+      <c r="H2747">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="2748" spans="1:15">
+      <c r="B2748" s="1">
+        <v>0.52013888888888893</v>
+      </c>
+      <c r="C2748" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D2748">
+        <v>1</v>
+      </c>
+      <c r="F2748">
+        <v>6.25</v>
+      </c>
+      <c r="G2748">
+        <v>3.01</v>
+      </c>
+      <c r="H2748">
+        <v>2.0699999999999998</v>
+      </c>
+      <c r="L2748">
+        <v>12.2</v>
+      </c>
+      <c r="M2748">
+        <v>88.4</v>
+      </c>
+      <c r="N2748">
+        <v>76.72</v>
+      </c>
+      <c r="O2748">
+        <v>9.84</v>
+      </c>
+    </row>
+    <row r="2749" spans="1:15">
+      <c r="D2749">
+        <v>2</v>
+      </c>
+      <c r="F2749">
+        <v>35.82</v>
+      </c>
+      <c r="G2749">
+        <v>1.34</v>
+      </c>
+      <c r="H2749">
+        <v>26.73</v>
+      </c>
+    </row>
+    <row r="2750" spans="1:15">
+      <c r="D2750">
+        <v>3</v>
+      </c>
+      <c r="F2750">
+        <v>96.08</v>
+      </c>
+      <c r="G2750">
+        <v>4.63</v>
+      </c>
+      <c r="H2750">
+        <v>20.75</v>
+      </c>
+    </row>
+    <row r="2751" spans="1:15">
+      <c r="B2751" s="1">
+        <v>0.48888888888888887</v>
+      </c>
+      <c r="C2751" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2751">
+        <v>1</v>
+      </c>
+      <c r="F2751">
+        <v>0.1</v>
+      </c>
+      <c r="G2751">
+        <v>0.05</v>
+      </c>
+      <c r="H2751">
+        <v>2</v>
+      </c>
+      <c r="L2751">
+        <v>12.6</v>
+      </c>
+      <c r="M2751">
+        <v>96.1</v>
+      </c>
+      <c r="N2751">
+        <v>7.11</v>
+      </c>
+      <c r="O2751">
+        <v>3.56</v>
+      </c>
+    </row>
+    <row r="2752" spans="1:15">
+      <c r="D2752">
+        <v>2</v>
+      </c>
+      <c r="F2752">
+        <v>0.1</v>
+      </c>
+      <c r="G2752">
+        <v>2.77</v>
+      </c>
+      <c r="H2752">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="2753" spans="2:15">
+      <c r="D2753">
+        <v>3</v>
+      </c>
+      <c r="F2753">
+        <v>0.1</v>
+      </c>
+      <c r="G2753">
+        <v>3.95</v>
+      </c>
+      <c r="H2753">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="2754" spans="2:15">
+      <c r="B2754" s="1">
+        <v>0.4826388888888889</v>
+      </c>
+      <c r="C2754" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2754">
+        <v>1</v>
+      </c>
+      <c r="F2754">
+        <v>0.1</v>
+      </c>
+      <c r="G2754">
+        <v>0.05</v>
+      </c>
+      <c r="H2754">
+        <v>2</v>
+      </c>
+      <c r="L2754">
+        <v>12.2</v>
+      </c>
+      <c r="M2754">
+        <v>99.2</v>
+      </c>
+      <c r="N2754">
+        <v>0.85</v>
+      </c>
+      <c r="O2754">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="2755" spans="2:15">
+      <c r="D2755">
+        <v>2</v>
+      </c>
+      <c r="F2755">
+        <v>7.75</v>
+      </c>
+      <c r="G2755">
+        <v>0.6</v>
+      </c>
+      <c r="H2755">
+        <v>12.91</v>
+      </c>
+    </row>
+    <row r="2756" spans="2:15">
+      <c r="D2756">
+        <v>3</v>
+      </c>
+      <c r="F2756">
+        <v>20.170000000000002</v>
+      </c>
+      <c r="G2756">
+        <v>0.75</v>
+      </c>
+      <c r="H2756">
+        <v>26.89</v>
+      </c>
+    </row>
+    <row r="2757" spans="2:15">
+      <c r="B2757" s="1">
+        <v>0.47569444444444442</v>
+      </c>
+      <c r="C2757" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2757">
+        <v>1</v>
+      </c>
+      <c r="F2757">
+        <v>20.95</v>
+      </c>
+      <c r="G2757">
+        <v>0.8</v>
+      </c>
+      <c r="H2757">
+        <v>26.18</v>
+      </c>
+      <c r="L2757">
+        <v>12.4</v>
+      </c>
+      <c r="M2757">
+        <v>98.6</v>
+      </c>
+      <c r="N2757">
+        <v>0.71</v>
+      </c>
+      <c r="O2757">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="2758" spans="2:15">
+      <c r="D2758">
+        <v>2</v>
+      </c>
+      <c r="F2758">
+        <v>79.650000000000006</v>
+      </c>
+      <c r="G2758">
+        <v>1.29</v>
+      </c>
+      <c r="H2758">
+        <v>61.74</v>
+      </c>
+    </row>
+    <row r="2759" spans="2:15">
+      <c r="D2759">
+        <v>3</v>
+      </c>
+      <c r="F2759">
+        <v>25.65</v>
+      </c>
+      <c r="G2759">
+        <v>1.04</v>
+      </c>
+      <c r="H2759">
+        <v>24.66</v>
+      </c>
+    </row>
+    <row r="2760" spans="2:15">
+      <c r="B2760" s="1">
+        <v>0.41041666666666665</v>
+      </c>
+      <c r="C2760" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2760">
+        <v>1</v>
+      </c>
+      <c r="F2760">
+        <v>34.25</v>
+      </c>
+      <c r="G2760">
+        <v>0.95</v>
+      </c>
+      <c r="H2760">
+        <v>36.06</v>
+      </c>
+      <c r="L2760">
+        <v>11</v>
+      </c>
+      <c r="M2760">
+        <v>97.3</v>
+      </c>
+      <c r="N2760">
+        <v>0.92</v>
+      </c>
+      <c r="O2760">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="2761" spans="2:15">
+      <c r="D2761">
+        <v>2</v>
+      </c>
+      <c r="F2761">
+        <v>7.75</v>
+      </c>
+      <c r="G2761">
+        <v>0.4</v>
+      </c>
+      <c r="H2761">
+        <v>19.37</v>
+      </c>
+    </row>
+    <row r="2762" spans="2:15">
+      <c r="D2762">
+        <v>3</v>
+      </c>
+      <c r="F2762">
+        <v>40.520000000000003</v>
+      </c>
+      <c r="G2762">
+        <v>1.29</v>
+      </c>
+      <c r="H2762">
+        <v>31.41</v>
+      </c>
+    </row>
+    <row r="2763" spans="2:15">
+      <c r="B2763" s="1">
+        <v>0.4548611111111111</v>
+      </c>
+      <c r="C2763" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D2763">
+        <v>1</v>
+      </c>
+      <c r="F2763">
+        <v>0.1</v>
+      </c>
+      <c r="G2763">
+        <v>0.3</v>
+      </c>
+      <c r="H2763">
+        <v>0.33</v>
+      </c>
+      <c r="L2763">
+        <v>12.2</v>
+      </c>
+      <c r="M2763">
+        <v>98.7</v>
+      </c>
+      <c r="N2763">
+        <v>0.81</v>
+      </c>
+      <c r="O2763">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="2764" spans="2:15">
+      <c r="D2764">
+        <v>2</v>
+      </c>
+      <c r="F2764">
+        <v>36.6</v>
+      </c>
+      <c r="G2764">
+        <v>0.75</v>
+      </c>
+      <c r="H2764">
+        <v>48.8</v>
+      </c>
+    </row>
+    <row r="2765" spans="2:15">
+      <c r="D2765">
+        <v>3</v>
+      </c>
+      <c r="F2765">
+        <v>39.729999999999997</v>
+      </c>
+      <c r="G2765">
+        <v>0.85</v>
+      </c>
+      <c r="H2765">
+        <v>46.74</v>
+      </c>
+    </row>
+    <row r="2766" spans="2:15">
+      <c r="B2766" s="1">
+        <v>0.58888888888888891</v>
+      </c>
+      <c r="C2766" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D2766">
+        <v>1</v>
+      </c>
+      <c r="F2766">
+        <v>0.1</v>
+      </c>
+      <c r="G2766">
+        <v>1.63</v>
+      </c>
+      <c r="H2766">
+        <v>0.06</v>
+      </c>
+      <c r="L2766">
+        <v>15.3</v>
+      </c>
+      <c r="M2766">
+        <v>97.6</v>
+      </c>
+      <c r="N2766">
+        <v>0.84</v>
+      </c>
+      <c r="O2766">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="2767" spans="2:15">
+      <c r="C2767" s="3"/>
+      <c r="D2767">
+        <v>2</v>
+      </c>
+      <c r="F2767">
+        <v>0.1</v>
+      </c>
+      <c r="G2767">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="H2767">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="2768" spans="2:15">
+      <c r="D2768">
+        <v>3</v>
+      </c>
+      <c r="F2768">
+        <v>0.1</v>
+      </c>
+      <c r="G2768">
+        <v>1.73</v>
+      </c>
+      <c r="H2768">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="2769" spans="5:5" s="19" customFormat="1">
+      <c r="E2769" s="36"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
